--- a/VerveStacks_IND_grids_kan60/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND_grids_kan60/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan60\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E21C97D-6B3F-4481-A9E3-FAEA43CEAA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B299EE-78C9-4CE1-AA1C-AA6254221D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12772" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -1233,18 +1233,42 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IND_010</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_037</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_041</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_050</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 50</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IND_003</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 3</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_IND_005</t>
   </si>
   <si>
@@ -1281,6 +1305,168 @@
     <t>connecting solar to buses in cluster 73</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IND_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IND_024</t>
   </si>
   <si>
@@ -1305,6 +1491,192 @@
     <t>connecting solar to buses in cluster 72</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IND_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_022</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_029</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_030</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_035</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_060</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_070</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 70</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_071</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 71</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IND_013</t>
   </si>
   <si>
@@ -1335,384 +1707,24 @@
     <t>connecting solar to buses in cluster 76</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_010</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_037</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_041</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_050</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_022</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_029</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_030</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_035</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_060</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 60</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_070</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 70</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_071</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 71</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Gaya_IND</t>
+  </si>
+  <si>
+    <t>e_Raichur_IND</t>
+  </si>
+  <si>
+    <t>e_Kakinada_IND</t>
+  </si>
+  <si>
+    <t>e_Mainpuri_IND</t>
+  </si>
+  <si>
     <t>e_Gwalior_IND</t>
   </si>
   <si>
@@ -1734,118 +1746,214 @@
     <t>e_Sasaram_IND</t>
   </si>
   <si>
+    <t>e_Satna_IND</t>
+  </si>
+  <si>
+    <t>e_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>e_Moga_IND</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Bhatpara_IND</t>
+  </si>
+  <si>
+    <t>e_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>e_Asansol_IND</t>
+  </si>
+  <si>
+    <t>e_Indore_IND</t>
+  </si>
+  <si>
+    <t>e_Raipur_IND</t>
+  </si>
+  <si>
+    <t>e_Talcher_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND</t>
+  </si>
+  <si>
+    <t>e_ArniKaKhera_IND</t>
+  </si>
+  <si>
+    <t>e_Bhagalpur_IND</t>
+  </si>
+  <si>
+    <t>e_Meerut_IND</t>
+  </si>
+  <si>
+    <t>e_Aurangabad_IND</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND</t>
+  </si>
+  <si>
+    <t>e_BarmhanKalan_IND</t>
+  </si>
+  <si>
+    <t>e_Narasaraopet_IND</t>
+  </si>
+  <si>
+    <t>e_Jammu_IND</t>
+  </si>
+  <si>
     <t>e_Angul_IND</t>
   </si>
   <si>
     <t>e_Dharmapuri_IND</t>
   </si>
   <si>
-    <t>e_Kakinada_IND</t>
-  </si>
-  <si>
     <t>e_Bihar_IND</t>
   </si>
   <si>
+    <t>e_Singrauliya_IND</t>
+  </si>
+  <si>
+    <t>e_Nakhtarana_IND</t>
+  </si>
+  <si>
+    <t>e_Karaikandi_IND</t>
+  </si>
+  <si>
+    <t>e_Jabalpur_IND</t>
+  </si>
+  <si>
+    <t>e_Jharsugra_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>e_Bongaigaon_IND</t>
+  </si>
+  <si>
     <t>e_Cuddapah_IND</t>
   </si>
   <si>
     <t>e_Ajmer_IND</t>
   </si>
   <si>
-    <t>e_Bongaigaon_IND</t>
-  </si>
-  <si>
     <t>e_BokaroSteelCity_IND</t>
   </si>
   <si>
-    <t>e_Gaya_IND</t>
-  </si>
-  <si>
-    <t>e_Raichur_IND</t>
-  </si>
-  <si>
-    <t>e_Mainpuri_IND</t>
-  </si>
-  <si>
-    <t>e_Wardha_IND</t>
-  </si>
-  <si>
-    <t>e_Kurnool_IND</t>
-  </si>
-  <si>
-    <t>e_Jaipur_IND</t>
-  </si>
-  <si>
-    <t>e_Narasaraopet_IND</t>
-  </si>
-  <si>
-    <t>e_Bhagalpur_IND</t>
-  </si>
-  <si>
-    <t>e_Raipur_IND</t>
-  </si>
-  <si>
-    <t>e_Singrauliya_IND</t>
-  </si>
-  <si>
-    <t>e_Nakhtarana_IND</t>
-  </si>
-  <si>
-    <t>e_Karaikandi_IND</t>
-  </si>
-  <si>
-    <t>e_Korba_IND</t>
-  </si>
-  <si>
-    <t>e_ArniKaKhera_IND</t>
-  </si>
-  <si>
-    <t>e_Satna_IND</t>
-  </si>
-  <si>
-    <t>e_Vadodara_IND</t>
-  </si>
-  <si>
-    <t>e_Moga_IND</t>
-  </si>
-  <si>
-    <t>e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>e_Bhatpara_IND</t>
-  </si>
-  <si>
-    <t>e_Tezpur_IND</t>
-  </si>
-  <si>
-    <t>e_Asansol_IND</t>
-  </si>
-  <si>
-    <t>e_Indore_IND</t>
-  </si>
-  <si>
-    <t>e_Talcher_IND</t>
-  </si>
-  <si>
-    <t>e_Meerut_IND</t>
-  </si>
-  <si>
-    <t>e_Aurangabad_IND</t>
-  </si>
-  <si>
-    <t>e_Phalodi_IND</t>
-  </si>
-  <si>
-    <t>e_Jabalpur_IND</t>
-  </si>
-  <si>
-    <t>e_Jharsugra_IND</t>
-  </si>
-  <si>
-    <t>e_BarmhanKalan_IND</t>
-  </si>
-  <si>
-    <t>e_Jammu_IND</t>
+    <t>distr_wonelc_won_IND_009</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_021</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_040</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_046</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_066</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_016</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_047</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_061</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_020</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_063</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_006</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_023</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_035</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 35</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_049</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_053</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 53</t>
   </si>
   <si>
     <t>distr_wonelc_won_IND_014</t>
@@ -1866,34 +1974,238 @@
     <t>connecting wind onshore to buses in cluster 59</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_009</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_021</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_040</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_046</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_066</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 66</t>
+    <t>distr_wonelc_won_IND_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_018</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_022</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_024</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_025</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_026</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_032</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_045</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 45</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_052</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
   </si>
   <si>
     <t>distr_wonelc_won_IND_010</t>
@@ -1932,316 +2244,58 @@
     <t>connecting wind onshore to buses in cluster 60</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_016</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_047</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_061</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_018</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_022</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_024</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_025</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_026</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_032</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_045</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_052</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_006</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_023</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_035</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 35</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_049</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_053</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_020</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_063</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
+    <t>elc_won_IND_009</t>
+  </si>
+  <si>
+    <t>elc_won_IND_021</t>
+  </si>
+  <si>
+    <t>elc_won_IND_040</t>
+  </si>
+  <si>
+    <t>elc_won_IND_046</t>
+  </si>
+  <si>
+    <t>elc_won_IND_066</t>
+  </si>
+  <si>
+    <t>elc_won_IND_016</t>
+  </si>
+  <si>
+    <t>elc_won_IND_047</t>
+  </si>
+  <si>
+    <t>elc_won_IND_061</t>
+  </si>
+  <si>
+    <t>elc_won_IND_020</t>
+  </si>
+  <si>
+    <t>elc_won_IND_063</t>
+  </si>
+  <si>
+    <t>elc_won_IND_019</t>
+  </si>
+  <si>
+    <t>elc_won_IND_030</t>
+  </si>
+  <si>
+    <t>elc_won_IND_033</t>
+  </si>
+  <si>
+    <t>elc_won_IND_006</t>
+  </si>
+  <si>
+    <t>elc_won_IND_023</t>
+  </si>
+  <si>
+    <t>elc_won_IND_035</t>
+  </si>
+  <si>
+    <t>elc_won_IND_049</t>
+  </si>
+  <si>
+    <t>elc_won_IND_053</t>
   </si>
   <si>
     <t>elc_won_IND_014</t>
@@ -2253,19 +2307,121 @@
     <t>elc_won_IND_059</t>
   </si>
   <si>
-    <t>elc_won_IND_009</t>
-  </si>
-  <si>
-    <t>elc_won_IND_021</t>
-  </si>
-  <si>
-    <t>elc_won_IND_040</t>
-  </si>
-  <si>
-    <t>elc_won_IND_046</t>
-  </si>
-  <si>
-    <t>elc_won_IND_066</t>
+    <t>elc_won_IND_011</t>
+  </si>
+  <si>
+    <t>elc_won_IND_012</t>
+  </si>
+  <si>
+    <t>elc_won_IND_044</t>
+  </si>
+  <si>
+    <t>elc_won_IND_058</t>
+  </si>
+  <si>
+    <t>elc_won_IND_013</t>
+  </si>
+  <si>
+    <t>elc_won_IND_015</t>
+  </si>
+  <si>
+    <t>elc_won_IND_028</t>
+  </si>
+  <si>
+    <t>elc_won_IND_051</t>
+  </si>
+  <si>
+    <t>elc_won_IND_062</t>
+  </si>
+  <si>
+    <t>elc_won_IND_005</t>
+  </si>
+  <si>
+    <t>elc_won_IND_042</t>
+  </si>
+  <si>
+    <t>elc_won_IND_018</t>
+  </si>
+  <si>
+    <t>elc_won_IND_022</t>
+  </si>
+  <si>
+    <t>elc_won_IND_024</t>
+  </si>
+  <si>
+    <t>elc_won_IND_025</t>
+  </si>
+  <si>
+    <t>elc_won_IND_026</t>
+  </si>
+  <si>
+    <t>elc_won_IND_032</t>
+  </si>
+  <si>
+    <t>elc_won_IND_045</t>
+  </si>
+  <si>
+    <t>elc_won_IND_052</t>
+  </si>
+  <si>
+    <t>elc_won_IND_001</t>
+  </si>
+  <si>
+    <t>elc_won_IND_003</t>
+  </si>
+  <si>
+    <t>elc_won_IND_004</t>
+  </si>
+  <si>
+    <t>elc_won_IND_031</t>
+  </si>
+  <si>
+    <t>elc_won_IND_034</t>
+  </si>
+  <si>
+    <t>elc_won_IND_043</t>
+  </si>
+  <si>
+    <t>elc_won_IND_029</t>
+  </si>
+  <si>
+    <t>elc_won_IND_036</t>
+  </si>
+  <si>
+    <t>elc_won_IND_048</t>
+  </si>
+  <si>
+    <t>elc_won_IND_054</t>
+  </si>
+  <si>
+    <t>elc_won_IND_056</t>
+  </si>
+  <si>
+    <t>elc_won_IND_007</t>
+  </si>
+  <si>
+    <t>elc_won_IND_008</t>
+  </si>
+  <si>
+    <t>elc_won_IND_017</t>
+  </si>
+  <si>
+    <t>elc_won_IND_039</t>
+  </si>
+  <si>
+    <t>elc_won_IND_050</t>
+  </si>
+  <si>
+    <t>elc_won_IND_064</t>
+  </si>
+  <si>
+    <t>elc_won_IND_065</t>
+  </si>
+  <si>
+    <t>elc_won_IND_002</t>
+  </si>
+  <si>
+    <t>elc_won_IND_057</t>
   </si>
   <si>
     <t>elc_won_IND_010</t>
@@ -2286,160 +2442,46 @@
     <t>elc_won_IND_060</t>
   </si>
   <si>
-    <t>elc_won_IND_007</t>
-  </si>
-  <si>
-    <t>elc_won_IND_008</t>
-  </si>
-  <si>
-    <t>elc_won_IND_017</t>
-  </si>
-  <si>
-    <t>elc_won_IND_039</t>
-  </si>
-  <si>
-    <t>elc_won_IND_050</t>
-  </si>
-  <si>
-    <t>elc_won_IND_064</t>
-  </si>
-  <si>
-    <t>elc_won_IND_065</t>
-  </si>
-  <si>
-    <t>elc_won_IND_011</t>
-  </si>
-  <si>
-    <t>elc_won_IND_012</t>
-  </si>
-  <si>
-    <t>elc_won_IND_044</t>
-  </si>
-  <si>
-    <t>elc_won_IND_058</t>
-  </si>
-  <si>
-    <t>elc_won_IND_029</t>
-  </si>
-  <si>
-    <t>elc_won_IND_036</t>
-  </si>
-  <si>
-    <t>elc_won_IND_048</t>
-  </si>
-  <si>
-    <t>elc_won_IND_054</t>
-  </si>
-  <si>
-    <t>elc_won_IND_056</t>
-  </si>
-  <si>
-    <t>elc_won_IND_001</t>
-  </si>
-  <si>
-    <t>elc_won_IND_003</t>
-  </si>
-  <si>
-    <t>elc_won_IND_004</t>
-  </si>
-  <si>
-    <t>elc_won_IND_031</t>
-  </si>
-  <si>
-    <t>elc_won_IND_034</t>
-  </si>
-  <si>
-    <t>elc_won_IND_043</t>
-  </si>
-  <si>
-    <t>elc_won_IND_019</t>
-  </si>
-  <si>
-    <t>elc_won_IND_030</t>
-  </si>
-  <si>
-    <t>elc_won_IND_033</t>
-  </si>
-  <si>
-    <t>elc_won_IND_016</t>
-  </si>
-  <si>
-    <t>elc_won_IND_047</t>
-  </si>
-  <si>
-    <t>elc_won_IND_061</t>
-  </si>
-  <si>
-    <t>elc_won_IND_018</t>
-  </si>
-  <si>
-    <t>elc_won_IND_022</t>
-  </si>
-  <si>
-    <t>elc_won_IND_024</t>
-  </si>
-  <si>
-    <t>elc_won_IND_025</t>
-  </si>
-  <si>
-    <t>elc_won_IND_026</t>
-  </si>
-  <si>
-    <t>elc_won_IND_032</t>
-  </si>
-  <si>
-    <t>elc_won_IND_045</t>
-  </si>
-  <si>
-    <t>elc_won_IND_052</t>
-  </si>
-  <si>
-    <t>elc_won_IND_002</t>
-  </si>
-  <si>
-    <t>elc_won_IND_057</t>
-  </si>
-  <si>
-    <t>elc_won_IND_013</t>
-  </si>
-  <si>
-    <t>elc_won_IND_015</t>
-  </si>
-  <si>
-    <t>elc_won_IND_028</t>
-  </si>
-  <si>
-    <t>elc_won_IND_051</t>
-  </si>
-  <si>
-    <t>elc_won_IND_062</t>
-  </si>
-  <si>
-    <t>elc_won_IND_006</t>
-  </si>
-  <si>
-    <t>elc_won_IND_023</t>
-  </si>
-  <si>
-    <t>elc_won_IND_035</t>
-  </si>
-  <si>
-    <t>elc_won_IND_049</t>
-  </si>
-  <si>
-    <t>elc_won_IND_053</t>
-  </si>
-  <si>
-    <t>elc_won_IND_020</t>
-  </si>
-  <si>
-    <t>elc_won_IND_063</t>
-  </si>
-  <si>
-    <t>elc_won_IND_005</t>
-  </si>
-  <si>
-    <t>elc_won_IND_042</t>
+    <t>distr_wofelc_wof_IND_013</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_014</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_003</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_011</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_012</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_023</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_024</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 24</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IND_007</t>
@@ -2448,10 +2490,64 @@
     <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_014</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 14</t>
+    <t>distr_wofelc_wof_IND_005</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_021</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_010</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_018</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_008</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_015</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IND_001</t>
@@ -2460,48 +2556,6 @@
     <t>connecting wind offshore to buses in cluster 1</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_003</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_011</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_012</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_023</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_024</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_005</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_021</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 21</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_IND_002</t>
   </si>
   <si>
@@ -2514,6 +2568,12 @@
     <t>connecting wind offshore to buses in cluster 9</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_IND_016</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 16</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_IND_004</t>
   </si>
   <si>
@@ -2526,136 +2586,76 @@
     <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_010</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_018</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_016</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_013</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_008</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_015</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
+    <t>elc_wof_IND_013</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_014</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_003</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_011</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_012</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_023</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_024</t>
   </si>
   <si>
     <t>elc_wof_IND_007</t>
   </si>
   <si>
-    <t>elc_wof_IND_014</t>
+    <t>elc_wof_IND_005</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_021</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_010</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_018</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_017</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_022</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_008</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_015</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_019</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_020</t>
   </si>
   <si>
     <t>elc_wof_IND_001</t>
   </si>
   <si>
-    <t>elc_wof_IND_003</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_011</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_012</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_023</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_024</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_005</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_021</t>
-  </si>
-  <si>
     <t>elc_wof_IND_002</t>
   </si>
   <si>
     <t>elc_wof_IND_009</t>
   </si>
   <si>
+    <t>elc_wof_IND_016</t>
+  </si>
+  <si>
     <t>elc_wof_IND_004</t>
   </si>
   <si>
     <t>elc_wof_IND_006</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_010</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_018</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_016</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_013</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_008</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_015</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_019</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_017</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_022</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_020</t>
   </si>
   <si>
     <t>e_won_IND_001</t>
@@ -7512,7 +7512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7DF42AF-6F7D-4741-BC94-509813478C16}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63951672-8E43-413D-AAC4-06F71E9CAC43}">
   <dimension ref="B9:BD88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7750,16 +7750,16 @@
         <v>389</v>
       </c>
       <c r="Y11" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="Z11" t="s">
         <v>549</v>
       </c>
       <c r="AA11">
-        <v>0.9937576135345404</v>
+        <v>0.99574277994898297</v>
       </c>
       <c r="AB11">
-        <v>114.44375186676042</v>
+        <v>78.049034268645343</v>
       </c>
       <c r="AD11" t="s">
         <v>388</v>
@@ -7789,13 +7789,13 @@
         <v>726</v>
       </c>
       <c r="AN11" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
       <c r="AO11">
-        <v>0.99072423448493052</v>
+        <v>0.99460623000179826</v>
       </c>
       <c r="AP11">
-        <v>170.05570110960724</v>
+        <v>98.885783300365674</v>
       </c>
       <c r="AR11" t="s">
         <v>388</v>
@@ -7825,13 +7825,13 @@
         <v>840</v>
       </c>
       <c r="BB11" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="BC11">
-        <v>0.98617370816492766</v>
+        <v>0.98385755699927302</v>
       </c>
       <c r="BD11">
-        <v>913.05032219063128</v>
+        <v>941.2687638921899</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7896,16 +7896,16 @@
         <v>393</v>
       </c>
       <c r="Y12" t="s">
-        <v>313</v>
+        <v>345</v>
       </c>
       <c r="Z12" t="s">
         <v>550</v>
       </c>
       <c r="AA12">
-        <v>0.99492636929999068</v>
+        <v>0.98237714666165721</v>
       </c>
       <c r="AB12">
-        <v>93.016562833504807</v>
+        <v>323.08564453628389</v>
       </c>
       <c r="AD12" t="s">
         <v>388</v>
@@ -7935,13 +7935,13 @@
         <v>727</v>
       </c>
       <c r="AN12" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AO12">
-        <v>0.99538801767339902</v>
+        <v>0.99150673149027269</v>
       </c>
       <c r="AP12">
-        <v>84.553009321017754</v>
+        <v>155.70992267833407</v>
       </c>
       <c r="AR12" t="s">
         <v>388</v>
@@ -7971,7 +7971,7 @@
         <v>841</v>
       </c>
       <c r="BB12" t="s">
-        <v>592</v>
+        <v>577</v>
       </c>
       <c r="BC12">
         <v>0.97753834043268606</v>
@@ -8042,16 +8042,16 @@
         <v>395</v>
       </c>
       <c r="Y13" t="s">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="Z13" t="s">
         <v>551</v>
       </c>
       <c r="AA13">
-        <v>0.98434977749377373</v>
+        <v>0.98850112471309615</v>
       </c>
       <c r="AB13">
-        <v>286.9207459474826</v>
+        <v>210.81271359323659</v>
       </c>
       <c r="AD13" t="s">
         <v>388</v>
@@ -8081,13 +8081,13 @@
         <v>728</v>
       </c>
       <c r="AN13" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="AO13">
-        <v>0.98686185087293077</v>
+        <v>0.99428348998771221</v>
       </c>
       <c r="AP13">
-        <v>240.86606732960294</v>
+        <v>104.80268355861014</v>
       </c>
       <c r="AR13" t="s">
         <v>388</v>
@@ -8117,13 +8117,13 @@
         <v>842</v>
       </c>
       <c r="BB13" t="s">
-        <v>551</v>
+        <v>580</v>
       </c>
       <c r="BC13">
-        <v>0.97462367221641244</v>
+        <v>0.98473459040058986</v>
       </c>
       <c r="BD13">
-        <v>1053.7682601633755</v>
+        <v>930.58357361947958</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8188,16 +8188,16 @@
         <v>397</v>
       </c>
       <c r="Y14" t="s">
-        <v>339</v>
+        <v>358</v>
       </c>
       <c r="Z14" t="s">
         <v>552</v>
       </c>
       <c r="AA14">
-        <v>0.99326064633097277</v>
+        <v>0.99482221718343289</v>
       </c>
       <c r="AB14">
-        <v>123.55481726549976</v>
+        <v>94.926018303729833</v>
       </c>
       <c r="AD14" t="s">
         <v>388</v>
@@ -8227,13 +8227,13 @@
         <v>729</v>
       </c>
       <c r="AN14" t="s">
-        <v>585</v>
+        <v>564</v>
       </c>
       <c r="AO14">
-        <v>0.99460623000179826</v>
+        <v>0.99089509058322967</v>
       </c>
       <c r="AP14">
-        <v>98.885783300365674</v>
+        <v>166.92333930745593</v>
       </c>
       <c r="AR14" t="s">
         <v>388</v>
@@ -8263,13 +8263,13 @@
         <v>843</v>
       </c>
       <c r="BB14" t="s">
-        <v>556</v>
+        <v>577</v>
       </c>
       <c r="BC14">
-        <v>0.98473459040058986</v>
+        <v>0.9888190320671576</v>
       </c>
       <c r="BD14">
-        <v>930.58357361947958</v>
+        <v>880.82145931513014</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8334,16 +8334,16 @@
         <v>399</v>
       </c>
       <c r="Y15" t="s">
-        <v>364</v>
+        <v>311</v>
       </c>
       <c r="Z15" t="s">
         <v>553</v>
       </c>
       <c r="AA15">
-        <v>0.99457218279364812</v>
+        <v>0.9937576135345404</v>
       </c>
       <c r="AB15">
-        <v>99.509982116450402</v>
+        <v>114.44375186676042</v>
       </c>
       <c r="AD15" t="s">
         <v>388</v>
@@ -8373,13 +8373,13 @@
         <v>730</v>
       </c>
       <c r="AN15" t="s">
-        <v>556</v>
+        <v>573</v>
       </c>
       <c r="AO15">
-        <v>0.99150673149027269</v>
+        <v>0.99450138933360577</v>
       </c>
       <c r="AP15">
-        <v>155.70992267833407</v>
+        <v>100.80786221722684</v>
       </c>
       <c r="AR15" t="s">
         <v>388</v>
@@ -8409,13 +8409,13 @@
         <v>844</v>
       </c>
       <c r="BB15" t="s">
-        <v>592</v>
+        <v>577</v>
       </c>
       <c r="BC15">
-        <v>0.9888190320671576</v>
+        <v>0.98444840170938386</v>
       </c>
       <c r="BD15">
-        <v>880.82145931513014</v>
+        <v>934.07030584067388</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8480,16 +8480,16 @@
         <v>401</v>
       </c>
       <c r="Y16" t="s">
-        <v>372</v>
+        <v>313</v>
       </c>
       <c r="Z16" t="s">
         <v>554</v>
       </c>
       <c r="AA16">
-        <v>0.99259244228658239</v>
+        <v>0.99492636929999068</v>
       </c>
       <c r="AB16">
-        <v>135.80522474598871</v>
+        <v>93.016562833504807</v>
       </c>
       <c r="AD16" t="s">
         <v>388</v>
@@ -8519,13 +8519,13 @@
         <v>731</v>
       </c>
       <c r="AN16" t="s">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="AO16">
-        <v>0.99428348998771221</v>
+        <v>0.99429570648020904</v>
       </c>
       <c r="AP16">
-        <v>104.80268355861014</v>
+        <v>104.57871452950124</v>
       </c>
       <c r="AR16" t="s">
         <v>388</v>
@@ -8555,13 +8555,13 @@
         <v>845</v>
       </c>
       <c r="BB16" t="s">
-        <v>592</v>
+        <v>558</v>
       </c>
       <c r="BC16">
-        <v>0.98444840170938386</v>
+        <v>0.98664748299407956</v>
       </c>
       <c r="BD16">
-        <v>934.07030584067388</v>
+        <v>907.27816552213119</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8626,16 +8626,16 @@
         <v>403</v>
       </c>
       <c r="Y17" t="s">
-        <v>381</v>
+        <v>322</v>
       </c>
       <c r="Z17" t="s">
         <v>555</v>
       </c>
       <c r="AA17">
-        <v>0.99486868336004353</v>
+        <v>0.98434977749377373</v>
       </c>
       <c r="AB17">
-        <v>94.074138399201615</v>
+        <v>286.9207459474826</v>
       </c>
       <c r="AD17" t="s">
         <v>388</v>
@@ -8665,13 +8665,13 @@
         <v>732</v>
       </c>
       <c r="AN17" t="s">
-        <v>582</v>
+        <v>564</v>
       </c>
       <c r="AO17">
-        <v>0.99089509058322967</v>
+        <v>0.99452028244067281</v>
       </c>
       <c r="AP17">
-        <v>166.92333930745593</v>
+        <v>100.46148858766527</v>
       </c>
       <c r="AR17" t="s">
         <v>388</v>
@@ -8701,13 +8701,13 @@
         <v>846</v>
       </c>
       <c r="BB17" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="BC17">
-        <v>0.98664748299407956</v>
+        <v>0.98382004037728943</v>
       </c>
       <c r="BD17">
-        <v>907.27816552213119</v>
+        <v>941.72584140335653</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8772,16 +8772,16 @@
         <v>405</v>
       </c>
       <c r="Y18" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="Z18" t="s">
         <v>556</v>
       </c>
       <c r="AA18">
-        <v>0.99275682304809643</v>
+        <v>0.99326064633097277</v>
       </c>
       <c r="AB18">
-        <v>132.79157745156544</v>
+        <v>123.55481726549976</v>
       </c>
       <c r="AD18" t="s">
         <v>388</v>
@@ -8811,13 +8811,13 @@
         <v>733</v>
       </c>
       <c r="AN18" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="AO18">
-        <v>0.99450138933360577</v>
+        <v>0.98743486034963512</v>
       </c>
       <c r="AP18">
-        <v>100.80786221722684</v>
+        <v>230.36089359002219</v>
       </c>
       <c r="AR18" t="s">
         <v>388</v>
@@ -8847,13 +8847,13 @@
         <v>847</v>
       </c>
       <c r="BB18" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="BC18">
-        <v>0.98382004037728943</v>
+        <v>0.98617370816492766</v>
       </c>
       <c r="BD18">
-        <v>941.72584140335653</v>
+        <v>913.05032219063128</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8918,16 +8918,16 @@
         <v>407</v>
       </c>
       <c r="Y19" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="Z19" t="s">
         <v>557</v>
       </c>
       <c r="AA19">
-        <v>0.98666777524932958</v>
+        <v>0.99457218279364812</v>
       </c>
       <c r="AB19">
-        <v>244.42412042895722</v>
+        <v>99.509982116450402</v>
       </c>
       <c r="AD19" t="s">
         <v>388</v>
@@ -8957,13 +8957,13 @@
         <v>734</v>
       </c>
       <c r="AN19" t="s">
-        <v>560</v>
+        <v>586</v>
       </c>
       <c r="AO19">
-        <v>0.99327255672282233</v>
+        <v>0.9946374817042809</v>
       </c>
       <c r="AP19">
-        <v>123.33646008159123</v>
+        <v>98.312835421515885</v>
       </c>
       <c r="AR19" t="s">
         <v>388</v>
@@ -8993,7 +8993,7 @@
         <v>848</v>
       </c>
       <c r="BB19" t="s">
-        <v>565</v>
+        <v>550</v>
       </c>
       <c r="BC19">
         <v>0.97059082241136851</v>
@@ -9064,16 +9064,16 @@
         <v>409</v>
       </c>
       <c r="Y20" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="Z20" t="s">
         <v>558</v>
       </c>
       <c r="AA20">
-        <v>0.99269116352039599</v>
+        <v>0.99259244228658239</v>
       </c>
       <c r="AB20">
-        <v>133.99533545940744</v>
+        <v>135.80522474598871</v>
       </c>
       <c r="AD20" t="s">
         <v>388</v>
@@ -9103,13 +9103,13 @@
         <v>735</v>
       </c>
       <c r="AN20" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="AO20">
-        <v>0.99390831940949842</v>
+        <v>0.99545219173782828</v>
       </c>
       <c r="AP20">
-        <v>111.68081082586212</v>
+        <v>83.376484806480903</v>
       </c>
       <c r="AR20" t="s">
         <v>388</v>
@@ -9139,7 +9139,7 @@
         <v>849</v>
       </c>
       <c r="BB20" t="s">
-        <v>574</v>
+        <v>584</v>
       </c>
       <c r="BC20">
         <v>0.98631188388799174</v>
@@ -9210,16 +9210,16 @@
         <v>411</v>
       </c>
       <c r="Y21" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="Z21" t="s">
         <v>559</v>
       </c>
       <c r="AA21">
-        <v>0.99006453671041028</v>
+        <v>0.99486868336004353</v>
       </c>
       <c r="AB21">
-        <v>182.15016030914441</v>
+        <v>94.074138399201615</v>
       </c>
       <c r="AD21" t="s">
         <v>388</v>
@@ -9249,13 +9249,13 @@
         <v>736</v>
       </c>
       <c r="AN21" t="s">
-        <v>592</v>
+        <v>575</v>
       </c>
       <c r="AO21">
-        <v>0.99249186107477694</v>
+        <v>0.99145037244742884</v>
       </c>
       <c r="AP21">
-        <v>137.64921362908964</v>
+        <v>156.74317179713734</v>
       </c>
       <c r="AR21" t="s">
         <v>388</v>
@@ -9285,13 +9285,13 @@
         <v>850</v>
       </c>
       <c r="BB21" t="s">
-        <v>551</v>
+        <v>577</v>
       </c>
       <c r="BC21">
-        <v>0.96754380619969493</v>
+        <v>0.98424383368757629</v>
       </c>
       <c r="BD21">
-        <v>1140.0246278003831</v>
+        <v>936.56262623969508</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9356,16 +9356,16 @@
         <v>413</v>
       </c>
       <c r="Y22" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="Z22" t="s">
         <v>560</v>
       </c>
       <c r="AA22">
-        <v>0.9938080410601946</v>
+        <v>0.99449168757100159</v>
       </c>
       <c r="AB22">
-        <v>113.51924722976577</v>
+        <v>100.98572786497003</v>
       </c>
       <c r="AD22" t="s">
         <v>388</v>
@@ -9395,13 +9395,13 @@
         <v>737</v>
       </c>
       <c r="AN22" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AO22">
-        <v>0.99433320017484694</v>
+        <v>0.98960196900926922</v>
       </c>
       <c r="AP22">
-        <v>103.89133012780634</v>
+        <v>190.63056816339852</v>
       </c>
       <c r="AR22" t="s">
         <v>388</v>
@@ -9431,13 +9431,13 @@
         <v>851</v>
       </c>
       <c r="BB22" t="s">
-        <v>592</v>
+        <v>557</v>
       </c>
       <c r="BC22">
-        <v>0.98056622345336075</v>
+        <v>0.9864641946771695</v>
       </c>
       <c r="BD22">
-        <v>981.36817759322128</v>
+        <v>909.51122818315105</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9502,16 +9502,16 @@
         <v>415</v>
       </c>
       <c r="Y23" t="s">
-        <v>355</v>
+        <v>334</v>
       </c>
       <c r="Z23" t="s">
         <v>561</v>
       </c>
       <c r="AA23">
-        <v>0.99382896634585005</v>
+        <v>0.99024242083669489</v>
       </c>
       <c r="AB23">
-        <v>113.13561699274842</v>
+        <v>178.88895132725995</v>
       </c>
       <c r="AD23" t="s">
         <v>388</v>
@@ -9541,13 +9541,13 @@
         <v>738</v>
       </c>
       <c r="AN23" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="AO23">
-        <v>0.98660390748007576</v>
+        <v>0.99043701029499331</v>
       </c>
       <c r="AP23">
-        <v>245.5950295319436</v>
+        <v>175.3214779251216</v>
       </c>
       <c r="AR23" t="s">
         <v>388</v>
@@ -9577,13 +9577,13 @@
         <v>852</v>
       </c>
       <c r="BB23" t="s">
-        <v>556</v>
+        <v>578</v>
       </c>
       <c r="BC23">
-        <v>0.98811227602433394</v>
+        <v>0.9915182189163928</v>
       </c>
       <c r="BD23">
-        <v>889.43210377019864</v>
+        <v>791.61037277293372</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9648,16 +9648,16 @@
         <v>417</v>
       </c>
       <c r="Y24" t="s">
-        <v>375</v>
+        <v>344</v>
       </c>
       <c r="Z24" t="s">
         <v>562</v>
       </c>
       <c r="AA24">
-        <v>0.99140742806735527</v>
+        <v>0.99373222027139962</v>
       </c>
       <c r="AB24">
-        <v>157.53048543182001</v>
+        <v>114.90929502433978</v>
       </c>
       <c r="AD24" t="s">
         <v>388</v>
@@ -9687,13 +9687,13 @@
         <v>739</v>
       </c>
       <c r="AN24" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="AO24">
-        <v>0.99356924052650486</v>
+        <v>0.99286149679037794</v>
       </c>
       <c r="AP24">
-        <v>117.89725701407761</v>
+        <v>130.8725588430718</v>
       </c>
       <c r="AR24" t="s">
         <v>388</v>
@@ -9723,13 +9723,13 @@
         <v>853</v>
       </c>
       <c r="BB24" t="s">
-        <v>557</v>
+        <v>584</v>
       </c>
       <c r="BC24">
-        <v>0.964765711303333</v>
+        <v>0.98016998510849251</v>
       </c>
       <c r="BD24">
-        <v>1173.8710839543928</v>
+        <v>986.19568142819946</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9794,16 +9794,16 @@
         <v>419</v>
       </c>
       <c r="Y25" t="s">
-        <v>382</v>
+        <v>351</v>
       </c>
       <c r="Z25" t="s">
-        <v>555</v>
+        <v>563</v>
       </c>
       <c r="AA25">
-        <v>0.98706515821359619</v>
+        <v>0.99448854992358493</v>
       </c>
       <c r="AB25">
-        <v>237.13876608406935</v>
+        <v>101.04325140094389</v>
       </c>
       <c r="AD25" t="s">
         <v>388</v>
@@ -9833,13 +9833,13 @@
         <v>740</v>
       </c>
       <c r="AN25" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="AO25">
-        <v>0.99689862129048645</v>
+        <v>0.99188199243556163</v>
       </c>
       <c r="AP25">
-        <v>56.858609674414254</v>
+        <v>148.83013868136976</v>
       </c>
       <c r="AR25" t="s">
         <v>388</v>
@@ -9869,13 +9869,13 @@
         <v>854</v>
       </c>
       <c r="BB25" t="s">
-        <v>592</v>
+        <v>551</v>
       </c>
       <c r="BC25">
-        <v>0.98424383368757629</v>
+        <v>0.99333706474272454</v>
       </c>
       <c r="BD25">
-        <v>936.56262623969508</v>
+        <v>676.17429099508138</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9940,16 +9940,16 @@
         <v>421</v>
       </c>
       <c r="Y26" t="s">
-        <v>384</v>
+        <v>361</v>
       </c>
       <c r="Z26" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AA26">
-        <v>0.99504215698918186</v>
+        <v>0.99338948553444661</v>
       </c>
       <c r="AB26">
-        <v>90.893788531666857</v>
+        <v>121.19276520181113</v>
       </c>
       <c r="AD26" t="s">
         <v>388</v>
@@ -9979,13 +9979,13 @@
         <v>741</v>
       </c>
       <c r="AN26" t="s">
-        <v>585</v>
+        <v>551</v>
       </c>
       <c r="AO26">
-        <v>0.99177044540821302</v>
+        <v>0.98666678680685382</v>
       </c>
       <c r="AP26">
-        <v>150.87516751609439</v>
+        <v>244.44224187434608</v>
       </c>
       <c r="AR26" t="s">
         <v>388</v>
@@ -10015,13 +10015,13 @@
         <v>855</v>
       </c>
       <c r="BB26" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="BC26">
-        <v>0.9864641946771695</v>
+        <v>0.98335099885385724</v>
       </c>
       <c r="BD26">
-        <v>909.51122818315105</v>
+        <v>947.44033063050631</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10086,16 +10086,16 @@
         <v>423</v>
       </c>
       <c r="Y27" t="s">
-        <v>318</v>
+        <v>373</v>
       </c>
       <c r="Z27" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AA27">
-        <v>0.99574277994898297</v>
+        <v>0.99418942224649776</v>
       </c>
       <c r="AB27">
-        <v>78.049034268645343</v>
+        <v>106.527258814208</v>
       </c>
       <c r="AD27" t="s">
         <v>388</v>
@@ -10125,13 +10125,13 @@
         <v>742</v>
       </c>
       <c r="AN27" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="AO27">
-        <v>0.99458282020478328</v>
+        <v>0.99461739117688308</v>
       </c>
       <c r="AP27">
-        <v>99.314962912306555</v>
+        <v>98.68116175714421</v>
       </c>
       <c r="AR27" t="s">
         <v>388</v>
@@ -10161,13 +10161,13 @@
         <v>856</v>
       </c>
       <c r="BB27" t="s">
-        <v>582</v>
+        <v>557</v>
       </c>
       <c r="BC27">
-        <v>0.98380308075994261</v>
+        <v>0.99542038465569349</v>
       </c>
       <c r="BD27">
-        <v>941.93246607469882</v>
+        <v>543.95292051865363</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10232,16 +10232,16 @@
         <v>425</v>
       </c>
       <c r="Y28" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="Z28" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AA28">
-        <v>0.98237714666165721</v>
+        <v>0.99472498859344116</v>
       </c>
       <c r="AB28">
-        <v>323.08564453628389</v>
+        <v>96.708542453579653</v>
       </c>
       <c r="AD28" t="s">
         <v>388</v>
@@ -10271,13 +10271,13 @@
         <v>743</v>
       </c>
       <c r="AN28" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="AO28">
-        <v>0.9919109979004006</v>
+        <v>0.98713907316291682</v>
       </c>
       <c r="AP28">
-        <v>148.29837182598865</v>
+        <v>235.78365867985792</v>
       </c>
       <c r="AR28" t="s">
         <v>388</v>
@@ -10307,13 +10307,13 @@
         <v>857</v>
       </c>
       <c r="BB28" t="s">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="BC28">
-        <v>0.98385755699927302</v>
+        <v>0.9889246589664985</v>
       </c>
       <c r="BD28">
-        <v>941.2687638921899</v>
+        <v>879.53457159149264</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10378,16 +10378,16 @@
         <v>427</v>
       </c>
       <c r="Y29" t="s">
-        <v>349</v>
+        <v>319</v>
       </c>
       <c r="Z29" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="AA29">
-        <v>0.98850112471309615</v>
+        <v>0.9917320687619966</v>
       </c>
       <c r="AB29">
-        <v>210.81271359323659</v>
+        <v>151.57873936339664</v>
       </c>
       <c r="AD29" t="s">
         <v>388</v>
@@ -10417,13 +10417,13 @@
         <v>744</v>
       </c>
       <c r="AN29" t="s">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="AO29">
-        <v>0.9944043961659097</v>
+        <v>0.99072423448493052</v>
       </c>
       <c r="AP29">
-        <v>102.58607029165618</v>
+        <v>170.05570110960724</v>
       </c>
       <c r="AR29" t="s">
         <v>388</v>
@@ -10453,13 +10453,13 @@
         <v>858</v>
       </c>
       <c r="BB29" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="BC29">
-        <v>0.99333706474272454</v>
+        <v>0.97462367221641244</v>
       </c>
       <c r="BD29">
-        <v>676.17429099508138</v>
+        <v>1053.7682601633755</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10524,16 +10524,16 @@
         <v>429</v>
       </c>
       <c r="Y30" t="s">
-        <v>358</v>
+        <v>325</v>
       </c>
       <c r="Z30" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AA30">
-        <v>0.99482221718343289</v>
+        <v>0.99396192960580998</v>
       </c>
       <c r="AB30">
-        <v>94.926018303729833</v>
+        <v>110.69795722681697</v>
       </c>
       <c r="AD30" t="s">
         <v>388</v>
@@ -10566,10 +10566,10 @@
         <v>563</v>
       </c>
       <c r="AO30">
-        <v>0.99602637227621282</v>
+        <v>0.99538801767339902</v>
       </c>
       <c r="AP30">
-        <v>72.849841602764897</v>
+        <v>84.553009321017754</v>
       </c>
       <c r="AR30" t="s">
         <v>388</v>
@@ -10599,13 +10599,13 @@
         <v>859</v>
       </c>
       <c r="BB30" t="s">
-        <v>582</v>
+        <v>555</v>
       </c>
       <c r="BC30">
-        <v>0.98335099885385724</v>
+        <v>0.96754380619969493</v>
       </c>
       <c r="BD30">
-        <v>947.44033063050631</v>
+        <v>1140.0246278003831</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10670,16 +10670,16 @@
         <v>431</v>
       </c>
       <c r="Y31" t="s">
-        <v>316</v>
+        <v>370</v>
       </c>
       <c r="Z31" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AA31">
-        <v>0.99335604161179136</v>
+        <v>0.99238783341703851</v>
       </c>
       <c r="AB31">
-        <v>121.80590378382558</v>
+        <v>139.55638735429352</v>
       </c>
       <c r="AD31" t="s">
         <v>388</v>
@@ -10709,13 +10709,13 @@
         <v>746</v>
       </c>
       <c r="AN31" t="s">
-        <v>571</v>
+        <v>585</v>
       </c>
       <c r="AO31">
-        <v>0.99333586753421554</v>
+        <v>0.98686185087293077</v>
       </c>
       <c r="AP31">
-        <v>122.17576187271403</v>
+        <v>240.86606732960294</v>
       </c>
       <c r="AR31" t="s">
         <v>388</v>
@@ -10745,13 +10745,13 @@
         <v>860</v>
       </c>
       <c r="BB31" t="s">
-        <v>553</v>
+        <v>577</v>
       </c>
       <c r="BC31">
-        <v>0.99542038465569349</v>
+        <v>0.98056622345336075</v>
       </c>
       <c r="BD31">
-        <v>543.95292051865363</v>
+        <v>981.36817759322128</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10816,16 +10816,16 @@
         <v>433</v>
       </c>
       <c r="Y32" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="Z32" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AA32">
-        <v>0.99498097012747577</v>
+        <v>0.98974554419194471</v>
       </c>
       <c r="AB32">
-        <v>92.015547662944215</v>
+        <v>187.99835648101393</v>
       </c>
       <c r="AD32" t="s">
         <v>388</v>
@@ -10855,7 +10855,7 @@
         <v>747</v>
       </c>
       <c r="AN32" t="s">
-        <v>560</v>
+        <v>591</v>
       </c>
       <c r="AO32">
         <v>0.99552417511484081</v>
@@ -10891,13 +10891,13 @@
         <v>861</v>
       </c>
       <c r="BB32" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="BC32">
-        <v>0.9915182189163928</v>
+        <v>0.98380308075994261</v>
       </c>
       <c r="BD32">
-        <v>791.61037277293372</v>
+        <v>941.93246607469882</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10962,16 +10962,16 @@
         <v>435</v>
       </c>
       <c r="Y33" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="Z33" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AA33">
-        <v>0.99068678367690288</v>
+        <v>0.99547433853743716</v>
       </c>
       <c r="AB33">
-        <v>170.7422992567804</v>
+        <v>82.970460146984365</v>
       </c>
       <c r="AD33" t="s">
         <v>388</v>
@@ -11001,7 +11001,7 @@
         <v>748</v>
       </c>
       <c r="AN33" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AO33">
         <v>0.98351881644633699</v>
@@ -11037,13 +11037,13 @@
         <v>862</v>
       </c>
       <c r="BB33" t="s">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="BC33">
-        <v>0.98016998510849251</v>
+        <v>0.98811227602433394</v>
       </c>
       <c r="BD33">
-        <v>986.19568142819946</v>
+        <v>889.43210377019864</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11108,16 +11108,16 @@
         <v>437</v>
       </c>
       <c r="Y34" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="Z34" t="s">
-        <v>569</v>
+        <v>556</v>
       </c>
       <c r="AA34">
-        <v>0.99380018286737304</v>
+        <v>0.99432421190931886</v>
       </c>
       <c r="AB34">
-        <v>113.66331409816142</v>
+        <v>104.05611499582191</v>
       </c>
       <c r="AD34" t="s">
         <v>388</v>
@@ -11147,7 +11147,7 @@
         <v>749</v>
       </c>
       <c r="AN34" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
       <c r="AO34">
         <v>0.99485915243795964</v>
@@ -11183,13 +11183,13 @@
         <v>863</v>
       </c>
       <c r="BB34" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="BC34">
-        <v>0.9889246589664985</v>
+        <v>0.964765711303333</v>
       </c>
       <c r="BD34">
-        <v>879.53457159149264</v>
+        <v>1173.8710839543928</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11254,16 +11254,16 @@
         <v>439</v>
       </c>
       <c r="Y35" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="Z35" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AA35">
-        <v>0.99045178849779958</v>
+        <v>0.99439207214359926</v>
       </c>
       <c r="AB35">
-        <v>175.0505442070075</v>
+        <v>102.81201070067981</v>
       </c>
       <c r="AD35" t="s">
         <v>388</v>
@@ -11293,7 +11293,7 @@
         <v>750</v>
       </c>
       <c r="AN35" t="s">
-        <v>562</v>
+        <v>590</v>
       </c>
       <c r="AO35">
         <v>0.98978334793138389</v>
@@ -11364,16 +11364,16 @@
         <v>441</v>
       </c>
       <c r="Y36" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="Z36" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="AA36">
-        <v>0.99360342768209686</v>
+        <v>0.99130148530232876</v>
       </c>
       <c r="AB36">
-        <v>117.27049249489188</v>
+        <v>159.47276945730601</v>
       </c>
       <c r="AD36" t="s">
         <v>388</v>
@@ -11403,13 +11403,13 @@
         <v>751</v>
       </c>
       <c r="AN36" t="s">
-        <v>580</v>
+        <v>555</v>
       </c>
       <c r="AO36">
-        <v>0.99296413260223493</v>
+        <v>0.99170932898012365</v>
       </c>
       <c r="AP36">
-        <v>128.99090229235989</v>
+        <v>151.99563536440075</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11474,16 +11474,16 @@
         <v>443</v>
       </c>
       <c r="Y37" t="s">
-        <v>386</v>
+        <v>323</v>
       </c>
       <c r="Z37" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="AA37">
-        <v>0.9941610020412821</v>
+        <v>0.99244124560610847</v>
       </c>
       <c r="AB37">
-        <v>107.04829590982715</v>
+        <v>138.57716388801143</v>
       </c>
       <c r="AD37" t="s">
         <v>388</v>
@@ -11513,13 +11513,13 @@
         <v>752</v>
       </c>
       <c r="AN37" t="s">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="AO37">
-        <v>0.99403594090084912</v>
+        <v>0.99400997521961898</v>
       </c>
       <c r="AP37">
-        <v>109.34108348443232</v>
+        <v>109.8171209736516</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11584,16 +11584,16 @@
         <v>445</v>
       </c>
       <c r="Y38" t="s">
-        <v>324</v>
+        <v>374</v>
       </c>
       <c r="Z38" t="s">
-        <v>572</v>
+        <v>565</v>
       </c>
       <c r="AA38">
-        <v>0.98899223079090937</v>
+        <v>0.98474401913329324</v>
       </c>
       <c r="AB38">
-        <v>201.80910216666135</v>
+        <v>279.69298255629104</v>
       </c>
       <c r="AD38" t="s">
         <v>388</v>
@@ -11623,13 +11623,13 @@
         <v>753</v>
       </c>
       <c r="AN38" t="s">
-        <v>570</v>
+        <v>589</v>
       </c>
       <c r="AO38">
-        <v>0.98943318015939452</v>
+        <v>0.99270356346131094</v>
       </c>
       <c r="AP38">
-        <v>193.72503041110133</v>
+        <v>133.76800320929971</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11694,16 +11694,16 @@
         <v>447</v>
       </c>
       <c r="Y39" t="s">
-        <v>347</v>
+        <v>309</v>
       </c>
       <c r="Z39" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
       <c r="AA39">
-        <v>0.99373922796305081</v>
+        <v>0.99245084214861234</v>
       </c>
       <c r="AB39">
-        <v>114.78082067740091</v>
+        <v>138.40122727544065</v>
       </c>
       <c r="AD39" t="s">
         <v>388</v>
@@ -11733,13 +11733,13 @@
         <v>754</v>
       </c>
       <c r="AN39" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="AO39">
-        <v>0.99037301617060403</v>
+        <v>0.98675990563829141</v>
       </c>
       <c r="AP39">
-        <v>176.49470353892534</v>
+        <v>242.73506329798991</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11804,16 +11804,16 @@
         <v>449</v>
       </c>
       <c r="Y40" t="s">
-        <v>354</v>
+        <v>328</v>
       </c>
       <c r="Z40" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AA40">
-        <v>0.99489337597419902</v>
+        <v>0.99410067440989558</v>
       </c>
       <c r="AB40">
-        <v>93.621440473017302</v>
+        <v>108.15430248524751</v>
       </c>
       <c r="AD40" t="s">
         <v>388</v>
@@ -11843,13 +11843,13 @@
         <v>755</v>
       </c>
       <c r="AN40" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="AO40">
-        <v>0.99215519768283411</v>
+        <v>0.99286153879604566</v>
       </c>
       <c r="AP40">
-        <v>143.82137581470715</v>
+        <v>130.87178873916278</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -11914,16 +11914,16 @@
         <v>451</v>
       </c>
       <c r="Y41" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="Z41" t="s">
-        <v>574</v>
+        <v>552</v>
       </c>
       <c r="AA41">
-        <v>0.98750565217961461</v>
+        <v>0.9875438296240775</v>
       </c>
       <c r="AB41">
-        <v>229.06304337373263</v>
+        <v>228.36312355857854</v>
       </c>
       <c r="AD41" t="s">
         <v>388</v>
@@ -11953,13 +11953,13 @@
         <v>756</v>
       </c>
       <c r="AN41" t="s">
-        <v>587</v>
+        <v>570</v>
       </c>
       <c r="AO41">
-        <v>0.99392053283098158</v>
+        <v>0.98940376322023671</v>
       </c>
       <c r="AP41">
-        <v>111.45689809867115</v>
+        <v>194.264340962326</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12024,16 +12024,16 @@
         <v>453</v>
       </c>
       <c r="Y42" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="Z42" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="AA42">
-        <v>0.99303639237349761</v>
+        <v>0.99433118964233247</v>
       </c>
       <c r="AB42">
-        <v>127.66613981921104</v>
+        <v>103.92818989057204</v>
       </c>
       <c r="AD42" t="s">
         <v>388</v>
@@ -12063,13 +12063,13 @@
         <v>757</v>
       </c>
       <c r="AN42" t="s">
-        <v>550</v>
+        <v>572</v>
       </c>
       <c r="AO42">
-        <v>0.99519706487556603</v>
+        <v>0.98898412609077158</v>
       </c>
       <c r="AP42">
-        <v>88.053810614623103</v>
+        <v>201.95768833585458</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12134,16 +12134,16 @@
         <v>455</v>
       </c>
       <c r="Y43" t="s">
-        <v>317</v>
+        <v>367</v>
       </c>
       <c r="Z43" t="s">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="AA43">
-        <v>0.98974554419194471</v>
+        <v>0.98861342542180985</v>
       </c>
       <c r="AB43">
-        <v>187.99835648101393</v>
+        <v>208.75386726681941</v>
       </c>
       <c r="AD43" t="s">
         <v>388</v>
@@ -12173,13 +12173,13 @@
         <v>758</v>
       </c>
       <c r="AN43" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="AO43">
-        <v>0.99116017126466804</v>
+        <v>0.99427706626581025</v>
       </c>
       <c r="AP43">
-        <v>162.0635268144182</v>
+        <v>104.92045179347788</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12244,16 +12244,16 @@
         <v>457</v>
       </c>
       <c r="Y44" t="s">
-        <v>336</v>
+        <v>371</v>
       </c>
       <c r="Z44" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="AA44">
-        <v>0.99547433853743716</v>
+        <v>0.99214710198915512</v>
       </c>
       <c r="AB44">
-        <v>82.970460146984365</v>
+        <v>143.9697968654902</v>
       </c>
       <c r="AD44" t="s">
         <v>388</v>
@@ -12283,13 +12283,13 @@
         <v>759</v>
       </c>
       <c r="AN44" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="AO44">
-        <v>0.99287761065972435</v>
+        <v>0.99121477309476114</v>
       </c>
       <c r="AP44">
-        <v>130.57713790505289</v>
+        <v>161.062493262712</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12354,16 +12354,16 @@
         <v>459</v>
       </c>
       <c r="Y45" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="Z45" t="s">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="AA45">
-        <v>0.99432421190931886</v>
+        <v>0.99329032731129618</v>
       </c>
       <c r="AB45">
-        <v>104.05611499582191</v>
+        <v>123.01066595957037</v>
       </c>
       <c r="AD45" t="s">
         <v>388</v>
@@ -12393,13 +12393,13 @@
         <v>760</v>
       </c>
       <c r="AN45" t="s">
-        <v>557</v>
+        <v>571</v>
       </c>
       <c r="AO45">
-        <v>0.9909825022671549</v>
+        <v>0.99329038799154346</v>
       </c>
       <c r="AP45">
-        <v>165.32079176882775</v>
+        <v>123.0095534883708</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12464,16 +12464,16 @@
         <v>461</v>
       </c>
       <c r="Y46" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="Z46" t="s">
         <v>577</v>
       </c>
       <c r="AA46">
-        <v>0.99439207214359926</v>
+        <v>0.99270917988914098</v>
       </c>
       <c r="AB46">
-        <v>102.81201070067981</v>
+        <v>133.66503536574953</v>
       </c>
       <c r="AD46" t="s">
         <v>388</v>
@@ -12503,13 +12503,13 @@
         <v>761</v>
       </c>
       <c r="AN46" t="s">
-        <v>577</v>
+        <v>587</v>
       </c>
       <c r="AO46">
-        <v>0.99409301598387334</v>
+        <v>0.99201459591478169</v>
       </c>
       <c r="AP46">
-        <v>108.29470696232133</v>
+        <v>146.39907489566812</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12574,16 +12574,16 @@
         <v>463</v>
       </c>
       <c r="Y47" t="s">
-        <v>385</v>
+        <v>362</v>
       </c>
       <c r="Z47" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="AA47">
-        <v>0.99130148530232876</v>
+        <v>0.99529481894214911</v>
       </c>
       <c r="AB47">
-        <v>159.47276945730601</v>
+        <v>86.26165272726621</v>
       </c>
       <c r="AD47" t="s">
         <v>388</v>
@@ -12613,13 +12613,13 @@
         <v>762</v>
       </c>
       <c r="AN47" t="s">
-        <v>588</v>
+        <v>556</v>
       </c>
       <c r="AO47">
-        <v>0.99145037244742884</v>
+        <v>0.99418817704352525</v>
       </c>
       <c r="AP47">
-        <v>156.74317179713734</v>
+        <v>106.5500875353703</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12684,16 +12684,16 @@
         <v>465</v>
       </c>
       <c r="Y48" t="s">
-        <v>315</v>
+        <v>369</v>
       </c>
       <c r="Z48" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AA48">
-        <v>0.99449168757100159</v>
+        <v>0.99452055660680094</v>
       </c>
       <c r="AB48">
-        <v>100.98572786497003</v>
+        <v>100.45646220864869</v>
       </c>
       <c r="AD48" t="s">
         <v>388</v>
@@ -12723,13 +12723,13 @@
         <v>763</v>
       </c>
       <c r="AN48" t="s">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="AO48">
-        <v>0.98960196900926922</v>
+        <v>0.98264007513427243</v>
       </c>
       <c r="AP48">
-        <v>190.63056816339852</v>
+        <v>318.26528920500613</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -12794,16 +12794,16 @@
         <v>467</v>
       </c>
       <c r="Y49" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="Z49" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AA49">
-        <v>0.99024242083669489</v>
+        <v>0.99275682304809643</v>
       </c>
       <c r="AB49">
-        <v>178.88895132725995</v>
+        <v>132.79157745156544</v>
       </c>
       <c r="AD49" t="s">
         <v>388</v>
@@ -12833,13 +12833,13 @@
         <v>764</v>
       </c>
       <c r="AN49" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="AO49">
-        <v>0.99043701029499331</v>
+        <v>0.98973070091819682</v>
       </c>
       <c r="AP49">
-        <v>175.3214779251216</v>
+        <v>188.27048316639193</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -12904,16 +12904,16 @@
         <v>469</v>
       </c>
       <c r="Y50" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="Z50" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AA50">
-        <v>0.99373222027139962</v>
+        <v>0.98666777524932958</v>
       </c>
       <c r="AB50">
-        <v>114.90929502433978</v>
+        <v>244.42412042895722</v>
       </c>
       <c r="AD50" t="s">
         <v>388</v>
@@ -12943,13 +12943,13 @@
         <v>765</v>
       </c>
       <c r="AN50" t="s">
-        <v>568</v>
+        <v>584</v>
       </c>
       <c r="AO50">
-        <v>0.99429570648020904</v>
+        <v>0.99017733442899913</v>
       </c>
       <c r="AP50">
-        <v>104.57871452950124</v>
+        <v>180.08220213501625</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -13014,16 +13014,16 @@
         <v>471</v>
       </c>
       <c r="Y51" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="Z51" t="s">
-        <v>581</v>
+        <v>551</v>
       </c>
       <c r="AA51">
-        <v>0.99448854992358493</v>
+        <v>0.99269116352039599</v>
       </c>
       <c r="AB51">
-        <v>101.04325140094389</v>
+        <v>133.99533545940744</v>
       </c>
       <c r="AD51" t="s">
         <v>388</v>
@@ -13053,13 +13053,13 @@
         <v>766</v>
       </c>
       <c r="AN51" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="AO51">
-        <v>0.99452028244067281</v>
+        <v>0.99392053283098158</v>
       </c>
       <c r="AP51">
-        <v>100.46148858766527</v>
+        <v>111.45689809867115</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -13124,16 +13124,16 @@
         <v>473</v>
       </c>
       <c r="Y52" t="s">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="Z52" t="s">
         <v>582</v>
       </c>
       <c r="AA52">
-        <v>0.99338948553444661</v>
+        <v>0.99006453671041028</v>
       </c>
       <c r="AB52">
-        <v>121.19276520181113</v>
+        <v>182.15016030914441</v>
       </c>
       <c r="AD52" t="s">
         <v>388</v>
@@ -13163,13 +13163,13 @@
         <v>767</v>
       </c>
       <c r="AN52" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AO52">
-        <v>0.98743486034963512</v>
+        <v>0.99519706487556603</v>
       </c>
       <c r="AP52">
-        <v>230.36089359002219</v>
+        <v>88.053810614623103</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13234,16 +13234,16 @@
         <v>475</v>
       </c>
       <c r="Y53" t="s">
-        <v>373</v>
+        <v>324</v>
       </c>
       <c r="Z53" t="s">
-        <v>583</v>
+        <v>568</v>
       </c>
       <c r="AA53">
-        <v>0.99418942224649776</v>
+        <v>0.98899223079090937</v>
       </c>
       <c r="AB53">
-        <v>106.527258814208</v>
+        <v>201.80910216666135</v>
       </c>
       <c r="AD53" t="s">
         <v>388</v>
@@ -13273,13 +13273,13 @@
         <v>768</v>
       </c>
       <c r="AN53" t="s">
-        <v>588</v>
+        <v>560</v>
       </c>
       <c r="AO53">
-        <v>0.99427706626581025</v>
+        <v>0.99116017126466804</v>
       </c>
       <c r="AP53">
-        <v>104.92045179347788</v>
+        <v>162.0635268144182</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -13344,16 +13344,16 @@
         <v>477</v>
       </c>
       <c r="Y54" t="s">
-        <v>383</v>
+        <v>347</v>
       </c>
       <c r="Z54" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="AA54">
-        <v>0.99472498859344116</v>
+        <v>0.99373922796305081</v>
       </c>
       <c r="AB54">
-        <v>96.708542453579653</v>
+        <v>114.78082067740091</v>
       </c>
       <c r="AD54" t="s">
         <v>388</v>
@@ -13383,13 +13383,13 @@
         <v>769</v>
       </c>
       <c r="AN54" t="s">
-        <v>579</v>
+        <v>550</v>
       </c>
       <c r="AO54">
-        <v>0.99121477309476114</v>
+        <v>0.99287761065972435</v>
       </c>
       <c r="AP54">
-        <v>161.062493262712</v>
+        <v>130.57713790505289</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -13454,16 +13454,16 @@
         <v>479</v>
       </c>
       <c r="Y55" t="s">
-        <v>319</v>
+        <v>354</v>
       </c>
       <c r="Z55" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="AA55">
-        <v>0.9917320687619966</v>
+        <v>0.99489337597419902</v>
       </c>
       <c r="AB55">
-        <v>151.57873936339664</v>
+        <v>93.621440473017302</v>
       </c>
       <c r="AD55" t="s">
         <v>388</v>
@@ -13493,13 +13493,13 @@
         <v>770</v>
       </c>
       <c r="AN55" t="s">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="AO55">
-        <v>0.99329038799154346</v>
+        <v>0.9909825022671549</v>
       </c>
       <c r="AP55">
-        <v>123.0095534883708</v>
+        <v>165.32079176882775</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -13564,16 +13564,16 @@
         <v>481</v>
       </c>
       <c r="Y56" t="s">
-        <v>325</v>
+        <v>365</v>
       </c>
       <c r="Z56" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="AA56">
-        <v>0.99396192960580998</v>
+        <v>0.98750565217961461</v>
       </c>
       <c r="AB56">
-        <v>110.69795722681697</v>
+        <v>229.06304337373263</v>
       </c>
       <c r="AD56" t="s">
         <v>388</v>
@@ -13603,13 +13603,13 @@
         <v>771</v>
       </c>
       <c r="AN56" t="s">
-        <v>591</v>
+        <v>572</v>
       </c>
       <c r="AO56">
-        <v>0.99201459591478169</v>
+        <v>0.99409301598387334</v>
       </c>
       <c r="AP56">
-        <v>146.39907489566812</v>
+        <v>108.29470696232133</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -13674,16 +13674,16 @@
         <v>483</v>
       </c>
       <c r="Y57" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="Z57" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AA57">
-        <v>0.99238783341703851</v>
+        <v>0.99303639237349761</v>
       </c>
       <c r="AB57">
-        <v>139.55638735429352</v>
+        <v>127.66613981921104</v>
       </c>
       <c r="AD57" t="s">
         <v>388</v>
@@ -13713,13 +13713,13 @@
         <v>772</v>
       </c>
       <c r="AN57" t="s">
-        <v>552</v>
+        <v>562</v>
       </c>
       <c r="AO57">
-        <v>0.99418817704352525</v>
+        <v>0.99296413260223493</v>
       </c>
       <c r="AP57">
-        <v>106.5500875353703</v>
+        <v>128.99090229235989</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -13784,16 +13784,16 @@
         <v>485</v>
       </c>
       <c r="Y58" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="Z58" t="s">
-        <v>551</v>
+        <v>580</v>
       </c>
       <c r="AA58">
-        <v>0.99244124560610847</v>
+        <v>0.99287457171029725</v>
       </c>
       <c r="AB58">
-        <v>138.57716388801143</v>
+        <v>130.63285197788394</v>
       </c>
       <c r="AD58" t="s">
         <v>388</v>
@@ -13823,13 +13823,13 @@
         <v>773</v>
       </c>
       <c r="AN58" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="AO58">
-        <v>0.98264007513427243</v>
+        <v>0.99403594090084912</v>
       </c>
       <c r="AP58">
-        <v>318.26528920500613</v>
+        <v>109.34108348443232</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -13894,16 +13894,16 @@
         <v>487</v>
       </c>
       <c r="Y59" t="s">
-        <v>374</v>
+        <v>346</v>
       </c>
       <c r="Z59" t="s">
-        <v>583</v>
+        <v>550</v>
       </c>
       <c r="AA59">
-        <v>0.98474401913329324</v>
+        <v>0.99268599671594204</v>
       </c>
       <c r="AB59">
-        <v>279.69298255629104</v>
+        <v>134.09006020772978</v>
       </c>
       <c r="AD59" t="s">
         <v>388</v>
@@ -13933,13 +13933,13 @@
         <v>774</v>
       </c>
       <c r="AN59" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="AO59">
-        <v>0.98973070091819682</v>
+        <v>0.98943318015939452</v>
       </c>
       <c r="AP59">
-        <v>188.27048316639193</v>
+        <v>193.72503041110133</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -14004,16 +14004,16 @@
         <v>489</v>
       </c>
       <c r="Y60" t="s">
-        <v>309</v>
+        <v>366</v>
       </c>
       <c r="Z60" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="AA60">
-        <v>0.99245084214861234</v>
+        <v>0.98961378001546085</v>
       </c>
       <c r="AB60">
-        <v>138.40122727544065</v>
+        <v>190.41403304988424</v>
       </c>
       <c r="AD60" t="s">
         <v>388</v>
@@ -14043,13 +14043,13 @@
         <v>775</v>
       </c>
       <c r="AN60" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AO60">
-        <v>0.99017733442899913</v>
+        <v>0.99037301617060403</v>
       </c>
       <c r="AP60">
-        <v>180.08220213501625</v>
+        <v>176.49470353892534</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -14114,16 +14114,16 @@
         <v>491</v>
       </c>
       <c r="Y61" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Z61" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="AA61">
-        <v>0.99410067440989558</v>
+        <v>0.99402818260314618</v>
       </c>
       <c r="AB61">
-        <v>108.15430248524751</v>
+        <v>109.48331894231943</v>
       </c>
       <c r="AD61" t="s">
         <v>388</v>
@@ -14153,13 +14153,13 @@
         <v>776</v>
       </c>
       <c r="AN61" t="s">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="AO61">
-        <v>0.99460493914808601</v>
+        <v>0.99215519768283411</v>
       </c>
       <c r="AP61">
-        <v>98.909448951756843</v>
+        <v>143.82137581470715</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -14224,16 +14224,16 @@
         <v>493</v>
       </c>
       <c r="Y62" t="s">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="Z62" t="s">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="AA62">
-        <v>0.9875438296240775</v>
+        <v>0.99351839907880191</v>
       </c>
       <c r="AB62">
-        <v>228.36312355857854</v>
+        <v>118.82935022196459</v>
       </c>
       <c r="AD62" t="s">
         <v>388</v>
@@ -14263,13 +14263,13 @@
         <v>777</v>
       </c>
       <c r="AN62" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="AO62">
-        <v>0.99226255824077458</v>
+        <v>0.99689862129048645</v>
       </c>
       <c r="AP62">
-        <v>141.853098919133</v>
+        <v>56.858609674414254</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -14334,16 +14334,16 @@
         <v>495</v>
       </c>
       <c r="Y63" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
       <c r="Z63" t="s">
-        <v>582</v>
+        <v>587</v>
       </c>
       <c r="AA63">
-        <v>0.99433118964233247</v>
+        <v>0.99546714226270061</v>
       </c>
       <c r="AB63">
-        <v>103.92818989057204</v>
+        <v>83.102391850488004</v>
       </c>
       <c r="AD63" t="s">
         <v>388</v>
@@ -14373,13 +14373,13 @@
         <v>778</v>
       </c>
       <c r="AN63" t="s">
-        <v>551</v>
+        <v>567</v>
       </c>
       <c r="AO63">
-        <v>0.99170932898012365</v>
+        <v>0.99177044540821302</v>
       </c>
       <c r="AP63">
-        <v>151.99563536440075</v>
+        <v>150.87516751609439</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -14444,16 +14444,16 @@
         <v>497</v>
       </c>
       <c r="Y64" t="s">
-        <v>367</v>
+        <v>343</v>
       </c>
       <c r="Z64" t="s">
-        <v>589</v>
+        <v>562</v>
       </c>
       <c r="AA64">
-        <v>0.98861342542180985</v>
+        <v>0.99030786115942782</v>
       </c>
       <c r="AB64">
-        <v>208.75386726681941</v>
+        <v>177.68921207715613</v>
       </c>
       <c r="AD64" t="s">
         <v>388</v>
@@ -14483,13 +14483,13 @@
         <v>779</v>
       </c>
       <c r="AN64" t="s">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="AO64">
-        <v>0.99400997521961898</v>
+        <v>0.99458282020478328</v>
       </c>
       <c r="AP64">
-        <v>109.8171209736516</v>
+        <v>99.314962912306555</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -14554,16 +14554,16 @@
         <v>499</v>
       </c>
       <c r="Y65" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="Z65" t="s">
-        <v>554</v>
+        <v>576</v>
       </c>
       <c r="AA65">
-        <v>0.99214710198915512</v>
+        <v>0.98889208513122484</v>
       </c>
       <c r="AB65">
-        <v>143.9697968654902</v>
+        <v>203.64510592754459</v>
       </c>
       <c r="AD65" t="s">
         <v>388</v>
@@ -14593,13 +14593,13 @@
         <v>780</v>
       </c>
       <c r="AN65" t="s">
-        <v>569</v>
+        <v>577</v>
       </c>
       <c r="AO65">
-        <v>0.99270356346131094</v>
+        <v>0.9919109979004006</v>
       </c>
       <c r="AP65">
-        <v>133.76800320929971</v>
+        <v>148.29837182598865</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -14664,16 +14664,16 @@
         <v>501</v>
       </c>
       <c r="Y66" t="s">
-        <v>312</v>
+        <v>378</v>
       </c>
       <c r="Z66" t="s">
-        <v>549</v>
+        <v>585</v>
       </c>
       <c r="AA66">
-        <v>0.99473753513404162</v>
+        <v>0.98915595886276608</v>
       </c>
       <c r="AB66">
-        <v>96.478522542569891</v>
+        <v>198.80742084928778</v>
       </c>
       <c r="AD66" t="s">
         <v>388</v>
@@ -14703,13 +14703,13 @@
         <v>781</v>
       </c>
       <c r="AN66" t="s">
-        <v>574</v>
+        <v>557</v>
       </c>
       <c r="AO66">
-        <v>0.98675990563829141</v>
+        <v>0.9944043961659097</v>
       </c>
       <c r="AP66">
-        <v>242.73506329798991</v>
+        <v>102.58607029165618</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -14774,16 +14774,16 @@
         <v>503</v>
       </c>
       <c r="Y67" t="s">
-        <v>320</v>
+        <v>379</v>
       </c>
       <c r="Z67" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="AA67">
-        <v>0.99462963762315071</v>
+        <v>0.99620638875319056</v>
       </c>
       <c r="AB67">
-        <v>98.456643575569544</v>
+        <v>69.549539524839389</v>
       </c>
       <c r="AD67" t="s">
         <v>388</v>
@@ -14813,13 +14813,13 @@
         <v>782</v>
       </c>
       <c r="AN67" t="s">
-        <v>555</v>
+        <v>593</v>
       </c>
       <c r="AO67">
-        <v>0.99286153879604566</v>
+        <v>0.99602637227621282</v>
       </c>
       <c r="AP67">
-        <v>130.87178873916278</v>
+        <v>72.849841602764897</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -14884,16 +14884,16 @@
         <v>505</v>
       </c>
       <c r="Y68" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="Z68" t="s">
-        <v>588</v>
+        <v>570</v>
       </c>
       <c r="AA68">
-        <v>0.99184091582017686</v>
+        <v>0.99335604161179136</v>
       </c>
       <c r="AB68">
-        <v>149.58320996342505</v>
+        <v>121.80590378382558</v>
       </c>
       <c r="AD68" t="s">
         <v>388</v>
@@ -14923,13 +14923,13 @@
         <v>783</v>
       </c>
       <c r="AN68" t="s">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="AO68">
-        <v>0.99286149679037794</v>
+        <v>0.99333586753421554</v>
       </c>
       <c r="AP68">
-        <v>130.8725588430718</v>
+        <v>122.17576187271403</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -14994,16 +14994,16 @@
         <v>507</v>
       </c>
       <c r="Y69" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="Z69" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="AA69">
-        <v>0.9956123485295133</v>
+        <v>0.99498097012747577</v>
       </c>
       <c r="AB69">
-        <v>80.440276958922396</v>
+        <v>92.015547662944215</v>
       </c>
       <c r="AD69" t="s">
         <v>388</v>
@@ -15033,13 +15033,13 @@
         <v>784</v>
       </c>
       <c r="AN69" t="s">
-        <v>579</v>
+        <v>553</v>
       </c>
       <c r="AO69">
-        <v>0.99188199243556163</v>
+        <v>0.99460493914808601</v>
       </c>
       <c r="AP69">
-        <v>148.83013868136976</v>
+        <v>98.909448951756843</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -15104,16 +15104,16 @@
         <v>509</v>
       </c>
       <c r="Y70" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="Z70" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="AA70">
-        <v>0.99290883235651795</v>
+        <v>0.99068678367690288</v>
       </c>
       <c r="AB70">
-        <v>130.00474013050507</v>
+        <v>170.7422992567804</v>
       </c>
       <c r="AD70" t="s">
         <v>388</v>
@@ -15146,10 +15146,10 @@
         <v>558</v>
       </c>
       <c r="AO70">
-        <v>0.98666678680685382</v>
+        <v>0.99226255824077458</v>
       </c>
       <c r="AP70">
-        <v>244.44224187434608</v>
+        <v>141.853098919133</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -15214,16 +15214,16 @@
         <v>511</v>
       </c>
       <c r="Y71" t="s">
-        <v>356</v>
+        <v>342</v>
       </c>
       <c r="Z71" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="AA71">
-        <v>0.98893783962199822</v>
+        <v>0.99380018286737304</v>
       </c>
       <c r="AB71">
-        <v>202.8062735966999</v>
+        <v>113.66331409816142</v>
       </c>
       <c r="AD71" t="s">
         <v>388</v>
@@ -15253,13 +15253,13 @@
         <v>786</v>
       </c>
       <c r="AN71" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="AO71">
-        <v>0.99461739117688308</v>
+        <v>0.99327255672282233</v>
       </c>
       <c r="AP71">
-        <v>98.68116175714421</v>
+        <v>123.33646008159123</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -15324,16 +15324,16 @@
         <v>513</v>
       </c>
       <c r="Y72" t="s">
-        <v>331</v>
+        <v>363</v>
       </c>
       <c r="Z72" t="s">
-        <v>556</v>
+        <v>578</v>
       </c>
       <c r="AA72">
-        <v>0.99287457171029725</v>
+        <v>0.99045178849779958</v>
       </c>
       <c r="AB72">
-        <v>130.63285197788394</v>
+        <v>175.0505442070075</v>
       </c>
       <c r="AD72" t="s">
         <v>388</v>
@@ -15366,10 +15366,10 @@
         <v>589</v>
       </c>
       <c r="AO72">
-        <v>0.98713907316291682</v>
+        <v>0.99390831940949842</v>
       </c>
       <c r="AP72">
-        <v>235.78365867985792</v>
+        <v>111.68081082586212</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -15434,16 +15434,16 @@
         <v>515</v>
       </c>
       <c r="Y73" t="s">
-        <v>346</v>
+        <v>376</v>
       </c>
       <c r="Z73" t="s">
-        <v>565</v>
+        <v>590</v>
       </c>
       <c r="AA73">
-        <v>0.99268599671594204</v>
+        <v>0.99360342768209686</v>
       </c>
       <c r="AB73">
-        <v>134.09006020772978</v>
+        <v>117.27049249489188</v>
       </c>
       <c r="AD73" t="s">
         <v>388</v>
@@ -15473,13 +15473,13 @@
         <v>788</v>
       </c>
       <c r="AN73" t="s">
-        <v>590</v>
+        <v>577</v>
       </c>
       <c r="AO73">
-        <v>0.9946374817042809</v>
+        <v>0.99249186107477694</v>
       </c>
       <c r="AP73">
-        <v>98.312835421515885</v>
+        <v>137.64921362908964</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -15544,16 +15544,16 @@
         <v>517</v>
       </c>
       <c r="Y74" t="s">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="Z74" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="AA74">
-        <v>0.98961378001546085</v>
+        <v>0.9941610020412821</v>
       </c>
       <c r="AB74">
-        <v>190.41403304988424</v>
+        <v>107.04829590982715</v>
       </c>
       <c r="AD74" t="s">
         <v>388</v>
@@ -15583,13 +15583,13 @@
         <v>789</v>
       </c>
       <c r="AN74" t="s">
-        <v>584</v>
+        <v>592</v>
       </c>
       <c r="AO74">
-        <v>0.99545219173782828</v>
+        <v>0.99433320017484694</v>
       </c>
       <c r="AP74">
-        <v>83.376484806480903</v>
+        <v>103.89133012780634</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -15654,16 +15654,16 @@
         <v>519</v>
       </c>
       <c r="Y75" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Z75" t="s">
-        <v>587</v>
+        <v>553</v>
       </c>
       <c r="AA75">
-        <v>0.99395804884905048</v>
+        <v>0.99473753513404162</v>
       </c>
       <c r="AB75">
-        <v>110.76910443407451</v>
+        <v>96.478522542569891</v>
       </c>
       <c r="AD75" t="s">
         <v>388</v>
@@ -15693,13 +15693,13 @@
         <v>790</v>
       </c>
       <c r="AN75" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AO75">
-        <v>0.98940376322023671</v>
+        <v>0.98660390748007576</v>
       </c>
       <c r="AP75">
-        <v>194.264340962326</v>
+        <v>245.5950295319436</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -15764,16 +15764,16 @@
         <v>521</v>
       </c>
       <c r="Y76" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="Z76" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="AA76">
-        <v>0.98876972660449969</v>
+        <v>0.99462963762315071</v>
       </c>
       <c r="AB76">
-        <v>205.88834558417196</v>
+        <v>98.456643575569544</v>
       </c>
       <c r="AD76" t="s">
         <v>388</v>
@@ -15803,13 +15803,13 @@
         <v>791</v>
       </c>
       <c r="AN76" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="AO76">
-        <v>0.98898412609077158</v>
+        <v>0.99356924052650486</v>
       </c>
       <c r="AP76">
-        <v>201.95768833585458</v>
+        <v>117.89725701407761</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -15874,16 +15874,16 @@
         <v>523</v>
       </c>
       <c r="Y77" t="s">
-        <v>353</v>
+        <v>327</v>
       </c>
       <c r="Z77" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AA77">
-        <v>0.99543619104776615</v>
+        <v>0.99184091582017686</v>
       </c>
       <c r="AB77">
-        <v>83.669830790954578</v>
+        <v>149.58320996342505</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -15948,16 +15948,16 @@
         <v>525</v>
       </c>
       <c r="Y78" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="Z78" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="AA78">
-        <v>0.99402818260314618</v>
+        <v>0.9956123485295133</v>
       </c>
       <c r="AB78">
-        <v>109.48331894231943</v>
+        <v>80.440276958922396</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -16022,16 +16022,16 @@
         <v>527</v>
       </c>
       <c r="Y79" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="Z79" t="s">
-        <v>591</v>
+        <v>571</v>
       </c>
       <c r="AA79">
-        <v>0.99351839907880191</v>
+        <v>0.99290883235651795</v>
       </c>
       <c r="AB79">
-        <v>118.82935022196459</v>
+        <v>130.00474013050507</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -16096,16 +16096,16 @@
         <v>529</v>
       </c>
       <c r="Y80" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="Z80" t="s">
-        <v>591</v>
+        <v>572</v>
       </c>
       <c r="AA80">
-        <v>0.99546714226270061</v>
+        <v>0.98893783962199822</v>
       </c>
       <c r="AB80">
-        <v>83.102391850488004</v>
+        <v>202.8062735966999</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -16170,16 +16170,16 @@
         <v>531</v>
       </c>
       <c r="Y81" t="s">
-        <v>343</v>
+        <v>310</v>
       </c>
       <c r="Z81" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="AA81">
-        <v>0.99030786115942782</v>
+        <v>0.99395804884905048</v>
       </c>
       <c r="AB81">
-        <v>177.68921207715613</v>
+        <v>110.76910443407451</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -16244,16 +16244,16 @@
         <v>533</v>
       </c>
       <c r="Y82" t="s">
-        <v>368</v>
+        <v>314</v>
       </c>
       <c r="Z82" t="s">
-        <v>589</v>
+        <v>560</v>
       </c>
       <c r="AA82">
-        <v>0.98889208513122484</v>
+        <v>0.98876972660449969</v>
       </c>
       <c r="AB82">
-        <v>203.64510592754459</v>
+        <v>205.88834558417196</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -16318,16 +16318,16 @@
         <v>535</v>
       </c>
       <c r="Y83" t="s">
-        <v>378</v>
+        <v>353</v>
       </c>
       <c r="Z83" t="s">
-        <v>575</v>
+        <v>583</v>
       </c>
       <c r="AA83">
-        <v>0.98915595886276608</v>
+        <v>0.99543619104776615</v>
       </c>
       <c r="AB83">
-        <v>198.80742084928778</v>
+        <v>83.669830790954578</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -16392,16 +16392,16 @@
         <v>537</v>
       </c>
       <c r="Y84" t="s">
-        <v>379</v>
+        <v>321</v>
       </c>
       <c r="Z84" t="s">
-        <v>559</v>
+        <v>591</v>
       </c>
       <c r="AA84">
-        <v>0.99620638875319056</v>
+        <v>0.9938080410601946</v>
       </c>
       <c r="AB84">
-        <v>69.549539524839389</v>
+        <v>113.51924722976577</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -16466,16 +16466,16 @@
         <v>539</v>
       </c>
       <c r="Y85" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="Z85" t="s">
-        <v>579</v>
+        <v>592</v>
       </c>
       <c r="AA85">
-        <v>0.99329032731129618</v>
+        <v>0.99382896634585005</v>
       </c>
       <c r="AB85">
-        <v>123.01066595957037</v>
+        <v>113.13561699274842</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -16540,16 +16540,16 @@
         <v>541</v>
       </c>
       <c r="Y86" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="Z86" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="AA86">
-        <v>0.99270917988914098</v>
+        <v>0.99140742806735527</v>
       </c>
       <c r="AB86">
-        <v>133.66503536574953</v>
+        <v>157.53048543182001</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -16614,16 +16614,16 @@
         <v>543</v>
       </c>
       <c r="Y87" t="s">
-        <v>362</v>
+        <v>382</v>
       </c>
       <c r="Z87" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="AA87">
-        <v>0.99529481894214911</v>
+        <v>0.98706515821359619</v>
       </c>
       <c r="AB87">
-        <v>86.26165272726621</v>
+        <v>237.13876608406935</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -16688,16 +16688,16 @@
         <v>545</v>
       </c>
       <c r="Y88" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="Z88" t="s">
         <v>593</v>
       </c>
       <c r="AA88">
-        <v>0.99452055660680094</v>
+        <v>0.99504215698918186</v>
       </c>
       <c r="AB88">
-        <v>100.45646220864869</v>
+        <v>90.893788531666857</v>
       </c>
     </row>
   </sheetData>
@@ -16706,7 +16706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BD82708-3328-4EF9-AD92-877C91579A28}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1EDDBA-3FEC-4FFA-B64B-0D1F0218426C}">
   <dimension ref="B9:Z76"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -16818,7 +16818,7 @@
         <v>864</v>
       </c>
       <c r="K11" t="s">
-        <v>756</v>
+        <v>766</v>
       </c>
       <c r="L11">
         <v>33.83147659537768</v>
@@ -16851,7 +16851,7 @@
         <v>996</v>
       </c>
       <c r="X11" t="s">
-        <v>842</v>
+        <v>858</v>
       </c>
       <c r="Y11">
         <v>30.066749999999999</v>
@@ -16886,7 +16886,7 @@
         <v>866</v>
       </c>
       <c r="K12" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="L12">
         <v>27.804556055352069</v>
@@ -16919,7 +16919,7 @@
         <v>998</v>
       </c>
       <c r="X12" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="Y12">
         <v>17.4435</v>
@@ -16954,7 +16954,7 @@
         <v>868</v>
       </c>
       <c r="K13" t="s">
-        <v>757</v>
+        <v>767</v>
       </c>
       <c r="L13">
         <v>24.791203937070382</v>
@@ -16987,7 +16987,7 @@
         <v>1000</v>
       </c>
       <c r="X13" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="Y13">
         <v>17.109749999999998</v>
@@ -17022,7 +17022,7 @@
         <v>870</v>
       </c>
       <c r="K14" t="s">
-        <v>758</v>
+        <v>768</v>
       </c>
       <c r="L14">
         <v>34.2342595317402</v>
@@ -17055,7 +17055,7 @@
         <v>1002</v>
       </c>
       <c r="X14" t="s">
-        <v>852</v>
+        <v>862</v>
       </c>
       <c r="Y14">
         <v>21.135750000000002</v>
@@ -17090,7 +17090,7 @@
         <v>872</v>
       </c>
       <c r="K15" t="s">
-        <v>790</v>
+        <v>756</v>
       </c>
       <c r="L15">
         <v>24.913123886642243</v>
@@ -17158,7 +17158,7 @@
         <v>874</v>
       </c>
       <c r="K16" t="s">
-        <v>783</v>
+        <v>739</v>
       </c>
       <c r="L16">
         <v>58.034317529098374</v>
@@ -17191,7 +17191,7 @@
         <v>1006</v>
       </c>
       <c r="X16" t="s">
-        <v>853</v>
+        <v>863</v>
       </c>
       <c r="Y16">
         <v>6.6974999999999998</v>
@@ -17226,7 +17226,7 @@
         <v>876</v>
       </c>
       <c r="K17" t="s">
-        <v>740</v>
+        <v>777</v>
       </c>
       <c r="L17">
         <v>7.6837750207160314</v>
@@ -17259,7 +17259,7 @@
         <v>1008</v>
       </c>
       <c r="X17" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="Y17">
         <v>10.605</v>
@@ -17294,7 +17294,7 @@
         <v>878</v>
       </c>
       <c r="K18" t="s">
-        <v>741</v>
+        <v>778</v>
       </c>
       <c r="L18">
         <v>16.250223804119301</v>
@@ -17327,7 +17327,7 @@
         <v>1010</v>
       </c>
       <c r="X18" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="Y18">
         <v>22.638000000000002</v>
@@ -17362,7 +17362,7 @@
         <v>880</v>
       </c>
       <c r="K19" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="L19">
         <v>36.889818336478399</v>
@@ -17395,7 +17395,7 @@
         <v>1012</v>
       </c>
       <c r="X19" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="Y19">
         <v>39.393000000000001</v>
@@ -17430,7 +17430,7 @@
         <v>882</v>
       </c>
       <c r="K20" t="s">
-        <v>734</v>
+        <v>786</v>
       </c>
       <c r="L20">
         <v>28.992008200964371</v>
@@ -17463,7 +17463,7 @@
         <v>1014</v>
       </c>
       <c r="X20" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="Y20">
         <v>26.508749999999999</v>
@@ -17531,7 +17531,7 @@
         <v>1016</v>
       </c>
       <c r="X21" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="Y21">
         <v>32.472000000000001</v>
@@ -17599,7 +17599,7 @@
         <v>1018</v>
       </c>
       <c r="X22" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="Y22">
         <v>51.573749999999997</v>
@@ -17634,7 +17634,7 @@
         <v>888</v>
       </c>
       <c r="K23" t="s">
-        <v>778</v>
+        <v>751</v>
       </c>
       <c r="L23">
         <v>82.640164540088762</v>
@@ -17667,7 +17667,7 @@
         <v>1020</v>
       </c>
       <c r="X23" t="s">
-        <v>857</v>
+        <v>840</v>
       </c>
       <c r="Y23">
         <v>10.83</v>
@@ -17702,7 +17702,7 @@
         <v>890</v>
       </c>
       <c r="K24" t="s">
-        <v>726</v>
+        <v>744</v>
       </c>
       <c r="L24">
         <v>31.759670242178537</v>
@@ -17770,7 +17770,7 @@
         <v>892</v>
       </c>
       <c r="K25" t="s">
-        <v>779</v>
+        <v>752</v>
       </c>
       <c r="L25">
         <v>11.496369756329127</v>
@@ -17803,7 +17803,7 @@
         <v>1024</v>
       </c>
       <c r="X25" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="Y25">
         <v>19.481999999999999</v>
@@ -17838,7 +17838,7 @@
         <v>894</v>
       </c>
       <c r="K26" t="s">
-        <v>765</v>
+        <v>731</v>
       </c>
       <c r="L26">
         <v>10.908640183890601</v>
@@ -17871,7 +17871,7 @@
         <v>1026</v>
       </c>
       <c r="X26" t="s">
-        <v>856</v>
+        <v>861</v>
       </c>
       <c r="Y26">
         <v>24.132000000000001</v>
@@ -17906,7 +17906,7 @@
         <v>896</v>
       </c>
       <c r="K27" t="s">
-        <v>742</v>
+        <v>779</v>
       </c>
       <c r="L27">
         <v>27.909273114027371</v>
@@ -17939,7 +17939,7 @@
         <v>1028</v>
       </c>
       <c r="X27" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="Y27">
         <v>9.37575</v>
@@ -17974,7 +17974,7 @@
         <v>898</v>
       </c>
       <c r="K28" t="s">
-        <v>768</v>
+        <v>758</v>
       </c>
       <c r="L28">
         <v>35.507746640042782</v>
@@ -18007,7 +18007,7 @@
         <v>1030</v>
       </c>
       <c r="X28" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="Y28">
         <v>10.142250000000001</v>
@@ -18042,7 +18042,7 @@
         <v>900</v>
       </c>
       <c r="K29" t="s">
-        <v>762</v>
+        <v>736</v>
       </c>
       <c r="L29">
         <v>26.872192854848723</v>
@@ -18075,7 +18075,7 @@
         <v>1032</v>
       </c>
       <c r="X29" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="Y29">
         <v>14.205</v>
@@ -18110,7 +18110,7 @@
         <v>902</v>
       </c>
       <c r="K30" t="s">
-        <v>788</v>
+        <v>734</v>
       </c>
       <c r="L30">
         <v>31.889876701248639</v>
@@ -18143,7 +18143,7 @@
         <v>1034</v>
       </c>
       <c r="X30" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="Y30">
         <v>28.951499999999999</v>
@@ -18178,7 +18178,7 @@
         <v>904</v>
       </c>
       <c r="K31" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="L31">
         <v>18.489507752816973</v>
@@ -18246,7 +18246,7 @@
         <v>906</v>
       </c>
       <c r="K32" t="s">
-        <v>769</v>
+        <v>759</v>
       </c>
       <c r="L32">
         <v>55.67336781800514</v>
@@ -18279,7 +18279,7 @@
         <v>1038</v>
       </c>
       <c r="X32" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="Y32">
         <v>29.553000000000001</v>
@@ -18314,7 +18314,7 @@
         <v>908</v>
       </c>
       <c r="K33" t="s">
-        <v>784</v>
+        <v>740</v>
       </c>
       <c r="L33">
         <v>40.30121650051354</v>
@@ -18347,7 +18347,7 @@
         <v>1040</v>
       </c>
       <c r="X33" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="Y33">
         <v>18.38775</v>
@@ -18382,7 +18382,7 @@
         <v>910</v>
       </c>
       <c r="K34" t="s">
-        <v>770</v>
+        <v>760</v>
       </c>
       <c r="L34">
         <v>2.2018767330895068</v>
@@ -18415,7 +18415,7 @@
         <v>1042</v>
       </c>
       <c r="X34" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="Y34">
         <v>31.49325</v>
@@ -18450,7 +18450,7 @@
         <v>912</v>
       </c>
       <c r="K35" t="s">
-        <v>771</v>
+        <v>761</v>
       </c>
       <c r="L35">
         <v>0.51870876860917992</v>
@@ -18485,7 +18485,7 @@
         <v>914</v>
       </c>
       <c r="K36" t="s">
-        <v>772</v>
+        <v>762</v>
       </c>
       <c r="L36">
         <v>33.956844037805517</v>
@@ -18520,7 +18520,7 @@
         <v>916</v>
       </c>
       <c r="K37" t="s">
-        <v>735</v>
+        <v>787</v>
       </c>
       <c r="L37">
         <v>15.006880463771946</v>
@@ -18555,7 +18555,7 @@
         <v>918</v>
       </c>
       <c r="K38" t="s">
-        <v>780</v>
+        <v>753</v>
       </c>
       <c r="L38">
         <v>23.284229642731745</v>
@@ -18590,7 +18590,7 @@
         <v>920</v>
       </c>
       <c r="K39" t="s">
-        <v>751</v>
+        <v>772</v>
       </c>
       <c r="L39">
         <v>15.321352411640023</v>
@@ -18625,7 +18625,7 @@
         <v>922</v>
       </c>
       <c r="K40" t="s">
-        <v>763</v>
+        <v>737</v>
       </c>
       <c r="L40">
         <v>23.785304147591408</v>
@@ -18660,7 +18660,7 @@
         <v>924</v>
       </c>
       <c r="K41" t="s">
-        <v>759</v>
+        <v>769</v>
       </c>
       <c r="L41">
         <v>52.745166437734376</v>
@@ -18695,7 +18695,7 @@
         <v>926</v>
       </c>
       <c r="K42" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="L42">
         <v>33.61899681334765</v>
@@ -18730,7 +18730,7 @@
         <v>928</v>
       </c>
       <c r="K43" t="s">
-        <v>764</v>
+        <v>738</v>
       </c>
       <c r="L43">
         <v>11.593697444968496</v>
@@ -18765,7 +18765,7 @@
         <v>930</v>
       </c>
       <c r="K44" t="s">
-        <v>760</v>
+        <v>770</v>
       </c>
       <c r="L44">
         <v>74.024525145569001</v>
@@ -18800,7 +18800,7 @@
         <v>932</v>
       </c>
       <c r="K45" t="s">
-        <v>785</v>
+        <v>741</v>
       </c>
       <c r="L45">
         <v>16.258644020270342</v>
@@ -18835,7 +18835,7 @@
         <v>934</v>
       </c>
       <c r="K46" t="s">
-        <v>752</v>
+        <v>773</v>
       </c>
       <c r="L46">
         <v>26.813047414923648</v>
@@ -18870,7 +18870,7 @@
         <v>936</v>
       </c>
       <c r="K47" t="s">
-        <v>727</v>
+        <v>745</v>
       </c>
       <c r="L47">
         <v>16.546770964036483</v>
@@ -18905,7 +18905,7 @@
         <v>938</v>
       </c>
       <c r="K48" t="s">
-        <v>736</v>
+        <v>788</v>
       </c>
       <c r="L48">
         <v>11.997781844082855</v>
@@ -18940,7 +18940,7 @@
         <v>940</v>
       </c>
       <c r="K49" t="s">
-        <v>743</v>
+        <v>780</v>
       </c>
       <c r="L49">
         <v>46.243621179927722</v>
@@ -18975,7 +18975,7 @@
         <v>942</v>
       </c>
       <c r="K50" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="L50">
         <v>4.2125637096126836</v>
@@ -19010,7 +19010,7 @@
         <v>944</v>
       </c>
       <c r="K51" t="s">
-        <v>737</v>
+        <v>789</v>
       </c>
       <c r="L51">
         <v>38.145385819354424</v>
@@ -19045,7 +19045,7 @@
         <v>946</v>
       </c>
       <c r="K52" t="s">
-        <v>791</v>
+        <v>757</v>
       </c>
       <c r="L52">
         <v>25.369500443235932</v>
@@ -19080,7 +19080,7 @@
         <v>948</v>
       </c>
       <c r="K53" t="s">
-        <v>761</v>
+        <v>771</v>
       </c>
       <c r="L53">
         <v>39.105697164199093</v>
@@ -19150,7 +19150,7 @@
         <v>952</v>
       </c>
       <c r="K55" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
       <c r="L55">
         <v>35.376685860779752</v>
@@ -19185,7 +19185,7 @@
         <v>954</v>
       </c>
       <c r="K56" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="L56">
         <v>8.4489492903276986</v>
@@ -19220,7 +19220,7 @@
         <v>956</v>
       </c>
       <c r="K57" t="s">
-        <v>766</v>
+        <v>732</v>
       </c>
       <c r="L57">
         <v>33.038237032166357</v>
@@ -19255,7 +19255,7 @@
         <v>958</v>
       </c>
       <c r="K58" t="s">
-        <v>753</v>
+        <v>774</v>
       </c>
       <c r="L58">
         <v>22.937581762872757</v>
@@ -19290,7 +19290,7 @@
         <v>960</v>
       </c>
       <c r="K59" t="s">
-        <v>786</v>
+        <v>742</v>
       </c>
       <c r="L59">
         <v>37.854069118280655</v>
@@ -19325,7 +19325,7 @@
         <v>962</v>
       </c>
       <c r="K60" t="s">
-        <v>744</v>
+        <v>781</v>
       </c>
       <c r="L60">
         <v>19.031552923919683</v>
@@ -19360,7 +19360,7 @@
         <v>964</v>
       </c>
       <c r="K61" t="s">
-        <v>781</v>
+        <v>754</v>
       </c>
       <c r="L61">
         <v>22.881530103416733</v>
@@ -19395,7 +19395,7 @@
         <v>966</v>
       </c>
       <c r="K62" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="L62">
         <v>66.366737714251741</v>
@@ -19430,7 +19430,7 @@
         <v>968</v>
       </c>
       <c r="K63" t="s">
-        <v>787</v>
+        <v>743</v>
       </c>
       <c r="L63">
         <v>37.179299980729631</v>
@@ -19465,7 +19465,7 @@
         <v>970</v>
       </c>
       <c r="K64" t="s">
-        <v>754</v>
+        <v>775</v>
       </c>
       <c r="L64">
         <v>75.340015936683557</v>
@@ -19500,7 +19500,7 @@
         <v>972</v>
       </c>
       <c r="K65" t="s">
-        <v>738</v>
+        <v>790</v>
       </c>
       <c r="L65">
         <v>1.671977286085228</v>
@@ -19535,7 +19535,7 @@
         <v>974</v>
       </c>
       <c r="K66" t="s">
-        <v>755</v>
+        <v>776</v>
       </c>
       <c r="L66">
         <v>21.281833534179093</v>
@@ -19570,7 +19570,7 @@
         <v>976</v>
       </c>
       <c r="K67" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="L67">
         <v>20.373488892344575</v>
@@ -19640,7 +19640,7 @@
         <v>980</v>
       </c>
       <c r="K69" t="s">
-        <v>728</v>
+        <v>746</v>
       </c>
       <c r="L69">
         <v>11.876635800692616</v>
@@ -19675,7 +19675,7 @@
         <v>982</v>
       </c>
       <c r="K70" t="s">
-        <v>739</v>
+        <v>791</v>
       </c>
       <c r="L70">
         <v>31.752829963824876</v>
@@ -19710,7 +19710,7 @@
         <v>984</v>
       </c>
       <c r="K71" t="s">
-        <v>767</v>
+        <v>733</v>
       </c>
       <c r="L71">
         <v>26.523136640432838</v>
@@ -19745,7 +19745,7 @@
         <v>986</v>
       </c>
       <c r="K72" t="s">
-        <v>782</v>
+        <v>755</v>
       </c>
       <c r="L72">
         <v>33.765756839519163</v>
@@ -19780,7 +19780,7 @@
         <v>988</v>
       </c>
       <c r="K73" t="s">
-        <v>789</v>
+        <v>735</v>
       </c>
       <c r="L73">
         <v>17.233040840286481</v>
@@ -19815,7 +19815,7 @@
         <v>990</v>
       </c>
       <c r="K74" t="s">
-        <v>745</v>
+        <v>782</v>
       </c>
       <c r="L74">
         <v>10.225876074214261</v>
@@ -19850,7 +19850,7 @@
         <v>992</v>
       </c>
       <c r="K75" t="s">
-        <v>746</v>
+        <v>783</v>
       </c>
       <c r="L75">
         <v>19.944768886736487</v>
@@ -19885,7 +19885,7 @@
         <v>994</v>
       </c>
       <c r="K76" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="L76">
         <v>22.01601541072662</v>
@@ -19900,7 +19900,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F43BE7D3-0BED-48D1-9884-144E7C624D3A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59278195-21B3-4545-BB53-0CFF916599F1}">
   <dimension ref="B9:Y151"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -24720,7 +24720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{991465E0-AFA7-44A0-A935-D5D86A35E443}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EC5E5-C3B3-4C3C-8871-0D6C3EA72DF5}">
   <dimension ref="B9:T79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>

--- a/VerveStacks_IND_grids_kan60/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
+++ b/VerveStacks_IND_grids_kan60/SubRES_Tmpl/SubRES_New_RE_and_Conventional.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan60\SubRES_Tmpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B299EE-78C9-4CE1-AA1C-AA6254221D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEFFBA4B-D64A-415E-AA0C-37463AB9401D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misc" sheetId="7" r:id="rId1"/>
@@ -1233,18 +1233,402 @@
     <t>pre</t>
   </si>
   <si>
+    <t>distr_solelc_spv_IND_015</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>NRGI</t>
+  </si>
+  <si>
+    <t>daynite</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_066</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 66</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_011</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_017</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_062</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 62</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_016</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 16</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_039</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_046</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 46</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_057</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 57</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_069</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 69</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_008</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_018</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 18</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_033</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_034</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_055</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_068</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 68</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_078</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 78</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_013</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_047</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 47</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_067</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 67</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_074</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 74</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_076</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 76</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_024</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 24</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_040</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 40</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_042</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_072</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 72</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_003</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_005</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_014</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_031</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_056</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_064</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_073</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 73</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_007</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_026</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 26</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_036</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_043</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_053</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 53</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_065</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_075</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 75</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_025</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 25</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_044</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_054</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_061</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 61</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_004</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_012</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_019</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_021</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 21</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_027</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_048</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_023</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 23</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_038</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_058</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_001</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_020</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 20</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_051</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_052</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 52</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_059</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 59</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_063</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 63</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_009</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 9</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_028</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_032</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 32</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_049</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 49</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_077</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 77</t>
+  </si>
+  <si>
     <t>distr_solelc_spv_IND_010</t>
   </si>
   <si>
     <t>connecting solar to buses in cluster 10</t>
   </si>
   <si>
-    <t>NRGI</t>
-  </si>
-  <si>
-    <t>daynite</t>
-  </si>
-  <si>
     <t>distr_solelc_spv_IND_037</t>
   </si>
   <si>
@@ -1263,280 +1647,22 @@
     <t>connecting solar to buses in cluster 50</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_003</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_005</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_014</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_031</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_056</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_064</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_073</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 73</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_007</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_026</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 26</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_036</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_043</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_053</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 53</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_065</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_075</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 75</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_011</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_017</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_062</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_009</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 9</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_028</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_032</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 32</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_049</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 49</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_077</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 77</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_015</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_066</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 66</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_001</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_020</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_051</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_052</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 52</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_059</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_063</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 63</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_025</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 25</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_044</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_054</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_061</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 61</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_024</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 24</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_040</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 40</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_042</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 42</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_072</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 72</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_016</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 16</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_039</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_046</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 46</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_057</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_069</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 69</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_023</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 23</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_038</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_058</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 58</t>
+    <t>distr_solelc_spv_IND_002</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_006</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 6</t>
+  </si>
+  <si>
+    <t>distr_solelc_spv_IND_045</t>
+  </si>
+  <si>
+    <t>connecting solar to buses in cluster 45</t>
   </si>
   <si>
     <t>distr_solelc_spv_IND_022</t>
@@ -1581,273 +1707,147 @@
     <t>connecting solar to buses in cluster 71</t>
   </si>
   <si>
-    <t>distr_solelc_spv_IND_008</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_018</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 18</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_033</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 33</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_034</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_055</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_068</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 68</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_078</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 78</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_004</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_012</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_019</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_021</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 21</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_027</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_048</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_002</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_006</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 6</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_045</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 45</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_013</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_047</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 47</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_067</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 67</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_074</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 74</t>
-  </si>
-  <si>
-    <t>distr_solelc_spv_IND_076</t>
-  </si>
-  <si>
-    <t>connecting solar to buses in cluster 76</t>
-  </si>
-  <si>
     <t>comm-in</t>
   </si>
   <si>
     <t>ncap_cost~USD21_alt</t>
   </si>
   <si>
+    <t>e_Solapur_IND</t>
+  </si>
+  <si>
+    <t>e_Tezpur_IND</t>
+  </si>
+  <si>
+    <t>e_Indore_IND</t>
+  </si>
+  <si>
+    <t>e_Raipur_IND</t>
+  </si>
+  <si>
+    <t>e_Talcher_IND</t>
+  </si>
+  <si>
+    <t>e_Dharmapuri_IND</t>
+  </si>
+  <si>
+    <t>e_Singrauliya_IND</t>
+  </si>
+  <si>
+    <t>e_Nakhtarana_IND</t>
+  </si>
+  <si>
+    <t>e_Karaikandi_IND</t>
+  </si>
+  <si>
+    <t>e_Wardha_IND</t>
+  </si>
+  <si>
+    <t>e_Kurnool_IND</t>
+  </si>
+  <si>
+    <t>e_Jaipur_IND</t>
+  </si>
+  <si>
+    <t>e_Narasaraopet_IND</t>
+  </si>
+  <si>
+    <t>e_Bongaigaon_IND</t>
+  </si>
+  <si>
+    <t>e_Bhagalpur_IND</t>
+  </si>
+  <si>
+    <t>e_Cuddapah_IND</t>
+  </si>
+  <si>
+    <t>e_Ajmer_IND</t>
+  </si>
+  <si>
+    <t>e_Sasaram_IND</t>
+  </si>
+  <si>
+    <t>e_BokaroSteelCity_IND</t>
+  </si>
+  <si>
+    <t>e_Angul_IND</t>
+  </si>
+  <si>
+    <t>e_Kakinada_IND</t>
+  </si>
+  <si>
+    <t>e_Bihar_IND</t>
+  </si>
+  <si>
+    <t>e_Gwalior_IND</t>
+  </si>
+  <si>
+    <t>e_Etawa_IND</t>
+  </si>
+  <si>
+    <t>e_Bhopal_IND</t>
+  </si>
+  <si>
+    <t>e_Chennai_IND</t>
+  </si>
+  <si>
+    <t>e_Madurai_IND</t>
+  </si>
+  <si>
+    <t>e_Satna_IND</t>
+  </si>
+  <si>
+    <t>e_Vadodara_IND</t>
+  </si>
+  <si>
+    <t>e_Moga_IND</t>
+  </si>
+  <si>
+    <t>e_Sikandarabad_IND</t>
+  </si>
+  <si>
+    <t>e_Bhatpara_IND</t>
+  </si>
+  <si>
+    <t>e_Asansol_IND</t>
+  </si>
+  <si>
+    <t>e_BarmhanKalan_IND</t>
+  </si>
+  <si>
+    <t>e_Jammu_IND</t>
+  </si>
+  <si>
+    <t>e_Aurangabad_IND</t>
+  </si>
+  <si>
+    <t>e_Jabalpur_IND</t>
+  </si>
+  <si>
+    <t>e_Korba_IND</t>
+  </si>
+  <si>
+    <t>e_ArniKaKhera_IND</t>
+  </si>
+  <si>
+    <t>e_Raichur_IND</t>
+  </si>
+  <si>
+    <t>e_Meerut_IND</t>
+  </si>
+  <si>
+    <t>e_Mainpuri_IND</t>
+  </si>
+  <si>
+    <t>e_Phalodi_IND</t>
+  </si>
+  <si>
     <t>e_Gaya_IND</t>
   </si>
   <si>
-    <t>e_Raichur_IND</t>
-  </si>
-  <si>
-    <t>e_Kakinada_IND</t>
-  </si>
-  <si>
-    <t>e_Mainpuri_IND</t>
-  </si>
-  <si>
-    <t>e_Gwalior_IND</t>
-  </si>
-  <si>
-    <t>e_Etawa_IND</t>
-  </si>
-  <si>
-    <t>e_Solapur_IND</t>
-  </si>
-  <si>
-    <t>e_Bhopal_IND</t>
-  </si>
-  <si>
-    <t>e_Chennai_IND</t>
-  </si>
-  <si>
-    <t>e_Madurai_IND</t>
-  </si>
-  <si>
-    <t>e_Sasaram_IND</t>
-  </si>
-  <si>
-    <t>e_Satna_IND</t>
-  </si>
-  <si>
-    <t>e_Vadodara_IND</t>
-  </si>
-  <si>
-    <t>e_Moga_IND</t>
-  </si>
-  <si>
-    <t>e_Sikandarabad_IND</t>
-  </si>
-  <si>
-    <t>e_Bhatpara_IND</t>
-  </si>
-  <si>
-    <t>e_Tezpur_IND</t>
-  </si>
-  <si>
-    <t>e_Asansol_IND</t>
-  </si>
-  <si>
-    <t>e_Indore_IND</t>
-  </si>
-  <si>
-    <t>e_Raipur_IND</t>
-  </si>
-  <si>
-    <t>e_Talcher_IND</t>
-  </si>
-  <si>
-    <t>e_Wardha_IND</t>
-  </si>
-  <si>
-    <t>e_Korba_IND</t>
-  </si>
-  <si>
-    <t>e_ArniKaKhera_IND</t>
-  </si>
-  <si>
-    <t>e_Bhagalpur_IND</t>
-  </si>
-  <si>
-    <t>e_Meerut_IND</t>
-  </si>
-  <si>
-    <t>e_Aurangabad_IND</t>
-  </si>
-  <si>
-    <t>e_Phalodi_IND</t>
-  </si>
-  <si>
-    <t>e_BarmhanKalan_IND</t>
-  </si>
-  <si>
-    <t>e_Narasaraopet_IND</t>
-  </si>
-  <si>
-    <t>e_Jammu_IND</t>
-  </si>
-  <si>
-    <t>e_Angul_IND</t>
-  </si>
-  <si>
-    <t>e_Dharmapuri_IND</t>
-  </si>
-  <si>
-    <t>e_Bihar_IND</t>
-  </si>
-  <si>
-    <t>e_Singrauliya_IND</t>
-  </si>
-  <si>
-    <t>e_Nakhtarana_IND</t>
-  </si>
-  <si>
-    <t>e_Karaikandi_IND</t>
-  </si>
-  <si>
-    <t>e_Jabalpur_IND</t>
-  </si>
-  <si>
     <t>e_Jharsugra_IND</t>
   </si>
   <si>
-    <t>e_Kurnool_IND</t>
-  </si>
-  <si>
-    <t>e_Jaipur_IND</t>
-  </si>
-  <si>
-    <t>e_Bongaigaon_IND</t>
-  </si>
-  <si>
-    <t>e_Cuddapah_IND</t>
-  </si>
-  <si>
-    <t>e_Ajmer_IND</t>
-  </si>
-  <si>
-    <t>e_BokaroSteelCity_IND</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_IND_009</t>
   </si>
   <si>
@@ -1878,6 +1878,24 @@
     <t>connecting wind onshore to buses in cluster 66</t>
   </si>
   <si>
+    <t>distr_wonelc_won_IND_014</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 14</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_037</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 37</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_059</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 59</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_IND_016</t>
   </si>
   <si>
@@ -1896,6 +1914,216 @@
     <t>connecting wind onshore to buses in cluster 61</t>
   </si>
   <si>
+    <t>distr_wonelc_won_IND_007</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 7</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_008</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 8</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_017</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_039</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 39</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_050</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 50</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_064</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 64</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_065</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 65</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_005</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 5</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_042</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 42</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_029</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 29</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_036</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 36</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_048</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 48</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_054</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 54</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_056</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 56</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_019</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 19</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_030</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 30</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_033</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 33</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_001</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_003</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 3</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_004</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_031</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 31</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_034</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 34</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_043</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 43</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_011</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 11</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_012</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 12</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_044</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 44</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_058</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 58</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_010</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 10</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_027</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 27</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_038</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 38</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_041</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 41</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_055</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 55</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_060</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 60</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_002</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_057</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 57</t>
+  </si>
+  <si>
     <t>distr_wonelc_won_IND_020</t>
   </si>
   <si>
@@ -1908,22 +2136,34 @@
     <t>connecting wind onshore to buses in cluster 63</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_019</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 19</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_030</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 30</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_033</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 33</t>
+    <t>distr_wonelc_won_IND_013</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 13</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_015</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 15</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_028</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 28</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_051</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 51</t>
+  </si>
+  <si>
+    <t>distr_wonelc_won_IND_062</t>
+  </si>
+  <si>
+    <t>connecting wind onshore to buses in cluster 62</t>
   </si>
   <si>
     <t>distr_wonelc_won_IND_006</t>
@@ -1956,90 +2196,6 @@
     <t>connecting wind onshore to buses in cluster 53</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_014</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 14</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_037</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 37</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_059</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 59</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_011</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 11</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_012</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 12</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_044</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 44</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_058</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 58</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_013</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 13</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_015</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 15</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_028</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 28</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_051</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 51</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_062</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 62</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_005</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 5</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_042</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 42</t>
-  </si>
-  <si>
     <t>distr_wonelc_won_IND_018</t>
   </si>
   <si>
@@ -2088,162 +2244,6 @@
     <t>connecting wind onshore to buses in cluster 52</t>
   </si>
   <si>
-    <t>distr_wonelc_won_IND_001</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_003</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 3</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_004</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_031</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 31</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_034</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 34</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_043</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 43</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_029</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 29</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_036</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 36</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_048</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 48</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_054</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 54</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_056</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 56</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_007</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 7</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_008</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 8</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_017</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_039</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 39</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_050</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 50</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_064</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 64</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_065</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 65</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_002</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_057</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 57</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_010</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 10</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_027</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 27</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_038</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 38</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_041</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 41</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_055</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 55</t>
-  </si>
-  <si>
-    <t>distr_wonelc_won_IND_060</t>
-  </si>
-  <si>
-    <t>connecting wind onshore to buses in cluster 60</t>
-  </si>
-  <si>
     <t>elc_won_IND_009</t>
   </si>
   <si>
@@ -2259,6 +2259,15 @@
     <t>elc_won_IND_066</t>
   </si>
   <si>
+    <t>elc_won_IND_014</t>
+  </si>
+  <si>
+    <t>elc_won_IND_037</t>
+  </si>
+  <si>
+    <t>elc_won_IND_059</t>
+  </si>
+  <si>
     <t>elc_won_IND_016</t>
   </si>
   <si>
@@ -2268,19 +2277,130 @@
     <t>elc_won_IND_061</t>
   </si>
   <si>
+    <t>elc_won_IND_007</t>
+  </si>
+  <si>
+    <t>elc_won_IND_008</t>
+  </si>
+  <si>
+    <t>elc_won_IND_017</t>
+  </si>
+  <si>
+    <t>elc_won_IND_039</t>
+  </si>
+  <si>
+    <t>elc_won_IND_050</t>
+  </si>
+  <si>
+    <t>elc_won_IND_064</t>
+  </si>
+  <si>
+    <t>elc_won_IND_065</t>
+  </si>
+  <si>
+    <t>elc_won_IND_005</t>
+  </si>
+  <si>
+    <t>elc_won_IND_042</t>
+  </si>
+  <si>
+    <t>elc_won_IND_029</t>
+  </si>
+  <si>
+    <t>elc_won_IND_036</t>
+  </si>
+  <si>
+    <t>elc_won_IND_048</t>
+  </si>
+  <si>
+    <t>elc_won_IND_054</t>
+  </si>
+  <si>
+    <t>elc_won_IND_056</t>
+  </si>
+  <si>
+    <t>elc_won_IND_019</t>
+  </si>
+  <si>
+    <t>elc_won_IND_030</t>
+  </si>
+  <si>
+    <t>elc_won_IND_033</t>
+  </si>
+  <si>
+    <t>elc_won_IND_001</t>
+  </si>
+  <si>
+    <t>elc_won_IND_003</t>
+  </si>
+  <si>
+    <t>elc_won_IND_004</t>
+  </si>
+  <si>
+    <t>elc_won_IND_031</t>
+  </si>
+  <si>
+    <t>elc_won_IND_034</t>
+  </si>
+  <si>
+    <t>elc_won_IND_043</t>
+  </si>
+  <si>
+    <t>elc_won_IND_011</t>
+  </si>
+  <si>
+    <t>elc_won_IND_012</t>
+  </si>
+  <si>
+    <t>elc_won_IND_044</t>
+  </si>
+  <si>
+    <t>elc_won_IND_058</t>
+  </si>
+  <si>
+    <t>elc_won_IND_010</t>
+  </si>
+  <si>
+    <t>elc_won_IND_027</t>
+  </si>
+  <si>
+    <t>elc_won_IND_038</t>
+  </si>
+  <si>
+    <t>elc_won_IND_041</t>
+  </si>
+  <si>
+    <t>elc_won_IND_055</t>
+  </si>
+  <si>
+    <t>elc_won_IND_060</t>
+  </si>
+  <si>
+    <t>elc_won_IND_002</t>
+  </si>
+  <si>
+    <t>elc_won_IND_057</t>
+  </si>
+  <si>
     <t>elc_won_IND_020</t>
   </si>
   <si>
     <t>elc_won_IND_063</t>
   </si>
   <si>
-    <t>elc_won_IND_019</t>
-  </si>
-  <si>
-    <t>elc_won_IND_030</t>
-  </si>
-  <si>
-    <t>elc_won_IND_033</t>
+    <t>elc_won_IND_013</t>
+  </si>
+  <si>
+    <t>elc_won_IND_015</t>
+  </si>
+  <si>
+    <t>elc_won_IND_028</t>
+  </si>
+  <si>
+    <t>elc_won_IND_051</t>
+  </si>
+  <si>
+    <t>elc_won_IND_062</t>
   </si>
   <si>
     <t>elc_won_IND_006</t>
@@ -2298,48 +2418,6 @@
     <t>elc_won_IND_053</t>
   </si>
   <si>
-    <t>elc_won_IND_014</t>
-  </si>
-  <si>
-    <t>elc_won_IND_037</t>
-  </si>
-  <si>
-    <t>elc_won_IND_059</t>
-  </si>
-  <si>
-    <t>elc_won_IND_011</t>
-  </si>
-  <si>
-    <t>elc_won_IND_012</t>
-  </si>
-  <si>
-    <t>elc_won_IND_044</t>
-  </si>
-  <si>
-    <t>elc_won_IND_058</t>
-  </si>
-  <si>
-    <t>elc_won_IND_013</t>
-  </si>
-  <si>
-    <t>elc_won_IND_015</t>
-  </si>
-  <si>
-    <t>elc_won_IND_028</t>
-  </si>
-  <si>
-    <t>elc_won_IND_051</t>
-  </si>
-  <si>
-    <t>elc_won_IND_062</t>
-  </si>
-  <si>
-    <t>elc_won_IND_005</t>
-  </si>
-  <si>
-    <t>elc_won_IND_042</t>
-  </si>
-  <si>
     <t>elc_won_IND_018</t>
   </si>
   <si>
@@ -2364,82 +2442,10 @@
     <t>elc_won_IND_052</t>
   </si>
   <si>
-    <t>elc_won_IND_001</t>
-  </si>
-  <si>
-    <t>elc_won_IND_003</t>
-  </si>
-  <si>
-    <t>elc_won_IND_004</t>
-  </si>
-  <si>
-    <t>elc_won_IND_031</t>
-  </si>
-  <si>
-    <t>elc_won_IND_034</t>
-  </si>
-  <si>
-    <t>elc_won_IND_043</t>
-  </si>
-  <si>
-    <t>elc_won_IND_029</t>
-  </si>
-  <si>
-    <t>elc_won_IND_036</t>
-  </si>
-  <si>
-    <t>elc_won_IND_048</t>
-  </si>
-  <si>
-    <t>elc_won_IND_054</t>
-  </si>
-  <si>
-    <t>elc_won_IND_056</t>
-  </si>
-  <si>
-    <t>elc_won_IND_007</t>
-  </si>
-  <si>
-    <t>elc_won_IND_008</t>
-  </si>
-  <si>
-    <t>elc_won_IND_017</t>
-  </si>
-  <si>
-    <t>elc_won_IND_039</t>
-  </si>
-  <si>
-    <t>elc_won_IND_050</t>
-  </si>
-  <si>
-    <t>elc_won_IND_064</t>
-  </si>
-  <si>
-    <t>elc_won_IND_065</t>
-  </si>
-  <si>
-    <t>elc_won_IND_002</t>
-  </si>
-  <si>
-    <t>elc_won_IND_057</t>
-  </si>
-  <si>
-    <t>elc_won_IND_010</t>
-  </si>
-  <si>
-    <t>elc_won_IND_027</t>
-  </si>
-  <si>
-    <t>elc_won_IND_038</t>
-  </si>
-  <si>
-    <t>elc_won_IND_041</t>
-  </si>
-  <si>
-    <t>elc_won_IND_055</t>
-  </si>
-  <si>
-    <t>elc_won_IND_060</t>
+    <t>distr_wofelc_wof_IND_007</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 7</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IND_013</t>
@@ -2448,6 +2454,30 @@
     <t>connecting wind offshore to buses in cluster 13</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_IND_017</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 17</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_022</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 22</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_002</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 2</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_009</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 9</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_IND_014</t>
   </si>
   <si>
@@ -2484,12 +2514,6 @@
     <t>connecting wind offshore to buses in cluster 24</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_007</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 7</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_IND_005</t>
   </si>
   <si>
@@ -2502,6 +2526,12 @@
     <t>connecting wind offshore to buses in cluster 21</t>
   </si>
   <si>
+    <t>distr_wofelc_wof_IND_020</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 20</t>
+  </si>
+  <si>
     <t>distr_wofelc_wof_IND_010</t>
   </si>
   <si>
@@ -2514,16 +2544,22 @@
     <t>connecting wind offshore to buses in cluster 18</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_017</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 17</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_022</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 22</t>
+    <t>distr_wofelc_wof_IND_001</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 1</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_004</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 4</t>
+  </si>
+  <si>
+    <t>distr_wofelc_wof_IND_006</t>
+  </si>
+  <si>
+    <t>connecting wind offshore to buses in cluster 6</t>
   </si>
   <si>
     <t>distr_wofelc_wof_IND_008</t>
@@ -2544,51 +2580,30 @@
     <t>connecting wind offshore to buses in cluster 19</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 20</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_001</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 1</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_002</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 2</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_009</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 9</t>
-  </si>
-  <si>
     <t>distr_wofelc_wof_IND_016</t>
   </si>
   <si>
     <t>connecting wind offshore to buses in cluster 16</t>
   </si>
   <si>
-    <t>distr_wofelc_wof_IND_004</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 4</t>
-  </si>
-  <si>
-    <t>distr_wofelc_wof_IND_006</t>
-  </si>
-  <si>
-    <t>connecting wind offshore to buses in cluster 6</t>
+    <t>elc_wof_IND_007</t>
   </si>
   <si>
     <t>elc_wof_IND_013</t>
   </si>
   <si>
+    <t>elc_wof_IND_017</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_022</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_002</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_009</t>
+  </si>
+  <si>
     <t>elc_wof_IND_014</t>
   </si>
   <si>
@@ -2607,25 +2622,28 @@
     <t>elc_wof_IND_024</t>
   </si>
   <si>
-    <t>elc_wof_IND_007</t>
-  </si>
-  <si>
     <t>elc_wof_IND_005</t>
   </si>
   <si>
     <t>elc_wof_IND_021</t>
   </si>
   <si>
+    <t>elc_wof_IND_020</t>
+  </si>
+  <si>
     <t>elc_wof_IND_010</t>
   </si>
   <si>
     <t>elc_wof_IND_018</t>
   </si>
   <si>
-    <t>elc_wof_IND_017</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_022</t>
+    <t>elc_wof_IND_001</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_004</t>
+  </si>
+  <si>
+    <t>elc_wof_IND_006</t>
   </si>
   <si>
     <t>elc_wof_IND_008</t>
@@ -2637,25 +2655,7 @@
     <t>elc_wof_IND_019</t>
   </si>
   <si>
-    <t>elc_wof_IND_020</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_001</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_002</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_009</t>
-  </si>
-  <si>
     <t>elc_wof_IND_016</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_004</t>
-  </si>
-  <si>
-    <t>elc_wof_IND_006</t>
   </si>
   <si>
     <t>e_won_IND_001</t>
@@ -7512,7 +7512,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63951672-8E43-413D-AAC4-06F71E9CAC43}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22988986-0CA7-4E26-917F-11FEDE84329F}">
   <dimension ref="B9:BD88"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -7750,16 +7750,16 @@
         <v>389</v>
       </c>
       <c r="Y11" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="Z11" t="s">
         <v>549</v>
       </c>
       <c r="AA11">
-        <v>0.99574277994898297</v>
+        <v>0.99244124560610847</v>
       </c>
       <c r="AB11">
-        <v>78.049034268645343</v>
+        <v>138.57716388801143</v>
       </c>
       <c r="AD11" t="s">
         <v>388</v>
@@ -7789,7 +7789,7 @@
         <v>726</v>
       </c>
       <c r="AN11" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="AO11">
         <v>0.99460623000179826</v>
@@ -7825,13 +7825,13 @@
         <v>840</v>
       </c>
       <c r="BB11" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="BC11">
-        <v>0.98385755699927302</v>
+        <v>0.98617370816492766</v>
       </c>
       <c r="BD11">
-        <v>941.2687638921899</v>
+        <v>913.05032219063128</v>
       </c>
     </row>
     <row r="12" spans="2:56">
@@ -7896,16 +7896,16 @@
         <v>393</v>
       </c>
       <c r="Y12" t="s">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="Z12" t="s">
         <v>550</v>
       </c>
       <c r="AA12">
-        <v>0.98237714666165721</v>
+        <v>0.98474401913329324</v>
       </c>
       <c r="AB12">
-        <v>323.08564453628389</v>
+        <v>279.69298255629104</v>
       </c>
       <c r="AD12" t="s">
         <v>388</v>
@@ -7935,7 +7935,7 @@
         <v>727</v>
       </c>
       <c r="AN12" t="s">
-        <v>580</v>
+        <v>568</v>
       </c>
       <c r="AO12">
         <v>0.99150673149027269</v>
@@ -7971,13 +7971,13 @@
         <v>841</v>
       </c>
       <c r="BB12" t="s">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="BC12">
-        <v>0.97753834043268606</v>
+        <v>0.98385755699927302</v>
       </c>
       <c r="BD12">
-        <v>1018.2578857284417</v>
+        <v>941.2687638921899</v>
       </c>
     </row>
     <row r="13" spans="2:56">
@@ -8042,16 +8042,16 @@
         <v>395</v>
       </c>
       <c r="Y13" t="s">
-        <v>349</v>
+        <v>319</v>
       </c>
       <c r="Z13" t="s">
         <v>551</v>
       </c>
       <c r="AA13">
-        <v>0.98850112471309615</v>
+        <v>0.9917320687619966</v>
       </c>
       <c r="AB13">
-        <v>210.81271359323659</v>
+        <v>151.57873936339664</v>
       </c>
       <c r="AD13" t="s">
         <v>388</v>
@@ -8081,7 +8081,7 @@
         <v>728</v>
       </c>
       <c r="AN13" t="s">
-        <v>583</v>
+        <v>555</v>
       </c>
       <c r="AO13">
         <v>0.99428348998771221</v>
@@ -8117,13 +8117,13 @@
         <v>842</v>
       </c>
       <c r="BB13" t="s">
-        <v>580</v>
+        <v>561</v>
       </c>
       <c r="BC13">
-        <v>0.98473459040058986</v>
+        <v>0.9915182189163928</v>
       </c>
       <c r="BD13">
-        <v>930.58357361947958</v>
+        <v>791.61037277293372</v>
       </c>
     </row>
     <row r="14" spans="2:56">
@@ -8188,16 +8188,16 @@
         <v>397</v>
       </c>
       <c r="Y14" t="s">
-        <v>358</v>
+        <v>325</v>
       </c>
       <c r="Z14" t="s">
         <v>552</v>
       </c>
       <c r="AA14">
-        <v>0.99482221718343289</v>
+        <v>0.99396192960580998</v>
       </c>
       <c r="AB14">
-        <v>94.926018303729833</v>
+        <v>110.69795722681697</v>
       </c>
       <c r="AD14" t="s">
         <v>388</v>
@@ -8227,7 +8227,7 @@
         <v>729</v>
       </c>
       <c r="AN14" t="s">
-        <v>564</v>
+        <v>580</v>
       </c>
       <c r="AO14">
         <v>0.99089509058322967</v>
@@ -8263,13 +8263,13 @@
         <v>843</v>
       </c>
       <c r="BB14" t="s">
-        <v>577</v>
+        <v>556</v>
       </c>
       <c r="BC14">
-        <v>0.9888190320671576</v>
+        <v>0.98016998510849251</v>
       </c>
       <c r="BD14">
-        <v>880.82145931513014</v>
+        <v>986.19568142819946</v>
       </c>
     </row>
     <row r="15" spans="2:56">
@@ -8334,16 +8334,16 @@
         <v>399</v>
       </c>
       <c r="Y15" t="s">
-        <v>311</v>
+        <v>370</v>
       </c>
       <c r="Z15" t="s">
         <v>553</v>
       </c>
       <c r="AA15">
-        <v>0.9937576135345404</v>
+        <v>0.99238783341703851</v>
       </c>
       <c r="AB15">
-        <v>114.44375186676042</v>
+        <v>139.55638735429352</v>
       </c>
       <c r="AD15" t="s">
         <v>388</v>
@@ -8373,7 +8373,7 @@
         <v>730</v>
       </c>
       <c r="AN15" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="AO15">
         <v>0.99450138933360577</v>
@@ -8409,13 +8409,13 @@
         <v>844</v>
       </c>
       <c r="BB15" t="s">
-        <v>577</v>
+        <v>549</v>
       </c>
       <c r="BC15">
-        <v>0.98444840170938386</v>
+        <v>0.96754380619969493</v>
       </c>
       <c r="BD15">
-        <v>934.07030584067388</v>
+        <v>1140.0246278003831</v>
       </c>
     </row>
     <row r="16" spans="2:56">
@@ -8480,16 +8480,16 @@
         <v>401</v>
       </c>
       <c r="Y16" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="Z16" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="AA16">
-        <v>0.99492636929999068</v>
+        <v>0.98899223079090937</v>
       </c>
       <c r="AB16">
-        <v>93.016562833504807</v>
+        <v>201.80910216666135</v>
       </c>
       <c r="AD16" t="s">
         <v>388</v>
@@ -8519,13 +8519,13 @@
         <v>731</v>
       </c>
       <c r="AN16" t="s">
-        <v>588</v>
+        <v>552</v>
       </c>
       <c r="AO16">
-        <v>0.99429570648020904</v>
+        <v>0.99072423448493052</v>
       </c>
       <c r="AP16">
-        <v>104.57871452950124</v>
+        <v>170.05570110960724</v>
       </c>
       <c r="AR16" t="s">
         <v>388</v>
@@ -8555,13 +8555,13 @@
         <v>845</v>
       </c>
       <c r="BB16" t="s">
-        <v>558</v>
+        <v>582</v>
       </c>
       <c r="BC16">
-        <v>0.98664748299407956</v>
+        <v>0.98056622345336075</v>
       </c>
       <c r="BD16">
-        <v>907.27816552213119</v>
+        <v>981.36817759322128</v>
       </c>
     </row>
     <row r="17" spans="2:56">
@@ -8626,16 +8626,16 @@
         <v>403</v>
       </c>
       <c r="Y17" t="s">
-        <v>322</v>
+        <v>347</v>
       </c>
       <c r="Z17" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="AA17">
-        <v>0.98434977749377373</v>
+        <v>0.99373922796305081</v>
       </c>
       <c r="AB17">
-        <v>286.9207459474826</v>
+        <v>114.78082067740091</v>
       </c>
       <c r="AD17" t="s">
         <v>388</v>
@@ -8665,13 +8665,13 @@
         <v>732</v>
       </c>
       <c r="AN17" t="s">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="AO17">
-        <v>0.99452028244067281</v>
+        <v>0.99538801767339902</v>
       </c>
       <c r="AP17">
-        <v>100.46148858766527</v>
+        <v>84.553009321017754</v>
       </c>
       <c r="AR17" t="s">
         <v>388</v>
@@ -8701,13 +8701,13 @@
         <v>846</v>
       </c>
       <c r="BB17" t="s">
-        <v>558</v>
+        <v>582</v>
       </c>
       <c r="BC17">
-        <v>0.98382004037728943</v>
+        <v>0.97753834043268606</v>
       </c>
       <c r="BD17">
-        <v>941.72584140335653</v>
+        <v>1018.2578857284417</v>
       </c>
     </row>
     <row r="18" spans="2:56">
@@ -8772,16 +8772,16 @@
         <v>405</v>
       </c>
       <c r="Y18" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="Z18" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AA18">
-        <v>0.99326064633097277</v>
+        <v>0.99489337597419902</v>
       </c>
       <c r="AB18">
-        <v>123.55481726549976</v>
+        <v>93.621440473017302</v>
       </c>
       <c r="AD18" t="s">
         <v>388</v>
@@ -8811,13 +8811,13 @@
         <v>733</v>
       </c>
       <c r="AN18" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="AO18">
-        <v>0.98743486034963512</v>
+        <v>0.98686185087293077</v>
       </c>
       <c r="AP18">
-        <v>230.36089359002219</v>
+        <v>240.86606732960294</v>
       </c>
       <c r="AR18" t="s">
         <v>388</v>
@@ -8847,13 +8847,13 @@
         <v>847</v>
       </c>
       <c r="BB18" t="s">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="BC18">
-        <v>0.98617370816492766</v>
+        <v>0.98473459040058986</v>
       </c>
       <c r="BD18">
-        <v>913.05032219063128</v>
+        <v>930.58357361947958</v>
       </c>
     </row>
     <row r="19" spans="2:56">
@@ -8918,16 +8918,16 @@
         <v>407</v>
       </c>
       <c r="Y19" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Z19" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AA19">
-        <v>0.99457218279364812</v>
+        <v>0.98750565217961461</v>
       </c>
       <c r="AB19">
-        <v>99.509982116450402</v>
+        <v>229.06304337373263</v>
       </c>
       <c r="AD19" t="s">
         <v>388</v>
@@ -8957,13 +8957,13 @@
         <v>734</v>
       </c>
       <c r="AN19" t="s">
-        <v>586</v>
+        <v>559</v>
       </c>
       <c r="AO19">
-        <v>0.9946374817042809</v>
+        <v>0.99429570648020904</v>
       </c>
       <c r="AP19">
-        <v>98.312835421515885</v>
+        <v>104.57871452950124</v>
       </c>
       <c r="AR19" t="s">
         <v>388</v>
@@ -8993,13 +8993,13 @@
         <v>848</v>
       </c>
       <c r="BB19" t="s">
-        <v>550</v>
+        <v>582</v>
       </c>
       <c r="BC19">
-        <v>0.97059082241136851</v>
+        <v>0.9888190320671576</v>
       </c>
       <c r="BD19">
-        <v>1102.9018136214943</v>
+        <v>880.82145931513014</v>
       </c>
     </row>
     <row r="20" spans="2:56">
@@ -9064,16 +9064,16 @@
         <v>409</v>
       </c>
       <c r="Y20" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="Z20" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="AA20">
-        <v>0.99259244228658239</v>
+        <v>0.99303639237349761</v>
       </c>
       <c r="AB20">
-        <v>135.80522474598871</v>
+        <v>127.66613981921104</v>
       </c>
       <c r="AD20" t="s">
         <v>388</v>
@@ -9103,13 +9103,13 @@
         <v>735</v>
       </c>
       <c r="AN20" t="s">
-        <v>566</v>
+        <v>580</v>
       </c>
       <c r="AO20">
-        <v>0.99545219173782828</v>
+        <v>0.99452028244067281</v>
       </c>
       <c r="AP20">
-        <v>83.376484806480903</v>
+        <v>100.46148858766527</v>
       </c>
       <c r="AR20" t="s">
         <v>388</v>
@@ -9139,13 +9139,13 @@
         <v>849</v>
       </c>
       <c r="BB20" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="BC20">
-        <v>0.98631188388799174</v>
+        <v>0.98444840170938386</v>
       </c>
       <c r="BD20">
-        <v>911.36688129796778</v>
+        <v>934.07030584067388</v>
       </c>
     </row>
     <row r="21" spans="2:56">
@@ -9210,16 +9210,16 @@
         <v>411</v>
       </c>
       <c r="Y21" t="s">
-        <v>381</v>
+        <v>316</v>
       </c>
       <c r="Z21" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="AA21">
-        <v>0.99486868336004353</v>
+        <v>0.99335604161179136</v>
       </c>
       <c r="AB21">
-        <v>94.074138399201615</v>
+        <v>121.80590378382558</v>
       </c>
       <c r="AD21" t="s">
         <v>388</v>
@@ -9249,13 +9249,13 @@
         <v>736</v>
       </c>
       <c r="AN21" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="AO21">
-        <v>0.99145037244742884</v>
+        <v>0.98743486034963512</v>
       </c>
       <c r="AP21">
-        <v>156.74317179713734</v>
+        <v>230.36089359002219</v>
       </c>
       <c r="AR21" t="s">
         <v>388</v>
@@ -9285,13 +9285,13 @@
         <v>850</v>
       </c>
       <c r="BB21" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="BC21">
-        <v>0.98424383368757629</v>
+        <v>0.98664748299407956</v>
       </c>
       <c r="BD21">
-        <v>936.56262623969508</v>
+        <v>907.27816552213119</v>
       </c>
     </row>
     <row r="22" spans="2:56">
@@ -9356,16 +9356,16 @@
         <v>413</v>
       </c>
       <c r="Y22" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="Z22" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AA22">
-        <v>0.99449168757100159</v>
+        <v>0.99498097012747577</v>
       </c>
       <c r="AB22">
-        <v>100.98572786497003</v>
+        <v>92.015547662944215</v>
       </c>
       <c r="AD22" t="s">
         <v>388</v>
@@ -9395,13 +9395,13 @@
         <v>737</v>
       </c>
       <c r="AN22" t="s">
-        <v>562</v>
+        <v>592</v>
       </c>
       <c r="AO22">
-        <v>0.98960196900926922</v>
+        <v>0.99689862129048645</v>
       </c>
       <c r="AP22">
-        <v>190.63056816339852</v>
+        <v>56.858609674414254</v>
       </c>
       <c r="AR22" t="s">
         <v>388</v>
@@ -9431,13 +9431,13 @@
         <v>851</v>
       </c>
       <c r="BB22" t="s">
-        <v>557</v>
+        <v>575</v>
       </c>
       <c r="BC22">
-        <v>0.9864641946771695</v>
+        <v>0.98382004037728943</v>
       </c>
       <c r="BD22">
-        <v>909.51122818315105</v>
+        <v>941.72584140335653</v>
       </c>
     </row>
     <row r="23" spans="2:56">
@@ -9502,16 +9502,16 @@
         <v>415</v>
       </c>
       <c r="Y23" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="Z23" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="AA23">
-        <v>0.99024242083669489</v>
+        <v>0.99068678367690288</v>
       </c>
       <c r="AB23">
-        <v>178.88895132725995</v>
+        <v>170.7422992567804</v>
       </c>
       <c r="AD23" t="s">
         <v>388</v>
@@ -9541,13 +9541,13 @@
         <v>738</v>
       </c>
       <c r="AN23" t="s">
-        <v>581</v>
+        <v>551</v>
       </c>
       <c r="AO23">
-        <v>0.99043701029499331</v>
+        <v>0.99177044540821302</v>
       </c>
       <c r="AP23">
-        <v>175.3214779251216</v>
+        <v>150.87516751609439</v>
       </c>
       <c r="AR23" t="s">
         <v>388</v>
@@ -9577,13 +9577,13 @@
         <v>852</v>
       </c>
       <c r="BB23" t="s">
-        <v>578</v>
+        <v>588</v>
       </c>
       <c r="BC23">
-        <v>0.9915182189163928</v>
+        <v>0.97059082241136851</v>
       </c>
       <c r="BD23">
-        <v>791.61037277293372</v>
+        <v>1102.9018136214943</v>
       </c>
     </row>
     <row r="24" spans="2:56">
@@ -9648,16 +9648,16 @@
         <v>417</v>
       </c>
       <c r="Y24" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="Z24" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="AA24">
-        <v>0.99373222027139962</v>
+        <v>0.99380018286737304</v>
       </c>
       <c r="AB24">
-        <v>114.90929502433978</v>
+        <v>113.66331409816142</v>
       </c>
       <c r="AD24" t="s">
         <v>388</v>
@@ -9687,13 +9687,13 @@
         <v>739</v>
       </c>
       <c r="AN24" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="AO24">
-        <v>0.99286149679037794</v>
+        <v>0.99458282020478328</v>
       </c>
       <c r="AP24">
-        <v>130.8725588430718</v>
+        <v>99.314962912306555</v>
       </c>
       <c r="AR24" t="s">
         <v>388</v>
@@ -9723,13 +9723,13 @@
         <v>853</v>
       </c>
       <c r="BB24" t="s">
-        <v>584</v>
+        <v>556</v>
       </c>
       <c r="BC24">
-        <v>0.98016998510849251</v>
+        <v>0.98631188388799174</v>
       </c>
       <c r="BD24">
-        <v>986.19568142819946</v>
+        <v>911.36688129796778</v>
       </c>
     </row>
     <row r="25" spans="2:56">
@@ -9794,16 +9794,16 @@
         <v>419</v>
       </c>
       <c r="Y25" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="Z25" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="AA25">
-        <v>0.99448854992358493</v>
+        <v>0.99045178849779958</v>
       </c>
       <c r="AB25">
-        <v>101.04325140094389</v>
+        <v>175.0505442070075</v>
       </c>
       <c r="AD25" t="s">
         <v>388</v>
@@ -9833,13 +9833,13 @@
         <v>740</v>
       </c>
       <c r="AN25" t="s">
-        <v>561</v>
+        <v>582</v>
       </c>
       <c r="AO25">
-        <v>0.99188199243556163</v>
+        <v>0.9919109979004006</v>
       </c>
       <c r="AP25">
-        <v>148.83013868136976</v>
+        <v>148.29837182598865</v>
       </c>
       <c r="AR25" t="s">
         <v>388</v>
@@ -9869,13 +9869,13 @@
         <v>854</v>
       </c>
       <c r="BB25" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="BC25">
-        <v>0.99333706474272454</v>
+        <v>0.9889246589664985</v>
       </c>
       <c r="BD25">
-        <v>676.17429099508138</v>
+        <v>879.53457159149264</v>
       </c>
     </row>
     <row r="26" spans="2:56">
@@ -9940,16 +9940,16 @@
         <v>421</v>
       </c>
       <c r="Y26" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="Z26" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="AA26">
-        <v>0.99338948553444661</v>
+        <v>0.99360342768209686</v>
       </c>
       <c r="AB26">
-        <v>121.19276520181113</v>
+        <v>117.27049249489188</v>
       </c>
       <c r="AD26" t="s">
         <v>388</v>
@@ -9979,13 +9979,13 @@
         <v>741</v>
       </c>
       <c r="AN26" t="s">
-        <v>551</v>
+        <v>574</v>
       </c>
       <c r="AO26">
-        <v>0.98666678680685382</v>
+        <v>0.9944043961659097</v>
       </c>
       <c r="AP26">
-        <v>244.44224187434608</v>
+        <v>102.58607029165618</v>
       </c>
       <c r="AR26" t="s">
         <v>388</v>
@@ -10015,13 +10015,13 @@
         <v>855</v>
       </c>
       <c r="BB26" t="s">
-        <v>564</v>
+        <v>582</v>
       </c>
       <c r="BC26">
-        <v>0.98335099885385724</v>
+        <v>0.98424383368757629</v>
       </c>
       <c r="BD26">
-        <v>947.44033063050631</v>
+        <v>936.56262623969508</v>
       </c>
     </row>
     <row r="27" spans="2:56">
@@ -10086,16 +10086,16 @@
         <v>423</v>
       </c>
       <c r="Y27" t="s">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="Z27" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="AA27">
-        <v>0.99418942224649776</v>
+        <v>0.9941610020412821</v>
       </c>
       <c r="AB27">
-        <v>106.527258814208</v>
+        <v>107.04829590982715</v>
       </c>
       <c r="AD27" t="s">
         <v>388</v>
@@ -10125,13 +10125,13 @@
         <v>742</v>
       </c>
       <c r="AN27" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="AO27">
-        <v>0.99461739117688308</v>
+        <v>0.99602637227621282</v>
       </c>
       <c r="AP27">
-        <v>98.68116175714421</v>
+        <v>72.849841602764897</v>
       </c>
       <c r="AR27" t="s">
         <v>388</v>
@@ -10161,13 +10161,13 @@
         <v>856</v>
       </c>
       <c r="BB27" t="s">
-        <v>557</v>
+        <v>574</v>
       </c>
       <c r="BC27">
-        <v>0.99542038465569349</v>
+        <v>0.9864641946771695</v>
       </c>
       <c r="BD27">
-        <v>543.95292051865363</v>
+        <v>909.51122818315105</v>
       </c>
     </row>
     <row r="28" spans="2:56">
@@ -10232,16 +10232,16 @@
         <v>425</v>
       </c>
       <c r="Y28" t="s">
-        <v>383</v>
+        <v>321</v>
       </c>
       <c r="Z28" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="AA28">
-        <v>0.99472498859344116</v>
+        <v>0.9938080410601946</v>
       </c>
       <c r="AB28">
-        <v>96.708542453579653</v>
+        <v>113.51924722976577</v>
       </c>
       <c r="AD28" t="s">
         <v>388</v>
@@ -10271,13 +10271,13 @@
         <v>743</v>
       </c>
       <c r="AN28" t="s">
-        <v>576</v>
+        <v>563</v>
       </c>
       <c r="AO28">
-        <v>0.98713907316291682</v>
+        <v>0.99333586753421554</v>
       </c>
       <c r="AP28">
-        <v>235.78365867985792</v>
+        <v>122.17576187271403</v>
       </c>
       <c r="AR28" t="s">
         <v>388</v>
@@ -10307,13 +10307,13 @@
         <v>857</v>
       </c>
       <c r="BB28" t="s">
-        <v>584</v>
+        <v>549</v>
       </c>
       <c r="BC28">
-        <v>0.9889246589664985</v>
+        <v>0.97462367221641244</v>
       </c>
       <c r="BD28">
-        <v>879.53457159149264</v>
+        <v>1053.7682601633755</v>
       </c>
     </row>
     <row r="29" spans="2:56">
@@ -10378,16 +10378,16 @@
         <v>427</v>
       </c>
       <c r="Y29" t="s">
-        <v>319</v>
+        <v>355</v>
       </c>
       <c r="Z29" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="AA29">
-        <v>0.9917320687619966</v>
+        <v>0.99382896634585005</v>
       </c>
       <c r="AB29">
-        <v>151.57873936339664</v>
+        <v>113.13561699274842</v>
       </c>
       <c r="AD29" t="s">
         <v>388</v>
@@ -10417,13 +10417,13 @@
         <v>744</v>
       </c>
       <c r="AN29" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
       <c r="AO29">
-        <v>0.99072423448493052</v>
+        <v>0.98940376322023671</v>
       </c>
       <c r="AP29">
-        <v>170.05570110960724</v>
+        <v>194.264340962326</v>
       </c>
       <c r="AR29" t="s">
         <v>388</v>
@@ -10453,13 +10453,13 @@
         <v>858</v>
       </c>
       <c r="BB29" t="s">
-        <v>555</v>
+        <v>568</v>
       </c>
       <c r="BC29">
-        <v>0.97462367221641244</v>
+        <v>0.98811227602433394</v>
       </c>
       <c r="BD29">
-        <v>1053.7682601633755</v>
+        <v>889.43210377019864</v>
       </c>
     </row>
     <row r="30" spans="2:56">
@@ -10524,16 +10524,16 @@
         <v>429</v>
       </c>
       <c r="Y30" t="s">
-        <v>325</v>
+        <v>375</v>
       </c>
       <c r="Z30" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="AA30">
-        <v>0.99396192960580998</v>
+        <v>0.99140742806735527</v>
       </c>
       <c r="AB30">
-        <v>110.69795722681697</v>
+        <v>157.53048543182001</v>
       </c>
       <c r="AD30" t="s">
         <v>388</v>
@@ -10563,13 +10563,13 @@
         <v>745</v>
       </c>
       <c r="AN30" t="s">
-        <v>563</v>
+        <v>587</v>
       </c>
       <c r="AO30">
-        <v>0.99538801767339902</v>
+        <v>0.98898412609077158</v>
       </c>
       <c r="AP30">
-        <v>84.553009321017754</v>
+        <v>201.95768833585458</v>
       </c>
       <c r="AR30" t="s">
         <v>388</v>
@@ -10599,13 +10599,13 @@
         <v>859</v>
       </c>
       <c r="BB30" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="BC30">
-        <v>0.96754380619969493</v>
+        <v>0.964765711303333</v>
       </c>
       <c r="BD30">
-        <v>1140.0246278003831</v>
+        <v>1173.8710839543928</v>
       </c>
     </row>
     <row r="31" spans="2:56">
@@ -10670,16 +10670,16 @@
         <v>431</v>
       </c>
       <c r="Y31" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="Z31" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="AA31">
-        <v>0.99238783341703851</v>
+        <v>0.98706515821359619</v>
       </c>
       <c r="AB31">
-        <v>139.55638735429352</v>
+        <v>237.13876608406935</v>
       </c>
       <c r="AD31" t="s">
         <v>388</v>
@@ -10709,13 +10709,13 @@
         <v>746</v>
       </c>
       <c r="AN31" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="AO31">
-        <v>0.98686185087293077</v>
+        <v>0.99296413260223493</v>
       </c>
       <c r="AP31">
-        <v>240.86606732960294</v>
+        <v>128.99090229235989</v>
       </c>
       <c r="AR31" t="s">
         <v>388</v>
@@ -10745,13 +10745,13 @@
         <v>860</v>
       </c>
       <c r="BB31" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="BC31">
-        <v>0.98056622345336075</v>
+        <v>0.99333706474272454</v>
       </c>
       <c r="BD31">
-        <v>981.36817759322128</v>
+        <v>676.17429099508138</v>
       </c>
     </row>
     <row r="32" spans="2:56">
@@ -10816,16 +10816,16 @@
         <v>433</v>
       </c>
       <c r="Y32" t="s">
-        <v>317</v>
+        <v>384</v>
       </c>
       <c r="Z32" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="AA32">
-        <v>0.98974554419194471</v>
+        <v>0.99504215698918186</v>
       </c>
       <c r="AB32">
-        <v>187.99835648101393</v>
+        <v>90.893788531666857</v>
       </c>
       <c r="AD32" t="s">
         <v>388</v>
@@ -10855,13 +10855,13 @@
         <v>747</v>
       </c>
       <c r="AN32" t="s">
-        <v>591</v>
+        <v>569</v>
       </c>
       <c r="AO32">
-        <v>0.99552417511484081</v>
+        <v>0.99403594090084912</v>
       </c>
       <c r="AP32">
-        <v>82.056789561251392</v>
+        <v>109.34108348443232</v>
       </c>
       <c r="AR32" t="s">
         <v>388</v>
@@ -10891,13 +10891,13 @@
         <v>861</v>
       </c>
       <c r="BB32" t="s">
-        <v>564</v>
+        <v>580</v>
       </c>
       <c r="BC32">
-        <v>0.98380308075994261</v>
+        <v>0.98335099885385724</v>
       </c>
       <c r="BD32">
-        <v>941.93246607469882</v>
+        <v>947.44033063050631</v>
       </c>
     </row>
     <row r="33" spans="2:56">
@@ -10962,16 +10962,16 @@
         <v>435</v>
       </c>
       <c r="Y33" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="Z33" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="AA33">
-        <v>0.99547433853743716</v>
+        <v>0.99275682304809643</v>
       </c>
       <c r="AB33">
-        <v>82.970460146984365</v>
+        <v>132.79157745156544</v>
       </c>
       <c r="AD33" t="s">
         <v>388</v>
@@ -11001,13 +11001,13 @@
         <v>748</v>
       </c>
       <c r="AN33" t="s">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="AO33">
-        <v>0.98351881644633699</v>
+        <v>0.98943318015939452</v>
       </c>
       <c r="AP33">
-        <v>302.15503181715462</v>
+        <v>193.72503041110133</v>
       </c>
       <c r="AR33" t="s">
         <v>388</v>
@@ -11037,13 +11037,13 @@
         <v>862</v>
       </c>
       <c r="BB33" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="BC33">
-        <v>0.98811227602433394</v>
+        <v>0.99542038465569349</v>
       </c>
       <c r="BD33">
-        <v>889.43210377019864</v>
+        <v>543.95292051865363</v>
       </c>
     </row>
     <row r="34" spans="2:56">
@@ -11108,16 +11108,16 @@
         <v>437</v>
       </c>
       <c r="Y34" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="Z34" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="AA34">
-        <v>0.99432421190931886</v>
+        <v>0.98666777524932958</v>
       </c>
       <c r="AB34">
-        <v>104.05611499582191</v>
+        <v>244.42412042895722</v>
       </c>
       <c r="AD34" t="s">
         <v>388</v>
@@ -11147,13 +11147,13 @@
         <v>749</v>
       </c>
       <c r="AN34" t="s">
-        <v>552</v>
+        <v>591</v>
       </c>
       <c r="AO34">
-        <v>0.99485915243795964</v>
+        <v>0.99037301617060403</v>
       </c>
       <c r="AP34">
-        <v>94.248871970740922</v>
+        <v>176.49470353892534</v>
       </c>
       <c r="AR34" t="s">
         <v>388</v>
@@ -11183,13 +11183,13 @@
         <v>863</v>
       </c>
       <c r="BB34" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="BC34">
-        <v>0.964765711303333</v>
+        <v>0.98380308075994261</v>
       </c>
       <c r="BD34">
-        <v>1173.8710839543928</v>
+        <v>941.93246607469882</v>
       </c>
     </row>
     <row r="35" spans="2:56">
@@ -11254,16 +11254,16 @@
         <v>439</v>
       </c>
       <c r="Y35" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="Z35" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="AA35">
-        <v>0.99439207214359926</v>
+        <v>0.99269116352039599</v>
       </c>
       <c r="AB35">
-        <v>102.81201070067981</v>
+        <v>133.99533545940744</v>
       </c>
       <c r="AD35" t="s">
         <v>388</v>
@@ -11293,13 +11293,13 @@
         <v>750</v>
       </c>
       <c r="AN35" t="s">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="AO35">
-        <v>0.98978334793138389</v>
+        <v>0.99215519768283411</v>
       </c>
       <c r="AP35">
-        <v>187.30528792462934</v>
+        <v>143.82137581470715</v>
       </c>
     </row>
     <row r="36" spans="2:56">
@@ -11364,16 +11364,16 @@
         <v>441</v>
       </c>
       <c r="Y36" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="Z36" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="AA36">
-        <v>0.99130148530232876</v>
+        <v>0.99006453671041028</v>
       </c>
       <c r="AB36">
-        <v>159.47276945730601</v>
+        <v>182.15016030914441</v>
       </c>
       <c r="AD36" t="s">
         <v>388</v>
@@ -11403,13 +11403,13 @@
         <v>751</v>
       </c>
       <c r="AN36" t="s">
-        <v>555</v>
+        <v>584</v>
       </c>
       <c r="AO36">
-        <v>0.99170932898012365</v>
+        <v>0.99145037244742884</v>
       </c>
       <c r="AP36">
-        <v>151.99563536440075</v>
+        <v>156.74317179713734</v>
       </c>
     </row>
     <row r="37" spans="2:56">
@@ -11474,16 +11474,16 @@
         <v>443</v>
       </c>
       <c r="Y37" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="Z37" t="s">
-        <v>555</v>
+        <v>571</v>
       </c>
       <c r="AA37">
-        <v>0.99244124560610847</v>
+        <v>0.9937576135345404</v>
       </c>
       <c r="AB37">
-        <v>138.57716388801143</v>
+        <v>114.44375186676042</v>
       </c>
       <c r="AD37" t="s">
         <v>388</v>
@@ -11513,13 +11513,13 @@
         <v>752</v>
       </c>
       <c r="AN37" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="AO37">
-        <v>0.99400997521961898</v>
+        <v>0.98960196900926922</v>
       </c>
       <c r="AP37">
-        <v>109.8171209736516</v>
+        <v>190.63056816339852</v>
       </c>
     </row>
     <row r="38" spans="2:56">
@@ -11584,16 +11584,16 @@
         <v>445</v>
       </c>
       <c r="Y38" t="s">
-        <v>374</v>
+        <v>313</v>
       </c>
       <c r="Z38" t="s">
-        <v>565</v>
+        <v>572</v>
       </c>
       <c r="AA38">
-        <v>0.98474401913329324</v>
+        <v>0.99492636929999068</v>
       </c>
       <c r="AB38">
-        <v>279.69298255629104</v>
+        <v>93.016562833504807</v>
       </c>
       <c r="AD38" t="s">
         <v>388</v>
@@ -11623,13 +11623,13 @@
         <v>753</v>
       </c>
       <c r="AN38" t="s">
-        <v>589</v>
+        <v>554</v>
       </c>
       <c r="AO38">
-        <v>0.99270356346131094</v>
+        <v>0.99043701029499331</v>
       </c>
       <c r="AP38">
-        <v>133.76800320929971</v>
+        <v>175.3214779251216</v>
       </c>
     </row>
     <row r="39" spans="2:56">
@@ -11694,16 +11694,16 @@
         <v>447</v>
       </c>
       <c r="Y39" t="s">
-        <v>309</v>
+        <v>322</v>
       </c>
       <c r="Z39" t="s">
-        <v>574</v>
+        <v>549</v>
       </c>
       <c r="AA39">
-        <v>0.99245084214861234</v>
+        <v>0.98434977749377373</v>
       </c>
       <c r="AB39">
-        <v>138.40122727544065</v>
+        <v>286.9207459474826</v>
       </c>
       <c r="AD39" t="s">
         <v>388</v>
@@ -11733,13 +11733,13 @@
         <v>754</v>
       </c>
       <c r="AN39" t="s">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="AO39">
-        <v>0.98675990563829141</v>
+        <v>0.99392053283098158</v>
       </c>
       <c r="AP39">
-        <v>242.73506329798991</v>
+        <v>111.45689809867115</v>
       </c>
     </row>
     <row r="40" spans="2:56">
@@ -11804,16 +11804,16 @@
         <v>449</v>
       </c>
       <c r="Y40" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="Z40" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="AA40">
-        <v>0.99410067440989558</v>
+        <v>0.99326064633097277</v>
       </c>
       <c r="AB40">
-        <v>108.15430248524751</v>
+        <v>123.55481726549976</v>
       </c>
       <c r="AD40" t="s">
         <v>388</v>
@@ -11843,13 +11843,13 @@
         <v>755</v>
       </c>
       <c r="AN40" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="AO40">
-        <v>0.99286153879604566</v>
+        <v>0.99519706487556603</v>
       </c>
       <c r="AP40">
-        <v>130.87178873916278</v>
+        <v>88.053810614623103</v>
       </c>
     </row>
     <row r="41" spans="2:56">
@@ -11914,16 +11914,16 @@
         <v>451</v>
       </c>
       <c r="Y41" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="Z41" t="s">
-        <v>552</v>
+        <v>574</v>
       </c>
       <c r="AA41">
-        <v>0.9875438296240775</v>
+        <v>0.99457218279364812</v>
       </c>
       <c r="AB41">
-        <v>228.36312355857854</v>
+        <v>99.509982116450402</v>
       </c>
       <c r="AD41" t="s">
         <v>388</v>
@@ -11953,13 +11953,13 @@
         <v>756</v>
       </c>
       <c r="AN41" t="s">
-        <v>570</v>
+        <v>576</v>
       </c>
       <c r="AO41">
-        <v>0.98940376322023671</v>
+        <v>0.99116017126466804</v>
       </c>
       <c r="AP41">
-        <v>194.264340962326</v>
+        <v>162.0635268144182</v>
       </c>
     </row>
     <row r="42" spans="2:56">
@@ -12024,16 +12024,16 @@
         <v>453</v>
       </c>
       <c r="Y42" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="Z42" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="AA42">
-        <v>0.99433118964233247</v>
+        <v>0.99259244228658239</v>
       </c>
       <c r="AB42">
-        <v>103.92818989057204</v>
+        <v>135.80522474598871</v>
       </c>
       <c r="AD42" t="s">
         <v>388</v>
@@ -12063,13 +12063,13 @@
         <v>757</v>
       </c>
       <c r="AN42" t="s">
-        <v>572</v>
+        <v>588</v>
       </c>
       <c r="AO42">
-        <v>0.98898412609077158</v>
+        <v>0.99287761065972435</v>
       </c>
       <c r="AP42">
-        <v>201.95768833585458</v>
+        <v>130.57713790505289</v>
       </c>
     </row>
     <row r="43" spans="2:56">
@@ -12134,16 +12134,16 @@
         <v>455</v>
       </c>
       <c r="Y43" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="Z43" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="AA43">
-        <v>0.98861342542180985</v>
+        <v>0.99486868336004353</v>
       </c>
       <c r="AB43">
-        <v>208.75386726681941</v>
+        <v>94.074138399201615</v>
       </c>
       <c r="AD43" t="s">
         <v>388</v>
@@ -12173,13 +12173,13 @@
         <v>758</v>
       </c>
       <c r="AN43" t="s">
-        <v>575</v>
+        <v>554</v>
       </c>
       <c r="AO43">
-        <v>0.99427706626581025</v>
+        <v>0.9909825022671549</v>
       </c>
       <c r="AP43">
-        <v>104.92045179347788</v>
+        <v>165.32079176882775</v>
       </c>
     </row>
     <row r="44" spans="2:56">
@@ -12244,16 +12244,16 @@
         <v>457</v>
       </c>
       <c r="Y44" t="s">
-        <v>371</v>
+        <v>315</v>
       </c>
       <c r="Z44" t="s">
-        <v>558</v>
+        <v>576</v>
       </c>
       <c r="AA44">
-        <v>0.99214710198915512</v>
+        <v>0.99449168757100159</v>
       </c>
       <c r="AB44">
-        <v>143.9697968654902</v>
+        <v>100.98572786497003</v>
       </c>
       <c r="AD44" t="s">
         <v>388</v>
@@ -12283,13 +12283,13 @@
         <v>759</v>
       </c>
       <c r="AN44" t="s">
-        <v>561</v>
+        <v>587</v>
       </c>
       <c r="AO44">
-        <v>0.99121477309476114</v>
+        <v>0.99409301598387334</v>
       </c>
       <c r="AP44">
-        <v>161.062493262712</v>
+        <v>108.29470696232133</v>
       </c>
     </row>
     <row r="45" spans="2:56">
@@ -12354,16 +12354,16 @@
         <v>459</v>
       </c>
       <c r="Y45" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Z45" t="s">
-        <v>561</v>
+        <v>577</v>
       </c>
       <c r="AA45">
-        <v>0.99329032731129618</v>
+        <v>0.99024242083669489</v>
       </c>
       <c r="AB45">
-        <v>123.01066595957037</v>
+        <v>178.88895132725995</v>
       </c>
       <c r="AD45" t="s">
         <v>388</v>
@@ -12393,13 +12393,13 @@
         <v>760</v>
       </c>
       <c r="AN45" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
       <c r="AO45">
-        <v>0.99329038799154346</v>
+        <v>0.99552417511484081</v>
       </c>
       <c r="AP45">
-        <v>123.0095534883708</v>
+        <v>82.056789561251392</v>
       </c>
     </row>
     <row r="46" spans="2:56">
@@ -12464,16 +12464,16 @@
         <v>461</v>
       </c>
       <c r="Y46" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="Z46" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AA46">
-        <v>0.99270917988914098</v>
+        <v>0.99373222027139962</v>
       </c>
       <c r="AB46">
-        <v>133.66503536574953</v>
+        <v>114.90929502433978</v>
       </c>
       <c r="AD46" t="s">
         <v>388</v>
@@ -12503,13 +12503,13 @@
         <v>761</v>
       </c>
       <c r="AN46" t="s">
-        <v>587</v>
+        <v>549</v>
       </c>
       <c r="AO46">
-        <v>0.99201459591478169</v>
+        <v>0.98351881644633699</v>
       </c>
       <c r="AP46">
-        <v>146.39907489566812</v>
+        <v>302.15503181715462</v>
       </c>
     </row>
     <row r="47" spans="2:56">
@@ -12574,16 +12574,16 @@
         <v>463</v>
       </c>
       <c r="Y47" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="Z47" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AA47">
-        <v>0.99529481894214911</v>
+        <v>0.99448854992358493</v>
       </c>
       <c r="AB47">
-        <v>86.26165272726621</v>
+        <v>101.04325140094389</v>
       </c>
       <c r="AD47" t="s">
         <v>388</v>
@@ -12613,13 +12613,13 @@
         <v>762</v>
       </c>
       <c r="AN47" t="s">
-        <v>556</v>
+        <v>590</v>
       </c>
       <c r="AO47">
-        <v>0.99418817704352525</v>
+        <v>0.99485915243795964</v>
       </c>
       <c r="AP47">
-        <v>106.5500875353703</v>
+        <v>94.248871970740922</v>
       </c>
     </row>
     <row r="48" spans="2:56">
@@ -12684,16 +12684,16 @@
         <v>465</v>
       </c>
       <c r="Y48" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="Z48" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AA48">
-        <v>0.99452055660680094</v>
+        <v>0.99338948553444661</v>
       </c>
       <c r="AB48">
-        <v>100.45646220864869</v>
+        <v>121.19276520181113</v>
       </c>
       <c r="AD48" t="s">
         <v>388</v>
@@ -12723,13 +12723,13 @@
         <v>763</v>
       </c>
       <c r="AN48" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="AO48">
-        <v>0.98264007513427243</v>
+        <v>0.98978334793138389</v>
       </c>
       <c r="AP48">
-        <v>318.26528920500613</v>
+        <v>187.30528792462934</v>
       </c>
     </row>
     <row r="49" spans="2:42">
@@ -12794,16 +12794,16 @@
         <v>467</v>
       </c>
       <c r="Y49" t="s">
-        <v>332</v>
+        <v>373</v>
       </c>
       <c r="Z49" t="s">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="AA49">
-        <v>0.99275682304809643</v>
+        <v>0.99418942224649776</v>
       </c>
       <c r="AB49">
-        <v>132.79157745156544</v>
+        <v>106.527258814208</v>
       </c>
       <c r="AD49" t="s">
         <v>388</v>
@@ -12833,13 +12833,13 @@
         <v>764</v>
       </c>
       <c r="AN49" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="AO49">
-        <v>0.98973070091819682</v>
+        <v>0.99327255672282233</v>
       </c>
       <c r="AP49">
-        <v>188.27048316639193</v>
+        <v>123.33646008159123</v>
       </c>
     </row>
     <row r="50" spans="2:42">
@@ -12904,16 +12904,16 @@
         <v>469</v>
       </c>
       <c r="Y50" t="s">
-        <v>348</v>
+        <v>383</v>
       </c>
       <c r="Z50" t="s">
         <v>581</v>
       </c>
       <c r="AA50">
-        <v>0.98666777524932958</v>
+        <v>0.99472498859344116</v>
       </c>
       <c r="AB50">
-        <v>244.42412042895722</v>
+        <v>96.708542453579653</v>
       </c>
       <c r="AD50" t="s">
         <v>388</v>
@@ -12943,13 +12943,13 @@
         <v>765</v>
       </c>
       <c r="AN50" t="s">
-        <v>584</v>
+        <v>560</v>
       </c>
       <c r="AO50">
-        <v>0.99017733442899913</v>
+        <v>0.99390831940949842</v>
       </c>
       <c r="AP50">
-        <v>180.08220213501625</v>
+        <v>111.68081082586212</v>
       </c>
     </row>
     <row r="51" spans="2:42">
@@ -13014,16 +13014,16 @@
         <v>471</v>
       </c>
       <c r="Y51" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="Z51" t="s">
-        <v>551</v>
+        <v>577</v>
       </c>
       <c r="AA51">
-        <v>0.99269116352039599</v>
+        <v>0.99329032731129618</v>
       </c>
       <c r="AB51">
-        <v>133.99533545940744</v>
+        <v>123.01066595957037</v>
       </c>
       <c r="AD51" t="s">
         <v>388</v>
@@ -13053,13 +13053,13 @@
         <v>766</v>
       </c>
       <c r="AN51" t="s">
-        <v>574</v>
+        <v>582</v>
       </c>
       <c r="AO51">
-        <v>0.99392053283098158</v>
+        <v>0.99249186107477694</v>
       </c>
       <c r="AP51">
-        <v>111.45689809867115</v>
+        <v>137.64921362908964</v>
       </c>
     </row>
     <row r="52" spans="2:42">
@@ -13124,16 +13124,16 @@
         <v>473</v>
       </c>
       <c r="Y52" t="s">
-        <v>380</v>
+        <v>352</v>
       </c>
       <c r="Z52" t="s">
         <v>582</v>
       </c>
       <c r="AA52">
-        <v>0.99006453671041028</v>
+        <v>0.99270917988914098</v>
       </c>
       <c r="AB52">
-        <v>182.15016030914441</v>
+        <v>133.66503536574953</v>
       </c>
       <c r="AD52" t="s">
         <v>388</v>
@@ -13163,13 +13163,13 @@
         <v>767</v>
       </c>
       <c r="AN52" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="AO52">
-        <v>0.99519706487556603</v>
+        <v>0.99433320017484694</v>
       </c>
       <c r="AP52">
-        <v>88.053810614623103</v>
+        <v>103.89133012780634</v>
       </c>
     </row>
     <row r="53" spans="2:42">
@@ -13234,16 +13234,16 @@
         <v>475</v>
       </c>
       <c r="Y53" t="s">
-        <v>324</v>
+        <v>362</v>
       </c>
       <c r="Z53" t="s">
-        <v>568</v>
+        <v>561</v>
       </c>
       <c r="AA53">
-        <v>0.98899223079090937</v>
+        <v>0.99529481894214911</v>
       </c>
       <c r="AB53">
-        <v>201.80910216666135</v>
+        <v>86.26165272726621</v>
       </c>
       <c r="AD53" t="s">
         <v>388</v>
@@ -13273,13 +13273,13 @@
         <v>768</v>
       </c>
       <c r="AN53" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
       <c r="AO53">
-        <v>0.99116017126466804</v>
+        <v>0.98660390748007576</v>
       </c>
       <c r="AP53">
-        <v>162.0635268144182</v>
+        <v>245.5950295319436</v>
       </c>
     </row>
     <row r="54" spans="2:42">
@@ -13344,16 +13344,16 @@
         <v>477</v>
       </c>
       <c r="Y54" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="Z54" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="AA54">
-        <v>0.99373922796305081</v>
+        <v>0.99452055660680094</v>
       </c>
       <c r="AB54">
-        <v>114.78082067740091</v>
+        <v>100.45646220864869</v>
       </c>
       <c r="AD54" t="s">
         <v>388</v>
@@ -13383,13 +13383,13 @@
         <v>769</v>
       </c>
       <c r="AN54" t="s">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="AO54">
-        <v>0.99287761065972435</v>
+        <v>0.99356924052650486</v>
       </c>
       <c r="AP54">
-        <v>130.57713790505289</v>
+        <v>117.89725701407761</v>
       </c>
     </row>
     <row r="55" spans="2:42">
@@ -13454,16 +13454,16 @@
         <v>479</v>
       </c>
       <c r="Y55" t="s">
-        <v>354</v>
+        <v>312</v>
       </c>
       <c r="Z55" t="s">
-        <v>583</v>
+        <v>571</v>
       </c>
       <c r="AA55">
-        <v>0.99489337597419902</v>
+        <v>0.99473753513404162</v>
       </c>
       <c r="AB55">
-        <v>93.621440473017302</v>
+        <v>96.478522542569891</v>
       </c>
       <c r="AD55" t="s">
         <v>388</v>
@@ -13493,13 +13493,13 @@
         <v>770</v>
       </c>
       <c r="AN55" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="AO55">
-        <v>0.9909825022671549</v>
+        <v>0.99460493914808601</v>
       </c>
       <c r="AP55">
-        <v>165.32079176882775</v>
+        <v>98.909448951756843</v>
       </c>
     </row>
     <row r="56" spans="2:42">
@@ -13564,16 +13564,16 @@
         <v>481</v>
       </c>
       <c r="Y56" t="s">
-        <v>365</v>
+        <v>320</v>
       </c>
       <c r="Z56" t="s">
-        <v>584</v>
+        <v>551</v>
       </c>
       <c r="AA56">
-        <v>0.98750565217961461</v>
+        <v>0.99462963762315071</v>
       </c>
       <c r="AB56">
-        <v>229.06304337373263</v>
+        <v>98.456643575569544</v>
       </c>
       <c r="AD56" t="s">
         <v>388</v>
@@ -13603,13 +13603,13 @@
         <v>771</v>
       </c>
       <c r="AN56" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AO56">
-        <v>0.99409301598387334</v>
+        <v>0.99226255824077458</v>
       </c>
       <c r="AP56">
-        <v>108.29470696232133</v>
+        <v>141.853098919133</v>
       </c>
     </row>
     <row r="57" spans="2:42">
@@ -13674,16 +13674,16 @@
         <v>483</v>
       </c>
       <c r="Y57" t="s">
-        <v>377</v>
+        <v>327</v>
       </c>
       <c r="Z57" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AA57">
-        <v>0.99303639237349761</v>
+        <v>0.99184091582017686</v>
       </c>
       <c r="AB57">
-        <v>127.66613981921104</v>
+        <v>149.58320996342505</v>
       </c>
       <c r="AD57" t="s">
         <v>388</v>
@@ -13713,13 +13713,13 @@
         <v>772</v>
       </c>
       <c r="AN57" t="s">
-        <v>562</v>
+        <v>585</v>
       </c>
       <c r="AO57">
-        <v>0.99296413260223493</v>
+        <v>0.9946374817042809</v>
       </c>
       <c r="AP57">
-        <v>128.99090229235989</v>
+        <v>98.312835421515885</v>
       </c>
     </row>
     <row r="58" spans="2:42">
@@ -13784,16 +13784,16 @@
         <v>485</v>
       </c>
       <c r="Y58" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="Z58" t="s">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="AA58">
-        <v>0.99287457171029725</v>
+        <v>0.9956123485295133</v>
       </c>
       <c r="AB58">
-        <v>130.63285197788394</v>
+        <v>80.440276958922396</v>
       </c>
       <c r="AD58" t="s">
         <v>388</v>
@@ -13823,13 +13823,13 @@
         <v>773</v>
       </c>
       <c r="AN58" t="s">
-        <v>551</v>
+        <v>581</v>
       </c>
       <c r="AO58">
-        <v>0.99403594090084912</v>
+        <v>0.99545219173782828</v>
       </c>
       <c r="AP58">
-        <v>109.34108348443232</v>
+        <v>83.376484806480903</v>
       </c>
     </row>
     <row r="59" spans="2:42">
@@ -13894,16 +13894,16 @@
         <v>487</v>
       </c>
       <c r="Y59" t="s">
-        <v>346</v>
+        <v>335</v>
       </c>
       <c r="Z59" t="s">
-        <v>550</v>
+        <v>586</v>
       </c>
       <c r="AA59">
-        <v>0.99268599671594204</v>
+        <v>0.99290883235651795</v>
       </c>
       <c r="AB59">
-        <v>134.09006020772978</v>
+        <v>130.00474013050507</v>
       </c>
       <c r="AD59" t="s">
         <v>388</v>
@@ -13933,13 +13933,13 @@
         <v>774</v>
       </c>
       <c r="AN59" t="s">
-        <v>578</v>
+        <v>549</v>
       </c>
       <c r="AO59">
-        <v>0.98943318015939452</v>
+        <v>0.99170932898012365</v>
       </c>
       <c r="AP59">
-        <v>193.72503041110133</v>
+        <v>151.99563536440075</v>
       </c>
     </row>
     <row r="60" spans="2:42">
@@ -14004,16 +14004,16 @@
         <v>489</v>
       </c>
       <c r="Y60" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="Z60" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="AA60">
-        <v>0.98961378001546085</v>
+        <v>0.98893783962199822</v>
       </c>
       <c r="AB60">
-        <v>190.41403304988424</v>
+        <v>202.8062735966999</v>
       </c>
       <c r="AD60" t="s">
         <v>388</v>
@@ -14043,13 +14043,13 @@
         <v>775</v>
       </c>
       <c r="AN60" t="s">
-        <v>576</v>
+        <v>552</v>
       </c>
       <c r="AO60">
-        <v>0.99037301617060403</v>
+        <v>0.99400997521961898</v>
       </c>
       <c r="AP60">
-        <v>176.49470353892534</v>
+        <v>109.8171209736516</v>
       </c>
     </row>
     <row r="61" spans="2:42">
@@ -14114,16 +14114,16 @@
         <v>491</v>
       </c>
       <c r="Y61" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Z61" t="s">
-        <v>586</v>
+        <v>568</v>
       </c>
       <c r="AA61">
-        <v>0.99402818260314618</v>
+        <v>0.99287457171029725</v>
       </c>
       <c r="AB61">
-        <v>109.48331894231943</v>
+        <v>130.63285197788394</v>
       </c>
       <c r="AD61" t="s">
         <v>388</v>
@@ -14153,13 +14153,13 @@
         <v>776</v>
       </c>
       <c r="AN61" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AO61">
-        <v>0.99215519768283411</v>
+        <v>0.99270356346131094</v>
       </c>
       <c r="AP61">
-        <v>143.82137581470715</v>
+        <v>133.76800320929971</v>
       </c>
     </row>
     <row r="62" spans="2:42">
@@ -14224,16 +14224,16 @@
         <v>493</v>
       </c>
       <c r="Y62" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="Z62" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AA62">
-        <v>0.99351839907880191</v>
+        <v>0.99268599671594204</v>
       </c>
       <c r="AB62">
-        <v>118.82935022196459</v>
+        <v>134.09006020772978</v>
       </c>
       <c r="AD62" t="s">
         <v>388</v>
@@ -14263,13 +14263,13 @@
         <v>777</v>
       </c>
       <c r="AN62" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="AO62">
-        <v>0.99689862129048645</v>
+        <v>0.98675990563829141</v>
       </c>
       <c r="AP62">
-        <v>56.858609674414254</v>
+        <v>242.73506329798991</v>
       </c>
     </row>
     <row r="63" spans="2:42">
@@ -14334,16 +14334,16 @@
         <v>495</v>
       </c>
       <c r="Y63" t="s">
-        <v>338</v>
+        <v>366</v>
       </c>
       <c r="Z63" t="s">
-        <v>587</v>
+        <v>556</v>
       </c>
       <c r="AA63">
-        <v>0.99546714226270061</v>
+        <v>0.98961378001546085</v>
       </c>
       <c r="AB63">
-        <v>83.102391850488004</v>
+        <v>190.41403304988424</v>
       </c>
       <c r="AD63" t="s">
         <v>388</v>
@@ -14373,13 +14373,13 @@
         <v>778</v>
       </c>
       <c r="AN63" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="AO63">
-        <v>0.99177044540821302</v>
+        <v>0.99286153879604566</v>
       </c>
       <c r="AP63">
-        <v>150.87516751609439</v>
+        <v>130.87178873916278</v>
       </c>
     </row>
     <row r="64" spans="2:42">
@@ -14444,16 +14444,16 @@
         <v>497</v>
       </c>
       <c r="Y64" t="s">
-        <v>343</v>
+        <v>309</v>
       </c>
       <c r="Z64" t="s">
-        <v>562</v>
+        <v>589</v>
       </c>
       <c r="AA64">
-        <v>0.99030786115942782</v>
+        <v>0.99245084214861234</v>
       </c>
       <c r="AB64">
-        <v>177.68921207715613</v>
+        <v>138.40122727544065</v>
       </c>
       <c r="AD64" t="s">
         <v>388</v>
@@ -14483,13 +14483,13 @@
         <v>779</v>
       </c>
       <c r="AN64" t="s">
-        <v>588</v>
+        <v>558</v>
       </c>
       <c r="AO64">
-        <v>0.99458282020478328</v>
+        <v>0.99286149679037794</v>
       </c>
       <c r="AP64">
-        <v>99.314962912306555</v>
+        <v>130.8725588430718</v>
       </c>
     </row>
     <row r="65" spans="2:42">
@@ -14554,16 +14554,16 @@
         <v>499</v>
       </c>
       <c r="Y65" t="s">
-        <v>368</v>
+        <v>328</v>
       </c>
       <c r="Z65" t="s">
-        <v>576</v>
+        <v>584</v>
       </c>
       <c r="AA65">
-        <v>0.98889208513122484</v>
+        <v>0.99410067440989558</v>
       </c>
       <c r="AB65">
-        <v>203.64510592754459</v>
+        <v>108.15430248524751</v>
       </c>
       <c r="AD65" t="s">
         <v>388</v>
@@ -14596,10 +14596,10 @@
         <v>577</v>
       </c>
       <c r="AO65">
-        <v>0.9919109979004006</v>
+        <v>0.99188199243556163</v>
       </c>
       <c r="AP65">
-        <v>148.29837182598865</v>
+        <v>148.83013868136976</v>
       </c>
     </row>
     <row r="66" spans="2:42">
@@ -14664,16 +14664,16 @@
         <v>501</v>
       </c>
       <c r="Y66" t="s">
-        <v>378</v>
+        <v>359</v>
       </c>
       <c r="Z66" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="AA66">
-        <v>0.98915595886276608</v>
+        <v>0.9875438296240775</v>
       </c>
       <c r="AB66">
-        <v>198.80742084928778</v>
+        <v>228.36312355857854</v>
       </c>
       <c r="AD66" t="s">
         <v>388</v>
@@ -14703,13 +14703,13 @@
         <v>781</v>
       </c>
       <c r="AN66" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="AO66">
-        <v>0.9944043961659097</v>
+        <v>0.98666678680685382</v>
       </c>
       <c r="AP66">
-        <v>102.58607029165618</v>
+        <v>244.44224187434608</v>
       </c>
     </row>
     <row r="67" spans="2:42">
@@ -14774,16 +14774,16 @@
         <v>503</v>
       </c>
       <c r="Y67" t="s">
-        <v>379</v>
+        <v>360</v>
       </c>
       <c r="Z67" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="AA67">
-        <v>0.99620638875319056</v>
+        <v>0.99433118964233247</v>
       </c>
       <c r="AB67">
-        <v>69.549539524839389</v>
+        <v>103.92818989057204</v>
       </c>
       <c r="AD67" t="s">
         <v>388</v>
@@ -14813,13 +14813,13 @@
         <v>782</v>
       </c>
       <c r="AN67" t="s">
-        <v>593</v>
+        <v>561</v>
       </c>
       <c r="AO67">
-        <v>0.99602637227621282</v>
+        <v>0.99461739117688308</v>
       </c>
       <c r="AP67">
-        <v>72.849841602764897</v>
+        <v>98.68116175714421</v>
       </c>
     </row>
     <row r="68" spans="2:42">
@@ -14884,16 +14884,16 @@
         <v>505</v>
       </c>
       <c r="Y68" t="s">
-        <v>316</v>
+        <v>367</v>
       </c>
       <c r="Z68" t="s">
-        <v>570</v>
+        <v>591</v>
       </c>
       <c r="AA68">
-        <v>0.99335604161179136</v>
+        <v>0.98861342542180985</v>
       </c>
       <c r="AB68">
-        <v>121.80590378382558</v>
+        <v>208.75386726681941</v>
       </c>
       <c r="AD68" t="s">
         <v>388</v>
@@ -14923,13 +14923,13 @@
         <v>783</v>
       </c>
       <c r="AN68" t="s">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="AO68">
-        <v>0.99333586753421554</v>
+        <v>0.98713907316291682</v>
       </c>
       <c r="AP68">
-        <v>122.17576187271403</v>
+        <v>235.78365867985792</v>
       </c>
     </row>
     <row r="69" spans="2:42">
@@ -14994,16 +14994,16 @@
         <v>507</v>
       </c>
       <c r="Y69" t="s">
-        <v>326</v>
+        <v>371</v>
       </c>
       <c r="Z69" t="s">
-        <v>588</v>
+        <v>575</v>
       </c>
       <c r="AA69">
-        <v>0.99498097012747577</v>
+        <v>0.99214710198915512</v>
       </c>
       <c r="AB69">
-        <v>92.015547662944215</v>
+        <v>143.9697968654902</v>
       </c>
       <c r="AD69" t="s">
         <v>388</v>
@@ -15033,13 +15033,13 @@
         <v>784</v>
       </c>
       <c r="AN69" t="s">
-        <v>553</v>
+        <v>584</v>
       </c>
       <c r="AO69">
-        <v>0.99460493914808601</v>
+        <v>0.99427706626581025</v>
       </c>
       <c r="AP69">
-        <v>98.909448951756843</v>
+        <v>104.92045179347788</v>
       </c>
     </row>
     <row r="70" spans="2:42">
@@ -15104,16 +15104,16 @@
         <v>509</v>
       </c>
       <c r="Y70" t="s">
-        <v>341</v>
+        <v>317</v>
       </c>
       <c r="Z70" t="s">
-        <v>589</v>
+        <v>558</v>
       </c>
       <c r="AA70">
-        <v>0.99068678367690288</v>
+        <v>0.98974554419194471</v>
       </c>
       <c r="AB70">
-        <v>170.7422992567804</v>
+        <v>187.99835648101393</v>
       </c>
       <c r="AD70" t="s">
         <v>388</v>
@@ -15143,13 +15143,13 @@
         <v>785</v>
       </c>
       <c r="AN70" t="s">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="AO70">
-        <v>0.99226255824077458</v>
+        <v>0.99121477309476114</v>
       </c>
       <c r="AP70">
-        <v>141.853098919133</v>
+        <v>161.062493262712</v>
       </c>
     </row>
     <row r="71" spans="2:42">
@@ -15214,16 +15214,16 @@
         <v>511</v>
       </c>
       <c r="Y71" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="Z71" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="AA71">
-        <v>0.99380018286737304</v>
+        <v>0.99547433853743716</v>
       </c>
       <c r="AB71">
-        <v>113.66331409816142</v>
+        <v>82.970460146984365</v>
       </c>
       <c r="AD71" t="s">
         <v>388</v>
@@ -15253,13 +15253,13 @@
         <v>786</v>
       </c>
       <c r="AN71" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="AO71">
-        <v>0.99327255672282233</v>
+        <v>0.99329038799154346</v>
       </c>
       <c r="AP71">
-        <v>123.33646008159123</v>
+        <v>123.0095534883708</v>
       </c>
     </row>
     <row r="72" spans="2:42">
@@ -15324,16 +15324,16 @@
         <v>513</v>
       </c>
       <c r="Y72" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="Z72" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="AA72">
-        <v>0.99045178849779958</v>
+        <v>0.99432421190931886</v>
       </c>
       <c r="AB72">
-        <v>175.0505442070075</v>
+        <v>104.05611499582191</v>
       </c>
       <c r="AD72" t="s">
         <v>388</v>
@@ -15363,13 +15363,13 @@
         <v>787</v>
       </c>
       <c r="AN72" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="AO72">
-        <v>0.99390831940949842</v>
+        <v>0.99201459591478169</v>
       </c>
       <c r="AP72">
-        <v>111.68081082586212</v>
+        <v>146.39907489566812</v>
       </c>
     </row>
     <row r="73" spans="2:42">
@@ -15434,16 +15434,16 @@
         <v>515</v>
       </c>
       <c r="Y73" t="s">
-        <v>376</v>
+        <v>357</v>
       </c>
       <c r="Z73" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="AA73">
-        <v>0.99360342768209686</v>
+        <v>0.99439207214359926</v>
       </c>
       <c r="AB73">
-        <v>117.27049249489188</v>
+        <v>102.81201070067981</v>
       </c>
       <c r="AD73" t="s">
         <v>388</v>
@@ -15473,13 +15473,13 @@
         <v>788</v>
       </c>
       <c r="AN73" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="AO73">
-        <v>0.99249186107477694</v>
+        <v>0.99418817704352525</v>
       </c>
       <c r="AP73">
-        <v>137.64921362908964</v>
+        <v>106.5500875353703</v>
       </c>
     </row>
     <row r="74" spans="2:42">
@@ -15544,16 +15544,16 @@
         <v>517</v>
       </c>
       <c r="Y74" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="Z74" t="s">
-        <v>573</v>
+        <v>563</v>
       </c>
       <c r="AA74">
-        <v>0.9941610020412821</v>
+        <v>0.99130148530232876</v>
       </c>
       <c r="AB74">
-        <v>107.04829590982715</v>
+        <v>159.47276945730601</v>
       </c>
       <c r="AD74" t="s">
         <v>388</v>
@@ -15583,13 +15583,13 @@
         <v>789</v>
       </c>
       <c r="AN74" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="AO74">
-        <v>0.99433320017484694</v>
+        <v>0.98264007513427243</v>
       </c>
       <c r="AP74">
-        <v>103.89133012780634</v>
+        <v>318.26528920500613</v>
       </c>
     </row>
     <row r="75" spans="2:42">
@@ -15654,16 +15654,16 @@
         <v>519</v>
       </c>
       <c r="Y75" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="Z75" t="s">
-        <v>553</v>
+        <v>592</v>
       </c>
       <c r="AA75">
-        <v>0.99473753513404162</v>
+        <v>0.99574277994898297</v>
       </c>
       <c r="AB75">
-        <v>96.478522542569891</v>
+        <v>78.049034268645343</v>
       </c>
       <c r="AD75" t="s">
         <v>388</v>
@@ -15693,13 +15693,13 @@
         <v>790</v>
       </c>
       <c r="AN75" t="s">
-        <v>569</v>
+        <v>590</v>
       </c>
       <c r="AO75">
-        <v>0.98660390748007576</v>
+        <v>0.98973070091819682</v>
       </c>
       <c r="AP75">
-        <v>245.5950295319436</v>
+        <v>188.27048316639193</v>
       </c>
     </row>
     <row r="76" spans="2:42">
@@ -15764,16 +15764,16 @@
         <v>521</v>
       </c>
       <c r="Y76" t="s">
-        <v>320</v>
+        <v>345</v>
       </c>
       <c r="Z76" t="s">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="AA76">
-        <v>0.99462963762315071</v>
+        <v>0.98237714666165721</v>
       </c>
       <c r="AB76">
-        <v>98.456643575569544</v>
+        <v>323.08564453628389</v>
       </c>
       <c r="AD76" t="s">
         <v>388</v>
@@ -15803,13 +15803,13 @@
         <v>791</v>
       </c>
       <c r="AN76" t="s">
-        <v>582</v>
+        <v>556</v>
       </c>
       <c r="AO76">
-        <v>0.99356924052650486</v>
+        <v>0.99017733442899913</v>
       </c>
       <c r="AP76">
-        <v>117.89725701407761</v>
+        <v>180.08220213501625</v>
       </c>
     </row>
     <row r="77" spans="2:42">
@@ -15874,16 +15874,16 @@
         <v>523</v>
       </c>
       <c r="Y77" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="Z77" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="AA77">
-        <v>0.99184091582017686</v>
+        <v>0.98850112471309615</v>
       </c>
       <c r="AB77">
-        <v>149.58320996342505</v>
+        <v>210.81271359323659</v>
       </c>
     </row>
     <row r="78" spans="2:42">
@@ -15948,16 +15948,16 @@
         <v>525</v>
       </c>
       <c r="Y78" t="s">
-        <v>329</v>
+        <v>358</v>
       </c>
       <c r="Z78" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="AA78">
-        <v>0.9956123485295133</v>
+        <v>0.99482221718343289</v>
       </c>
       <c r="AB78">
-        <v>80.440276958922396</v>
+        <v>94.926018303729833</v>
       </c>
     </row>
     <row r="79" spans="2:42">
@@ -16022,16 +16022,16 @@
         <v>527</v>
       </c>
       <c r="Y79" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="Z79" t="s">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="AA79">
-        <v>0.99290883235651795</v>
+        <v>0.99395804884905048</v>
       </c>
       <c r="AB79">
-        <v>130.00474013050507</v>
+        <v>110.76910443407451</v>
       </c>
     </row>
     <row r="80" spans="2:42">
@@ -16096,16 +16096,16 @@
         <v>529</v>
       </c>
       <c r="Y80" t="s">
-        <v>356</v>
+        <v>314</v>
       </c>
       <c r="Z80" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="AA80">
-        <v>0.98893783962199822</v>
+        <v>0.98876972660449969</v>
       </c>
       <c r="AB80">
-        <v>202.8062735966999</v>
+        <v>205.88834558417196</v>
       </c>
     </row>
     <row r="81" spans="2:28">
@@ -16170,16 +16170,16 @@
         <v>531</v>
       </c>
       <c r="Y81" t="s">
-        <v>310</v>
+        <v>353</v>
       </c>
       <c r="Z81" t="s">
-        <v>574</v>
+        <v>555</v>
       </c>
       <c r="AA81">
-        <v>0.99395804884905048</v>
+        <v>0.99543619104776615</v>
       </c>
       <c r="AB81">
-        <v>110.76910443407451</v>
+        <v>83.669830790954578</v>
       </c>
     </row>
     <row r="82" spans="2:28">
@@ -16244,16 +16244,16 @@
         <v>533</v>
       </c>
       <c r="Y82" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="Z82" t="s">
-        <v>560</v>
+        <v>585</v>
       </c>
       <c r="AA82">
-        <v>0.98876972660449969</v>
+        <v>0.99402818260314618</v>
       </c>
       <c r="AB82">
-        <v>205.88834558417196</v>
+        <v>109.48331894231943</v>
       </c>
     </row>
     <row r="83" spans="2:28">
@@ -16318,16 +16318,16 @@
         <v>535</v>
       </c>
       <c r="Y83" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="Z83" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="AA83">
-        <v>0.99543619104776615</v>
+        <v>0.99351839907880191</v>
       </c>
       <c r="AB83">
-        <v>83.669830790954578</v>
+        <v>118.82935022196459</v>
       </c>
     </row>
     <row r="84" spans="2:28">
@@ -16392,16 +16392,16 @@
         <v>537</v>
       </c>
       <c r="Y84" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="Z84" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AA84">
-        <v>0.9938080410601946</v>
+        <v>0.99546714226270061</v>
       </c>
       <c r="AB84">
-        <v>113.51924722976577</v>
+        <v>83.102391850488004</v>
       </c>
     </row>
     <row r="85" spans="2:28">
@@ -16466,16 +16466,16 @@
         <v>539</v>
       </c>
       <c r="Y85" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="Z85" t="s">
-        <v>592</v>
+        <v>578</v>
       </c>
       <c r="AA85">
-        <v>0.99382896634585005</v>
+        <v>0.99030786115942782</v>
       </c>
       <c r="AB85">
-        <v>113.13561699274842</v>
+        <v>177.68921207715613</v>
       </c>
     </row>
     <row r="86" spans="2:28">
@@ -16540,16 +16540,16 @@
         <v>541</v>
       </c>
       <c r="Y86" t="s">
-        <v>375</v>
+        <v>368</v>
       </c>
       <c r="Z86" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AA86">
-        <v>0.99140742806735527</v>
+        <v>0.98889208513122484</v>
       </c>
       <c r="AB86">
-        <v>157.53048543182001</v>
+        <v>203.64510592754459</v>
       </c>
     </row>
     <row r="87" spans="2:28">
@@ -16614,16 +16614,16 @@
         <v>543</v>
       </c>
       <c r="Y87" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="Z87" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="AA87">
-        <v>0.98706515821359619</v>
+        <v>0.98915595886276608</v>
       </c>
       <c r="AB87">
-        <v>237.13876608406935</v>
+        <v>198.80742084928778</v>
       </c>
     </row>
     <row r="88" spans="2:28">
@@ -16688,16 +16688,16 @@
         <v>545</v>
       </c>
       <c r="Y88" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="Z88" t="s">
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="AA88">
-        <v>0.99504215698918186</v>
+        <v>0.99620638875319056</v>
       </c>
       <c r="AB88">
-        <v>90.893788531666857</v>
+        <v>69.549539524839389</v>
       </c>
     </row>
   </sheetData>
@@ -16706,7 +16706,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1EDDBA-3FEC-4FFA-B64B-0D1F0218426C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCC1CEA1-A0C6-4230-8552-64EB8E2561D1}">
   <dimension ref="B9:Z76"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -16818,7 +16818,7 @@
         <v>864</v>
       </c>
       <c r="K11" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
       <c r="L11">
         <v>33.83147659537768</v>
@@ -16851,7 +16851,7 @@
         <v>996</v>
       </c>
       <c r="X11" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="Y11">
         <v>30.066749999999999</v>
@@ -16886,7 +16886,7 @@
         <v>866</v>
       </c>
       <c r="K12" t="s">
-        <v>784</v>
+        <v>770</v>
       </c>
       <c r="L12">
         <v>27.804556055352069</v>
@@ -16919,7 +16919,7 @@
         <v>998</v>
       </c>
       <c r="X12" t="s">
-        <v>859</v>
+        <v>844</v>
       </c>
       <c r="Y12">
         <v>17.4435</v>
@@ -16954,7 +16954,7 @@
         <v>868</v>
       </c>
       <c r="K13" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="L13">
         <v>24.791203937070382</v>
@@ -16987,7 +16987,7 @@
         <v>1000</v>
       </c>
       <c r="X13" t="s">
-        <v>842</v>
+        <v>847</v>
       </c>
       <c r="Y13">
         <v>17.109749999999998</v>
@@ -17022,7 +17022,7 @@
         <v>870</v>
       </c>
       <c r="K14" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
       <c r="L14">
         <v>34.2342595317402</v>
@@ -17055,7 +17055,7 @@
         <v>1002</v>
       </c>
       <c r="X14" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="Y14">
         <v>21.135750000000002</v>
@@ -17090,7 +17090,7 @@
         <v>872</v>
       </c>
       <c r="K15" t="s">
-        <v>756</v>
+        <v>744</v>
       </c>
       <c r="L15">
         <v>24.913123886642243</v>
@@ -17123,7 +17123,7 @@
         <v>1004</v>
       </c>
       <c r="X15" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="Y15">
         <v>4.07775</v>
@@ -17158,7 +17158,7 @@
         <v>874</v>
       </c>
       <c r="K16" t="s">
-        <v>739</v>
+        <v>779</v>
       </c>
       <c r="L16">
         <v>58.034317529098374</v>
@@ -17191,7 +17191,7 @@
         <v>1006</v>
       </c>
       <c r="X16" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="Y16">
         <v>6.6974999999999998</v>
@@ -17226,7 +17226,7 @@
         <v>876</v>
       </c>
       <c r="K17" t="s">
-        <v>777</v>
+        <v>737</v>
       </c>
       <c r="L17">
         <v>7.6837750207160314</v>
@@ -17259,7 +17259,7 @@
         <v>1008</v>
       </c>
       <c r="X17" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="Y17">
         <v>10.605</v>
@@ -17294,7 +17294,7 @@
         <v>878</v>
       </c>
       <c r="K18" t="s">
-        <v>778</v>
+        <v>738</v>
       </c>
       <c r="L18">
         <v>16.250223804119301</v>
@@ -17327,7 +17327,7 @@
         <v>1010</v>
       </c>
       <c r="X18" t="s">
-        <v>854</v>
+        <v>860</v>
       </c>
       <c r="Y18">
         <v>22.638000000000002</v>
@@ -17395,7 +17395,7 @@
         <v>1012</v>
       </c>
       <c r="X19" t="s">
-        <v>860</v>
+        <v>845</v>
       </c>
       <c r="Y19">
         <v>39.393000000000001</v>
@@ -17430,7 +17430,7 @@
         <v>882</v>
       </c>
       <c r="K20" t="s">
-        <v>786</v>
+        <v>764</v>
       </c>
       <c r="L20">
         <v>28.992008200964371</v>
@@ -17463,7 +17463,7 @@
         <v>1014</v>
       </c>
       <c r="X20" t="s">
-        <v>850</v>
+        <v>855</v>
       </c>
       <c r="Y20">
         <v>26.508749999999999</v>
@@ -17498,7 +17498,7 @@
         <v>884</v>
       </c>
       <c r="K21" t="s">
-        <v>747</v>
+        <v>760</v>
       </c>
       <c r="L21">
         <v>21.992280780836001</v>
@@ -17531,7 +17531,7 @@
         <v>1016</v>
       </c>
       <c r="X21" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="Y21">
         <v>32.472000000000001</v>
@@ -17566,7 +17566,7 @@
         <v>886</v>
       </c>
       <c r="K22" t="s">
-        <v>748</v>
+        <v>761</v>
       </c>
       <c r="L22">
         <v>22.810097654497607</v>
@@ -17599,7 +17599,7 @@
         <v>1018</v>
       </c>
       <c r="X22" t="s">
-        <v>844</v>
+        <v>849</v>
       </c>
       <c r="Y22">
         <v>51.573749999999997</v>
@@ -17634,7 +17634,7 @@
         <v>888</v>
       </c>
       <c r="K23" t="s">
-        <v>751</v>
+        <v>774</v>
       </c>
       <c r="L23">
         <v>82.640164540088762</v>
@@ -17667,7 +17667,7 @@
         <v>1020</v>
       </c>
       <c r="X23" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="Y23">
         <v>10.83</v>
@@ -17702,7 +17702,7 @@
         <v>890</v>
       </c>
       <c r="K24" t="s">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="L24">
         <v>31.759670242178537</v>
@@ -17735,7 +17735,7 @@
         <v>1022</v>
       </c>
       <c r="X24" t="s">
-        <v>841</v>
+        <v>846</v>
       </c>
       <c r="Y24">
         <v>17.925000000000001</v>
@@ -17770,7 +17770,7 @@
         <v>892</v>
       </c>
       <c r="K25" t="s">
-        <v>752</v>
+        <v>775</v>
       </c>
       <c r="L25">
         <v>11.496369756329127</v>
@@ -17803,7 +17803,7 @@
         <v>1024</v>
       </c>
       <c r="X25" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="Y25">
         <v>19.481999999999999</v>
@@ -17838,7 +17838,7 @@
         <v>894</v>
       </c>
       <c r="K26" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="L26">
         <v>10.908640183890601</v>
@@ -17871,7 +17871,7 @@
         <v>1026</v>
       </c>
       <c r="X26" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="Y26">
         <v>24.132000000000001</v>
@@ -17906,7 +17906,7 @@
         <v>896</v>
       </c>
       <c r="K27" t="s">
-        <v>779</v>
+        <v>739</v>
       </c>
       <c r="L27">
         <v>27.909273114027371</v>
@@ -17939,7 +17939,7 @@
         <v>1028</v>
       </c>
       <c r="X27" t="s">
-        <v>852</v>
+        <v>842</v>
       </c>
       <c r="Y27">
         <v>9.37575</v>
@@ -17974,7 +17974,7 @@
         <v>898</v>
       </c>
       <c r="K28" t="s">
-        <v>758</v>
+        <v>784</v>
       </c>
       <c r="L28">
         <v>35.507746640042782</v>
@@ -18007,7 +18007,7 @@
         <v>1030</v>
       </c>
       <c r="X28" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="Y28">
         <v>10.142250000000001</v>
@@ -18042,7 +18042,7 @@
         <v>900</v>
       </c>
       <c r="K29" t="s">
-        <v>736</v>
+        <v>751</v>
       </c>
       <c r="L29">
         <v>26.872192854848723</v>
@@ -18075,7 +18075,7 @@
         <v>1032</v>
       </c>
       <c r="X29" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="Y29">
         <v>14.205</v>
@@ -18110,7 +18110,7 @@
         <v>902</v>
       </c>
       <c r="K30" t="s">
-        <v>734</v>
+        <v>772</v>
       </c>
       <c r="L30">
         <v>31.889876701248639</v>
@@ -18143,7 +18143,7 @@
         <v>1034</v>
       </c>
       <c r="X30" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="Y30">
         <v>28.951499999999999</v>
@@ -18211,7 +18211,7 @@
         <v>1036</v>
       </c>
       <c r="X31" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="Y31">
         <v>32.726999999999997</v>
@@ -18246,7 +18246,7 @@
         <v>906</v>
       </c>
       <c r="K32" t="s">
-        <v>759</v>
+        <v>785</v>
       </c>
       <c r="L32">
         <v>55.67336781800514</v>
@@ -18279,7 +18279,7 @@
         <v>1038</v>
       </c>
       <c r="X32" t="s">
-        <v>853</v>
+        <v>843</v>
       </c>
       <c r="Y32">
         <v>29.553000000000001</v>
@@ -18314,7 +18314,7 @@
         <v>908</v>
       </c>
       <c r="K33" t="s">
-        <v>740</v>
+        <v>780</v>
       </c>
       <c r="L33">
         <v>40.30121650051354</v>
@@ -18347,7 +18347,7 @@
         <v>1040</v>
       </c>
       <c r="X33" t="s">
-        <v>845</v>
+        <v>850</v>
       </c>
       <c r="Y33">
         <v>18.38775</v>
@@ -18382,7 +18382,7 @@
         <v>910</v>
       </c>
       <c r="K34" t="s">
-        <v>760</v>
+        <v>786</v>
       </c>
       <c r="L34">
         <v>2.2018767330895068</v>
@@ -18415,7 +18415,7 @@
         <v>1042</v>
       </c>
       <c r="X34" t="s">
-        <v>846</v>
+        <v>851</v>
       </c>
       <c r="Y34">
         <v>31.49325</v>
@@ -18450,7 +18450,7 @@
         <v>912</v>
       </c>
       <c r="K35" t="s">
-        <v>761</v>
+        <v>787</v>
       </c>
       <c r="L35">
         <v>0.51870876860917992</v>
@@ -18485,7 +18485,7 @@
         <v>914</v>
       </c>
       <c r="K36" t="s">
-        <v>762</v>
+        <v>788</v>
       </c>
       <c r="L36">
         <v>33.956844037805517</v>
@@ -18520,7 +18520,7 @@
         <v>916</v>
       </c>
       <c r="K37" t="s">
-        <v>787</v>
+        <v>765</v>
       </c>
       <c r="L37">
         <v>15.006880463771946</v>
@@ -18555,7 +18555,7 @@
         <v>918</v>
       </c>
       <c r="K38" t="s">
-        <v>753</v>
+        <v>776</v>
       </c>
       <c r="L38">
         <v>23.284229642731745</v>
@@ -18590,7 +18590,7 @@
         <v>920</v>
       </c>
       <c r="K39" t="s">
-        <v>772</v>
+        <v>746</v>
       </c>
       <c r="L39">
         <v>15.321352411640023</v>
@@ -18625,7 +18625,7 @@
         <v>922</v>
       </c>
       <c r="K40" t="s">
-        <v>737</v>
+        <v>752</v>
       </c>
       <c r="L40">
         <v>23.785304147591408</v>
@@ -18660,7 +18660,7 @@
         <v>924</v>
       </c>
       <c r="K41" t="s">
-        <v>769</v>
+        <v>757</v>
       </c>
       <c r="L41">
         <v>52.745166437734376</v>
@@ -18695,7 +18695,7 @@
         <v>926</v>
       </c>
       <c r="K42" t="s">
-        <v>763</v>
+        <v>789</v>
       </c>
       <c r="L42">
         <v>33.61899681334765</v>
@@ -18730,7 +18730,7 @@
         <v>928</v>
       </c>
       <c r="K43" t="s">
-        <v>738</v>
+        <v>753</v>
       </c>
       <c r="L43">
         <v>11.593697444968496</v>
@@ -18765,7 +18765,7 @@
         <v>930</v>
       </c>
       <c r="K44" t="s">
-        <v>770</v>
+        <v>758</v>
       </c>
       <c r="L44">
         <v>74.024525145569001</v>
@@ -18800,7 +18800,7 @@
         <v>932</v>
       </c>
       <c r="K45" t="s">
-        <v>741</v>
+        <v>781</v>
       </c>
       <c r="L45">
         <v>16.258644020270342</v>
@@ -18835,7 +18835,7 @@
         <v>934</v>
       </c>
       <c r="K46" t="s">
-        <v>773</v>
+        <v>747</v>
       </c>
       <c r="L46">
         <v>26.813047414923648</v>
@@ -18870,7 +18870,7 @@
         <v>936</v>
       </c>
       <c r="K47" t="s">
-        <v>745</v>
+        <v>732</v>
       </c>
       <c r="L47">
         <v>16.546770964036483</v>
@@ -18905,7 +18905,7 @@
         <v>938</v>
       </c>
       <c r="K48" t="s">
-        <v>788</v>
+        <v>766</v>
       </c>
       <c r="L48">
         <v>11.997781844082855</v>
@@ -18940,7 +18940,7 @@
         <v>940</v>
       </c>
       <c r="K49" t="s">
-        <v>780</v>
+        <v>740</v>
       </c>
       <c r="L49">
         <v>46.243621179927722</v>
@@ -19010,7 +19010,7 @@
         <v>944</v>
       </c>
       <c r="K51" t="s">
-        <v>789</v>
+        <v>767</v>
       </c>
       <c r="L51">
         <v>38.145385819354424</v>
@@ -19045,7 +19045,7 @@
         <v>946</v>
       </c>
       <c r="K52" t="s">
-        <v>757</v>
+        <v>745</v>
       </c>
       <c r="L52">
         <v>25.369500443235932</v>
@@ -19080,7 +19080,7 @@
         <v>948</v>
       </c>
       <c r="K53" t="s">
-        <v>771</v>
+        <v>759</v>
       </c>
       <c r="L53">
         <v>39.105697164199093</v>
@@ -19115,7 +19115,7 @@
         <v>950</v>
       </c>
       <c r="K54" t="s">
-        <v>749</v>
+        <v>762</v>
       </c>
       <c r="L54">
         <v>20.763566167973863</v>
@@ -19150,7 +19150,7 @@
         <v>952</v>
       </c>
       <c r="K55" t="s">
-        <v>764</v>
+        <v>790</v>
       </c>
       <c r="L55">
         <v>35.376685860779752</v>
@@ -19220,7 +19220,7 @@
         <v>956</v>
       </c>
       <c r="K57" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="L57">
         <v>33.038237032166357</v>
@@ -19255,7 +19255,7 @@
         <v>958</v>
       </c>
       <c r="K58" t="s">
-        <v>774</v>
+        <v>748</v>
       </c>
       <c r="L58">
         <v>22.937581762872757</v>
@@ -19290,7 +19290,7 @@
         <v>960</v>
       </c>
       <c r="K59" t="s">
-        <v>742</v>
+        <v>782</v>
       </c>
       <c r="L59">
         <v>37.854069118280655</v>
@@ -19325,7 +19325,7 @@
         <v>962</v>
       </c>
       <c r="K60" t="s">
-        <v>781</v>
+        <v>741</v>
       </c>
       <c r="L60">
         <v>19.031552923919683</v>
@@ -19360,7 +19360,7 @@
         <v>964</v>
       </c>
       <c r="K61" t="s">
-        <v>754</v>
+        <v>777</v>
       </c>
       <c r="L61">
         <v>22.881530103416733</v>
@@ -19395,7 +19395,7 @@
         <v>966</v>
       </c>
       <c r="K62" t="s">
-        <v>765</v>
+        <v>791</v>
       </c>
       <c r="L62">
         <v>66.366737714251741</v>
@@ -19430,7 +19430,7 @@
         <v>968</v>
       </c>
       <c r="K63" t="s">
-        <v>743</v>
+        <v>783</v>
       </c>
       <c r="L63">
         <v>37.179299980729631</v>
@@ -19465,7 +19465,7 @@
         <v>970</v>
       </c>
       <c r="K64" t="s">
-        <v>775</v>
+        <v>749</v>
       </c>
       <c r="L64">
         <v>75.340015936683557</v>
@@ -19500,7 +19500,7 @@
         <v>972</v>
       </c>
       <c r="K65" t="s">
-        <v>790</v>
+        <v>768</v>
       </c>
       <c r="L65">
         <v>1.671977286085228</v>
@@ -19535,7 +19535,7 @@
         <v>974</v>
       </c>
       <c r="K66" t="s">
-        <v>776</v>
+        <v>750</v>
       </c>
       <c r="L66">
         <v>21.281833534179093</v>
@@ -19570,7 +19570,7 @@
         <v>976</v>
       </c>
       <c r="K67" t="s">
-        <v>785</v>
+        <v>771</v>
       </c>
       <c r="L67">
         <v>20.373488892344575</v>
@@ -19605,7 +19605,7 @@
         <v>978</v>
       </c>
       <c r="K68" t="s">
-        <v>750</v>
+        <v>763</v>
       </c>
       <c r="L68">
         <v>4.2525609415274319</v>
@@ -19640,7 +19640,7 @@
         <v>980</v>
       </c>
       <c r="K69" t="s">
-        <v>746</v>
+        <v>733</v>
       </c>
       <c r="L69">
         <v>11.876635800692616</v>
@@ -19675,7 +19675,7 @@
         <v>982</v>
       </c>
       <c r="K70" t="s">
-        <v>791</v>
+        <v>769</v>
       </c>
       <c r="L70">
         <v>31.752829963824876</v>
@@ -19710,7 +19710,7 @@
         <v>984</v>
       </c>
       <c r="K71" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="L71">
         <v>26.523136640432838</v>
@@ -19745,7 +19745,7 @@
         <v>986</v>
       </c>
       <c r="K72" t="s">
-        <v>755</v>
+        <v>778</v>
       </c>
       <c r="L72">
         <v>33.765756839519163</v>
@@ -19780,7 +19780,7 @@
         <v>988</v>
       </c>
       <c r="K73" t="s">
-        <v>735</v>
+        <v>773</v>
       </c>
       <c r="L73">
         <v>17.233040840286481</v>
@@ -19815,7 +19815,7 @@
         <v>990</v>
       </c>
       <c r="K74" t="s">
-        <v>782</v>
+        <v>742</v>
       </c>
       <c r="L74">
         <v>10.225876074214261</v>
@@ -19850,7 +19850,7 @@
         <v>992</v>
       </c>
       <c r="K75" t="s">
-        <v>783</v>
+        <v>743</v>
       </c>
       <c r="L75">
         <v>19.944768886736487</v>
@@ -19900,7 +19900,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59278195-21B3-4545-BB53-0CFF916599F1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B165C92-AE90-4B37-9696-F391E83EB392}">
   <dimension ref="B9:Y151"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -24720,7 +24720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{322EC5E5-C3B3-4C3C-8871-0D6C3EA72DF5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E84C49EE-ECFD-48A7-A926-C7B0656D2444}">
   <dimension ref="B9:T79"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
